--- a/docs/COPY-AUDIT.xlsx
+++ b/docs/COPY-AUDIT.xlsx
@@ -400,17 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H724"/>
-  <cols>
-    <col min="1" max="1" width="22.83203125" customWidth="1"/>
-    <col min="2" max="2" width="46.83203125" customWidth="1"/>
-    <col min="3" max="3" width="70.83203125" customWidth="1"/>
-    <col min="4" max="4" width="16.83203125" customWidth="1"/>
-    <col min="5" max="5" width="60.83203125" customWidth="1"/>
-    <col min="6" max="6" width="70.83203125" customWidth="1"/>
-    <col min="7" max="7" width="46.83203125" customWidth="1"/>
-    <col min="8" max="8" width="14.83203125" customWidth="1"/>
-  </cols>
+  <dimension ref="A1:I724"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -437,6 +427,9 @@
       <c r="H1" t="str">
         <v>source kind</v>
       </c>
+      <c r="I1" t="str">
+        <v>applied</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -463,6 +456,9 @@
       <c r="H2" t="str">
         <v>html-text</v>
       </c>
+      <c r="I2" t="str">
+        <v>applied by hand: &lt;title&gt; is now the product default (Warehouse Management System); after sign-in the tab shows "{tenant name} · WMS" from /auth/me tenantName (BRAND in js/util.js)</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -489,6 +485,9 @@
       <c r="H3" t="str">
         <v>html-text</v>
       </c>
+      <c r="I3" t="str">
+        <v>applied by hand: sidebar brand is BRAND.product (WMS) with the tenant name underneath from /auth/me; login header and manifest.json follow the same constant</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -515,6 +514,9 @@
       <c r="H4" t="str">
         <v>html-text</v>
       </c>
+      <c r="I4" t="str">
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
@@ -541,6 +543,9 @@
       <c r="H5" t="str">
         <v>html-text</v>
       </c>
+      <c r="I5" t="str">
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
@@ -567,6 +572,9 @@
       <c r="H6" t="str">
         <v>html-text</v>
       </c>
+      <c r="I6" t="str">
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
@@ -593,6 +601,9 @@
       <c r="H7" t="str">
         <v>html-text</v>
       </c>
+      <c r="I7" t="str">
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
@@ -619,6 +630,9 @@
       <c r="H8" t="str">
         <v>html-text</v>
       </c>
+      <c r="I8" t="str">
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
@@ -645,6 +659,9 @@
       <c r="H9" t="str">
         <v>html-text</v>
       </c>
+      <c r="I9" t="str">
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
@@ -671,6 +688,9 @@
       <c r="H10" t="str">
         <v>html-text</v>
       </c>
+      <c r="I10" t="str">
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
@@ -697,6 +717,9 @@
       <c r="H11" t="str">
         <v>html-text</v>
       </c>
+      <c r="I11" t="str">
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
@@ -723,6 +746,9 @@
       <c r="H12" t="str">
         <v>html-text</v>
       </c>
+      <c r="I12" t="str">
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
@@ -749,6 +775,9 @@
       <c r="H13" t="str">
         <v>html-text</v>
       </c>
+      <c r="I13" t="str">
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
@@ -775,6 +804,9 @@
       <c r="H14" t="str">
         <v>html-text</v>
       </c>
+      <c r="I14" t="str">
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
@@ -801,6 +833,9 @@
       <c r="H15" t="str">
         <v>html-text</v>
       </c>
+      <c r="I15" t="str">
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
@@ -827,6 +862,9 @@
       <c r="H16" t="str">
         <v>html-text</v>
       </c>
+      <c r="I16" t="str">
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
@@ -853,6 +891,9 @@
       <c r="H17" t="str">
         <v>html-text</v>
       </c>
+      <c r="I17" t="str">
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
@@ -879,6 +920,9 @@
       <c r="H18" t="str">
         <v>html-text</v>
       </c>
+      <c r="I18" t="str">
+        <v/>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
@@ -905,6 +949,9 @@
       <c r="H19" t="str">
         <v>html-text</v>
       </c>
+      <c r="I19" t="str">
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
@@ -931,6 +978,9 @@
       <c r="H20" t="str">
         <v>html-text</v>
       </c>
+      <c r="I20" t="str">
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
@@ -957,6 +1007,9 @@
       <c r="H21" t="str">
         <v>html-text</v>
       </c>
+      <c r="I21" t="str">
+        <v/>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
@@ -983,6 +1036,9 @@
       <c r="H22" t="str">
         <v>html-text</v>
       </c>
+      <c r="I22" t="str">
+        <v/>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
@@ -1009,6 +1065,9 @@
       <c r="H23" t="str">
         <v>html-text</v>
       </c>
+      <c r="I23" t="str">
+        <v/>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
@@ -1035,6 +1094,9 @@
       <c r="H24" t="str">
         <v>html-text</v>
       </c>
+      <c r="I24" t="str">
+        <v/>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
@@ -1061,6 +1123,9 @@
       <c r="H25" t="str">
         <v>html-text</v>
       </c>
+      <c r="I25" t="str">
+        <v/>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
@@ -1087,6 +1152,9 @@
       <c r="H26" t="str">
         <v>html-text</v>
       </c>
+      <c r="I26" t="str">
+        <v/>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
@@ -1113,6 +1181,9 @@
       <c r="H27" t="str">
         <v>html-text</v>
       </c>
+      <c r="I27" t="str">
+        <v/>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
@@ -1139,6 +1210,9 @@
       <c r="H28" t="str">
         <v>html-text</v>
       </c>
+      <c r="I28" t="str">
+        <v/>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
@@ -1165,6 +1239,9 @@
       <c r="H29" t="str">
         <v>option</v>
       </c>
+      <c r="I29" t="str">
+        <v/>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
@@ -1191,6 +1268,9 @@
       <c r="H30" t="str">
         <v>template-text</v>
       </c>
+      <c r="I30" t="str">
+        <v/>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
@@ -1217,6 +1297,9 @@
       <c r="H31" t="str">
         <v>template-text</v>
       </c>
+      <c r="I31" t="str">
+        <v/>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
@@ -1243,6 +1326,9 @@
       <c r="H32" t="str">
         <v>option</v>
       </c>
+      <c r="I32" t="str">
+        <v/>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
@@ -1269,6 +1355,9 @@
       <c r="H33" t="str">
         <v>template-text</v>
       </c>
+      <c r="I33" t="str">
+        <v/>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
@@ -1295,6 +1384,9 @@
       <c r="H34" t="str">
         <v>template-text</v>
       </c>
+      <c r="I34" t="str">
+        <v/>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
@@ -1321,6 +1413,9 @@
       <c r="H35" t="str">
         <v>template-text</v>
       </c>
+      <c r="I35" t="str">
+        <v/>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
@@ -1347,6 +1442,9 @@
       <c r="H36" t="str">
         <v>template-text</v>
       </c>
+      <c r="I36" t="str">
+        <v/>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
@@ -1373,6 +1471,9 @@
       <c r="H37" t="str">
         <v>template-text</v>
       </c>
+      <c r="I37" t="str">
+        <v/>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
@@ -1399,6 +1500,9 @@
       <c r="H38" t="str">
         <v>template-text</v>
       </c>
+      <c r="I38" t="str">
+        <v/>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
@@ -1425,6 +1529,9 @@
       <c r="H39" t="str">
         <v>template-text</v>
       </c>
+      <c r="I39" t="str">
+        <v/>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
@@ -1451,6 +1558,9 @@
       <c r="H40" t="str">
         <v>template-text</v>
       </c>
+      <c r="I40" t="str">
+        <v/>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
@@ -1477,6 +1587,9 @@
       <c r="H41" t="str">
         <v>template-text</v>
       </c>
+      <c r="I41" t="str">
+        <v/>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
@@ -1503,6 +1616,9 @@
       <c r="H42" t="str">
         <v>template-text</v>
       </c>
+      <c r="I42" t="str">
+        <v/>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
@@ -1529,6 +1645,9 @@
       <c r="H43" t="str">
         <v>template-text</v>
       </c>
+      <c r="I43" t="str">
+        <v/>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
@@ -1555,6 +1674,9 @@
       <c r="H44" t="str">
         <v>template-text</v>
       </c>
+      <c r="I44" t="str">
+        <v/>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
@@ -1581,6 +1703,9 @@
       <c r="H45" t="str">
         <v>template-text</v>
       </c>
+      <c r="I45" t="str">
+        <v/>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
@@ -1607,6 +1732,9 @@
       <c r="H46" t="str">
         <v>template-text</v>
       </c>
+      <c r="I46" t="str">
+        <v/>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
@@ -1633,6 +1761,9 @@
       <c r="H47" t="str">
         <v>template-text</v>
       </c>
+      <c r="I47" t="str">
+        <v/>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
@@ -1659,6 +1790,9 @@
       <c r="H48" t="str">
         <v>field-error</v>
       </c>
+      <c r="I48" t="str">
+        <v/>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
@@ -1685,6 +1819,9 @@
       <c r="H49" t="str">
         <v>template-text</v>
       </c>
+      <c r="I49" t="str">
+        <v/>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
@@ -1711,6 +1848,9 @@
       <c r="H50" t="str">
         <v>template-text</v>
       </c>
+      <c r="I50" t="str">
+        <v/>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
@@ -1737,6 +1877,9 @@
       <c r="H51" t="str">
         <v>template-text</v>
       </c>
+      <c r="I51" t="str">
+        <v/>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
@@ -1763,6 +1906,9 @@
       <c r="H52" t="str">
         <v>template-text</v>
       </c>
+      <c r="I52" t="str">
+        <v/>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
@@ -1789,6 +1935,9 @@
       <c r="H53" t="str">
         <v>template-text</v>
       </c>
+      <c r="I53" t="str">
+        <v/>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
@@ -1815,6 +1964,9 @@
       <c r="H54" t="str">
         <v>template-text</v>
       </c>
+      <c r="I54" t="str">
+        <v/>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
@@ -1841,6 +1993,9 @@
       <c r="H55" t="str">
         <v>template-text</v>
       </c>
+      <c r="I55" t="str">
+        <v/>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
@@ -1867,6 +2022,9 @@
       <c r="H56" t="str">
         <v>template-text</v>
       </c>
+      <c r="I56" t="str">
+        <v/>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
@@ -1893,6 +2051,9 @@
       <c r="H57" t="str">
         <v>text</v>
       </c>
+      <c r="I57" t="str">
+        <v/>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
@@ -1919,6 +2080,9 @@
       <c r="H58" t="str">
         <v>text</v>
       </c>
+      <c r="I58" t="str">
+        <v/>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
@@ -1945,6 +2109,9 @@
       <c r="H59" t="str">
         <v>text</v>
       </c>
+      <c r="I59" t="str">
+        <v/>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
@@ -1971,6 +2138,9 @@
       <c r="H60" t="str">
         <v>template-text</v>
       </c>
+      <c r="I60" t="str">
+        <v/>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
@@ -1997,6 +2167,9 @@
       <c r="H61" t="str">
         <v>template-text</v>
       </c>
+      <c r="I61" t="str">
+        <v/>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
@@ -2023,6 +2196,9 @@
       <c r="H62" t="str">
         <v>template-text</v>
       </c>
+      <c r="I62" t="str">
+        <v/>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
@@ -2049,6 +2225,9 @@
       <c r="H63" t="str">
         <v>template-text</v>
       </c>
+      <c r="I63" t="str">
+        <v/>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
@@ -2075,6 +2254,9 @@
       <c r="H64" t="str">
         <v>template-text</v>
       </c>
+      <c r="I64" t="str">
+        <v/>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
@@ -2101,6 +2283,9 @@
       <c r="H65" t="str">
         <v>template-text</v>
       </c>
+      <c r="I65" t="str">
+        <v/>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
@@ -2127,6 +2312,9 @@
       <c r="H66" t="str">
         <v>template-text</v>
       </c>
+      <c r="I66" t="str">
+        <v/>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
@@ -2153,6 +2341,9 @@
       <c r="H67" t="str">
         <v>template-text</v>
       </c>
+      <c r="I67" t="str">
+        <v/>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
@@ -2179,6 +2370,9 @@
       <c r="H68" t="str">
         <v>template-text</v>
       </c>
+      <c r="I68" t="str">
+        <v/>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
@@ -2205,6 +2399,9 @@
       <c r="H69" t="str">
         <v>template-text</v>
       </c>
+      <c r="I69" t="str">
+        <v/>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
@@ -2231,6 +2428,9 @@
       <c r="H70" t="str">
         <v>template-text</v>
       </c>
+      <c r="I70" t="str">
+        <v/>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
@@ -2257,6 +2457,9 @@
       <c r="H71" t="str">
         <v>template-text</v>
       </c>
+      <c r="I71" t="str">
+        <v/>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
@@ -2283,6 +2486,9 @@
       <c r="H72" t="str">
         <v>text</v>
       </c>
+      <c r="I72" t="str">
+        <v/>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
@@ -2309,6 +2515,9 @@
       <c r="H73" t="str">
         <v>template-text</v>
       </c>
+      <c r="I73" t="str">
+        <v/>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
@@ -2335,6 +2544,9 @@
       <c r="H74" t="str">
         <v>option</v>
       </c>
+      <c r="I74" t="str">
+        <v/>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
@@ -2361,6 +2573,9 @@
       <c r="H75" t="str">
         <v>api-error</v>
       </c>
+      <c r="I75" t="str">
+        <v>applied: Each change must allow, deny or clear a permission.</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
@@ -2387,6 +2602,9 @@
       <c r="H76" t="str">
         <v>api-error</v>
       </c>
+      <c r="I76" t="str">
+        <v>applied: Pick a base role: supervisor, floor or portal.</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
@@ -2413,6 +2631,9 @@
       <c r="H77" t="str">
         <v>api-error</v>
       </c>
+      <c r="I77" t="str">
+        <v>applied: The role to copy from, "${copyFrom}", does not exist.</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
@@ -2439,6 +2660,9 @@
       <c r="H78" t="str">
         <v>api-error</v>
       </c>
+      <c r="I78" t="str">
+        <v>applied: The role to copy from must be ${P.isPortalBase(base) ? 'a portal' : 'an ops'} role, like t</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
@@ -2465,6 +2689,9 @@
       <c r="H79" t="str">
         <v>api-error</v>
       </c>
+      <c r="I79" t="str">
+        <v>skipped — server log line, not user-facing</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
@@ -2491,6 +2718,9 @@
       <c r="H80" t="str">
         <v>api-error</v>
       </c>
+      <c r="I80" t="str">
+        <v>applied: Select at least one shipment.</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
@@ -2517,6 +2747,9 @@
       <c r="H81" t="str">
         <v>api-error</v>
       </c>
+      <c r="I81" t="str">
+        <v>applied: The match field must be one of: ${MATCH_FIELDS.join(', ')}.</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
@@ -2543,6 +2776,9 @@
       <c r="H82" t="str">
         <v>api-error</v>
       </c>
+      <c r="I82" t="str">
+        <v>applied: That record could not be found.</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
@@ -2569,6 +2805,9 @@
       <c r="H83" t="str">
         <v>api-error</v>
       </c>
+      <c r="I83" t="str">
+        <v>applied: That record could not be found.</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
@@ -2595,6 +2834,9 @@
       <c r="H84" t="str">
         <v>api-error</v>
       </c>
+      <c r="I84" t="str">
+        <v>applied: That record could not be found.</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
@@ -2621,6 +2863,9 @@
       <c r="H85" t="str">
         <v>api-error</v>
       </c>
+      <c r="I85" t="str">
+        <v>applied: Item import is not available yet — the database update (098) has not been applied.</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
@@ -2647,6 +2892,9 @@
       <c r="H86" t="str">
         <v>api-error</v>
       </c>
+      <c r="I86" t="str">
+        <v>applied: Pick a client.</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
@@ -2673,6 +2921,9 @@
       <c r="H87" t="str">
         <v>api-error</v>
       </c>
+      <c r="I87" t="str">
+        <v>applied: This client requires lot tracking. Turn off lot tracking for the client first.</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
@@ -2699,6 +2950,9 @@
       <c r="H88" t="str">
         <v>api-error</v>
       </c>
+      <c r="I88" t="str">
+        <v>applied: Your session has expired. Sign in again.</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
@@ -2725,6 +2979,9 @@
       <c r="H89" t="str">
         <v>api-error</v>
       </c>
+      <c r="I89" t="str">
+        <v>applied: Something went wrong on our side. Try again, and contact support if it keeps happening.</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
@@ -2751,6 +3008,9 @@
       <c r="H90" t="str">
         <v>api-error</v>
       </c>
+      <c r="I90" t="str">
+        <v>applied: That record could not be found.</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
@@ -2777,6 +3037,9 @@
       <c r="H91" t="str">
         <v>api-error</v>
       </c>
+      <c r="I91" t="str">
+        <v>applied: Nothing was picked. Raise a "Not found" exception instead.</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
@@ -2803,6 +3066,9 @@
       <c r="H92" t="str">
         <v>api-error</v>
       </c>
+      <c r="I92" t="str">
+        <v>applied: That record could not be found.</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
@@ -2829,6 +3095,9 @@
       <c r="H93" t="str">
         <v>api-error</v>
       </c>
+      <c r="I93" t="str">
+        <v>applied: Portal features are not available yet — the database update (095) has not been applied.</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
@@ -2855,6 +3124,9 @@
       <c r="H94" t="str">
         <v>api-error</v>
       </c>
+      <c r="I94" t="str">
+        <v>applied: Portal preview is not available yet — the database update (096) has not been applied.</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
@@ -2881,6 +3153,9 @@
       <c r="H95" t="str">
         <v>api-error</v>
       </c>
+      <c r="I95" t="str">
+        <v>applied: This is for portal accounts. Manage warehouse users under Users.</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
@@ -2907,6 +3182,9 @@
       <c r="H96" t="str">
         <v>api-error</v>
       </c>
+      <c r="I96" t="str">
+        <v>applied: Enter a valid issue date.</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
@@ -2933,6 +3211,9 @@
       <c r="H97" t="str">
         <v>api-error</v>
       </c>
+      <c r="I97" t="str">
+        <v>applied: Enter a valid expiry date.</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
@@ -2959,6 +3240,9 @@
       <c r="H98" t="str">
         <v>api-error</v>
       </c>
+      <c r="I98" t="str">
+        <v>applied: The expiry date must be on or after the issue date.</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
@@ -2985,6 +3269,9 @@
       <c r="H99" t="str">
         <v>api-error</v>
       </c>
+      <c r="I99" t="str">
+        <v>applied: Pick a client.</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
@@ -3011,6 +3298,9 @@
       <c r="H100" t="str">
         <v>api-error</v>
       </c>
+      <c r="I100" t="str">
+        <v xml:space="preserve">applied: Unit scans were sent for ${uc.client_code} / ${uc.sku_code}, but that item does not track </v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
@@ -3037,6 +3327,9 @@
       <c r="H101" t="str">
         <v>api-error</v>
       </c>
+      <c r="I101" t="str">
+        <v>applied: ${uc.sku_code} requires unit scans: scan ${line.quantity} unit(s).</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
@@ -3063,6 +3356,9 @@
       <c r="H102" t="str">
         <v>api-error</v>
       </c>
+      <c r="I102" t="str">
+        <v>applied: Pick a client before approving. None is set on this intake.</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
@@ -3089,6 +3385,9 @@
       <c r="H103" t="str">
         <v>api-error</v>
       </c>
+      <c r="I103" t="str">
+        <v>applied: Documents of type ${docType} cannot be auto-approved.</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
@@ -3115,6 +3414,9 @@
       <c r="H104" t="str">
         <v>api-error</v>
       </c>
+      <c r="I104" t="str">
+        <v>applied: Pick a client.</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
@@ -3141,6 +3443,9 @@
       <c r="H105" t="str">
         <v>api-error</v>
       </c>
+      <c r="I105" t="str">
+        <v>applied: Enter a from date and a to date (YYYY-MM-DD).</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
@@ -3167,6 +3472,9 @@
       <c r="H106" t="str">
         <v>api-error</v>
       </c>
+      <c r="I106" t="str">
+        <v>applied: The from date must be on or before the to date.</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
@@ -3193,6 +3501,9 @@
       <c r="H107" t="str">
         <v>api-error</v>
       </c>
+      <c r="I107" t="str">
+        <v>applied: The metric ${r.metric_key} does not exist.</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
@@ -3219,6 +3530,9 @@
       <c r="H108" t="str">
         <v>api-error</v>
       </c>
+      <c r="I108" t="str">
+        <v>applied: The AI extraction returned unreadable data: ${err.message}</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
@@ -3245,6 +3559,9 @@
       <c r="H109" t="str">
         <v>api-error</v>
       </c>
+      <c r="I109" t="str">
+        <v>applied: Add at least one tier rule.</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
@@ -3271,6 +3588,9 @@
       <c r="H110" t="str">
         <v>api-error</v>
       </c>
+      <c r="I110" t="str">
+        <v>applied: Tier ${i}: the from quantity must be 0 or more.</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
@@ -3297,6 +3617,9 @@
       <c r="H111" t="str">
         <v>api-error</v>
       </c>
+      <c r="I111" t="str">
+        <v>applied: Tier ${i}: the to quantity must be blank (open-ended) or greater than the from quantity.</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
@@ -3323,6 +3646,9 @@
       <c r="H112" t="str">
         <v>api-error</v>
       </c>
+      <c r="I112" t="str">
+        <v>applied: Add at least one aged escalation step.</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
@@ -3349,6 +3675,9 @@
       <c r="H113" t="str">
         <v>api-error</v>
       </c>
+      <c r="I113" t="str">
+        <v>applied: Escalation ${i}: after days must be a whole number greater than 0.</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
@@ -3375,6 +3704,9 @@
       <c r="H114" t="str">
         <v>api-error</v>
       </c>
+      <c r="I114" t="str">
+        <v>applied: Escalation ${i}: after days must increase from step to step.</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
@@ -3401,6 +3733,9 @@
       <c r="H115" t="str">
         <v>api-error</v>
       </c>
+      <c r="I115" t="str">
+        <v>applied: Free days apply only to license-plate occupancy lines.</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
@@ -3427,6 +3762,9 @@
       <c r="H116" t="str">
         <v>api-error</v>
       </c>
+      <c r="I116" t="str">
+        <v>applied: Slot type applies only to license-plate occupancy lines.</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
@@ -3453,6 +3791,9 @@
       <c r="H117" t="str">
         <v>api-error</v>
       </c>
+      <c r="I117" t="str">
+        <v xml:space="preserve">applied: Tier rules and aged escalation cannot combine on one line (deferred until a real contract </v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
@@ -3479,6 +3820,9 @@
       <c r="H118" t="str">
         <v>api-error</v>
       </c>
+      <c r="I118" t="str">
+        <v xml:space="preserve">applied: Tier rules cannot combine with MONTHLY_ANNIVERSARY — "first N" is undefined when every LP </v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
@@ -3505,6 +3849,9 @@
       <c r="H119" t="str">
         <v>api-error</v>
       </c>
+      <c r="I119" t="str">
+        <v>applied: Two license-plate occupancy lines claim the slot type ${key === '*' ? '(catch-all)' : key}</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
@@ -3531,6 +3878,9 @@
       <c r="H120" t="str">
         <v>api-error</v>
       </c>
+      <c r="I120" t="str">
+        <v>applied: Pick a client.</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
@@ -3557,6 +3907,9 @@
       <c r="H121" t="str">
         <v>api-error</v>
       </c>
+      <c r="I121" t="str">
+        <v>applied: This client has no active legacy billing rates to map.</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
@@ -3583,6 +3936,9 @@
       <c r="H122" t="str">
         <v>api-error</v>
       </c>
+      <c r="I122" t="str">
+        <v>applied: No charge code maps the legacy rate type(s) ${[...new Set(unmapped.map((r) =&gt; r.rate_type)</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
@@ -3609,6 +3965,9 @@
       <c r="H123" t="str">
         <v>api-error</v>
       </c>
+      <c r="I123" t="str">
+        <v>applied: The SDS extraction returned unreadable data.</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
@@ -3635,6 +3994,9 @@
       <c r="H124" t="str">
         <v>api-error</v>
       </c>
+      <c r="I124" t="str">
+        <v>applied: The AI extraction returned unreadable data: ${err.message}</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
@@ -3661,6 +4023,9 @@
       <c r="H125" t="str">
         <v>api-error</v>
       </c>
+      <c r="I125" t="str">
+        <v>applied: Enter a rule key.</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
@@ -3687,6 +4052,9 @@
       <c r="H126" t="str">
         <v>api-error</v>
       </c>
+      <c r="I126" t="str">
+        <v>applied: Enter a rule label.</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
@@ -3713,6 +4081,9 @@
       <c r="H127" t="str">
         <v>api-error</v>
       </c>
+      <c r="I127" t="str">
+        <v>applied: That preset could not be found.</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
@@ -3739,6 +4110,9 @@
       <c r="H128" t="str">
         <v>api-error</v>
       </c>
+      <c r="I128" t="str">
+        <v>applied: That client could not be found.</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
@@ -3765,6 +4139,9 @@
       <c r="H129" t="str">
         <v>api-error</v>
       </c>
+      <c r="I129" t="str">
+        <v>applied: That schedule could not be found.</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
@@ -3791,6 +4168,9 @@
       <c r="H130" t="str">
         <v>api-error</v>
       </c>
+      <c r="I130" t="str">
+        <v>applied: This is for portal accounts. Sign in as a client user.</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
@@ -3817,6 +4197,9 @@
       <c r="H131" t="str">
         <v>api-error</v>
       </c>
+      <c r="I131" t="str">
+        <v>applied: Pick an item.</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
@@ -3843,6 +4226,9 @@
       <c r="H132" t="str">
         <v>api-error</v>
       </c>
+      <c r="I132" t="str">
+        <v>applied: Pick a reason category.</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
@@ -3869,6 +4255,9 @@
       <c r="H133" t="str">
         <v>api-error</v>
       </c>
+      <c r="I133" t="str">
+        <v>applied: Enter your current PIN to set a new one.</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
@@ -3895,6 +4284,9 @@
       <c r="H134" t="str">
         <v>api-error</v>
       </c>
+      <c r="I134" t="str">
+        <v>applied: Pick an item.</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
@@ -3921,6 +4313,9 @@
       <c r="H135" t="str">
         <v>api-error</v>
       </c>
+      <c r="I135" t="str">
+        <v>applied: Pick a client.</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
@@ -3947,6 +4342,9 @@
       <c r="H136" t="str">
         <v>api-error</v>
       </c>
+      <c r="I136" t="str">
+        <v>applied: Every handling unit needs an item code.</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
@@ -3973,6 +4371,9 @@
       <c r="H137" t="str">
         <v>api-error</v>
       </c>
+      <c r="I137" t="str">
+        <v>applied: Every handling unit needs a pack level.</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
@@ -3999,6 +4400,9 @@
       <c r="H138" t="str">
         <v>api-error</v>
       </c>
+      <c r="I138" t="str">
+        <v>applied: Pick a pack level.</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
@@ -4025,6 +4429,9 @@
       <c r="H139" t="str">
         <v>api-error</v>
       </c>
+      <c r="I139" t="str">
+        <v>applied: Enter an item code.</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
@@ -4051,6 +4458,9 @@
       <c r="H140" t="str">
         <v>api-error</v>
       </c>
+      <c r="I140" t="str">
+        <v>applied: Client type must be one of: ${CLIENT_TYPES.join(', ')} (got "${type}").</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
@@ -4077,6 +4487,9 @@
       <c r="H141" t="str">
         <v>api-error</v>
       </c>
+      <c r="I141" t="str">
+        <v>applied: Invoice detail must be one of: ${INVOICE_MODES.join(', ')} (got "${invoiceMode}").</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
@@ -4103,6 +4516,9 @@
       <c r="H142" t="str">
         <v>api-error</v>
       </c>
+      <c r="I142" t="str">
+        <v>applied: Invoice detail must be Detailed or Summary.</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
@@ -4129,6 +4545,9 @@
       <c r="H143" t="str">
         <v>api-error</v>
       </c>
+      <c r="I143" t="str">
+        <v>applied: Label mode must be label first or label at pack.</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
@@ -4155,6 +4574,9 @@
       <c r="H144" t="str">
         <v>api-error</v>
       </c>
+      <c r="I144" t="str">
+        <v>applied: Unit control must be none, optional or required.</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
@@ -4181,6 +4603,9 @@
       <c r="H145" t="str">
         <v>api-error</v>
       </c>
+      <c r="I145" t="str">
+        <v>applied: Ship rules are not in the expected shape.</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
@@ -4207,6 +4632,9 @@
       <c r="H146" t="str">
         <v>api-error</v>
       </c>
+      <c r="I146" t="str">
+        <v>applied: The default box in ship rules is not a valid box.</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
@@ -4233,6 +4661,9 @@
       <c r="H147" t="str">
         <v>api-error</v>
       </c>
+      <c r="I147" t="str">
+        <v>applied: Pick rules are not in the expected shape.</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
@@ -4259,6 +4690,9 @@
       <c r="H148" t="str">
         <v>api-error</v>
       </c>
+      <c r="I148" t="str">
+        <v>applied: The location mode in pick rules must be tap or scan.</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
@@ -4285,6 +4719,9 @@
       <c r="H149" t="str">
         <v>api-error</v>
       </c>
+      <c r="I149" t="str">
+        <v>applied: Client type must be B2B, B2C or BOTH (got "${v}").</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
@@ -4311,6 +4748,9 @@
       <c r="H150" t="str">
         <v>api-error</v>
       </c>
+      <c r="I150" t="str">
+        <v>applied: That client could not be found.</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
@@ -4337,6 +4777,9 @@
       <c r="H151" t="str">
         <v>api-error</v>
       </c>
+      <c r="I151" t="str">
+        <v>applied: That client could not be found.</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
@@ -4363,6 +4806,9 @@
       <c r="H152" t="str">
         <v>api-error</v>
       </c>
+      <c r="I152" t="str">
+        <v>applied: That warehouse could not be found.</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
@@ -4389,6 +4835,9 @@
       <c r="H153" t="str">
         <v>api-error</v>
       </c>
+      <c r="I153" t="str">
+        <v>applied: That record could not be found.</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
@@ -4415,6 +4864,9 @@
       <c r="H154" t="str">
         <v>api-error</v>
       </c>
+      <c r="I154" t="str">
+        <v>applied: That template could not be found.</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
@@ -4441,6 +4893,9 @@
       <c r="H155" t="str">
         <v>api-error</v>
       </c>
+      <c r="I155" t="str">
+        <v>applied: That template could not be found.</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
@@ -4467,6 +4922,9 @@
       <c r="H156" t="str">
         <v>api-error</v>
       </c>
+      <c r="I156" t="str">
+        <v>applied: That scan profile could not be found.</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
@@ -4493,6 +4951,9 @@
       <c r="H157" t="str">
         <v>api-error</v>
       </c>
+      <c r="I157" t="str">
+        <v>applied: Pick a shipping rate.</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
@@ -4519,6 +4980,9 @@
       <c r="H158" t="str">
         <v>api-error</v>
       </c>
+      <c r="I158" t="str">
+        <v>applied: Pick a shipping rate.</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
@@ -4545,6 +5009,9 @@
       <c r="H159" t="str">
         <v>api-error</v>
       </c>
+      <c r="I159" t="str">
+        <v>applied: That record could not be found.</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
@@ -4571,6 +5038,9 @@
       <c r="H160" t="str">
         <v>api-error</v>
       </c>
+      <c r="I160" t="str">
+        <v>applied: That record could not be found.</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
@@ -4597,6 +5067,9 @@
       <c r="H161" t="str">
         <v>api-error</v>
       </c>
+      <c r="I161" t="str">
+        <v>applied: That record could not be found.</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
@@ -4623,6 +5096,9 @@
       <c r="H162" t="str">
         <v>api-error</v>
       </c>
+      <c r="I162" t="str">
+        <v>applied: That record could not be found.</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
@@ -4649,6 +5125,9 @@
       <c r="H163" t="str">
         <v>api-error</v>
       </c>
+      <c r="I163" t="str">
+        <v>applied: User administration is not available yet — the database update (094) has not been applied.</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
@@ -4675,6 +5154,9 @@
       <c r="H164" t="str">
         <v>api-error</v>
       </c>
+      <c r="I164" t="str">
+        <v>applied: Sign out everywhere is not available yet — the database update (097) has not been applied.</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
@@ -4701,6 +5183,9 @@
       <c r="H165" t="str">
         <v>api-error</v>
       </c>
+      <c r="I165" t="str">
+        <v>applied: Each change must allow, deny or clear a permission.</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
@@ -4727,6 +5212,9 @@
       <c r="H166" t="str">
         <v>api-error</v>
       </c>
+      <c r="I166" t="str">
+        <v>skipped — server log line, not user-facing</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
@@ -4753,6 +5241,9 @@
       <c r="H167" t="str">
         <v>html-text</v>
       </c>
+      <c r="I167" t="str">
+        <v>applied: Aged escalation</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
@@ -4779,6 +5270,9 @@
       <c r="H168" t="str">
         <v>html-text</v>
       </c>
+      <c r="I168" t="str">
+        <v>applied: Tiers</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
@@ -4805,6 +5299,9 @@
       <c r="H169" t="str">
         <v>html-text</v>
       </c>
+      <c r="I169" t="str">
+        <v>applied: every receive, case break, pick and ship event for the license plate family</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
@@ -4831,6 +5328,9 @@
       <c r="H170" t="str">
         <v>html-text</v>
       </c>
+      <c r="I170" t="str">
+        <v>applied: Review — high</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
@@ -4857,6 +5357,9 @@
       <c r="H171" t="str">
         <v>html-text</v>
       </c>
+      <c r="I171" t="str">
+        <v>applied: Review — low</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
@@ -4883,6 +5386,9 @@
       <c r="H172" t="str">
         <v>template-text</v>
       </c>
+      <c r="I172" t="str">
+        <v>skipped — code fragment mis-extracted; the visible words in it are fine</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
@@ -4909,6 +5415,9 @@
       <c r="H173" t="str">
         <v>template-text</v>
       </c>
+      <c r="I173" t="str">
+        <v>skipped — code fragment mis-extracted; the visible words in it are fine</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
@@ -4935,6 +5444,9 @@
       <c r="H174" t="str">
         <v>template-text</v>
       </c>
+      <c r="I174" t="str">
+        <v>skipped — code fragment mis-extracted; the visible words in it are fine</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
@@ -4961,6 +5473,9 @@
       <c r="H175" t="str">
         <v>template-text</v>
       </c>
+      <c r="I175" t="str">
+        <v>applied: Charges are billed when an order falls outside the SLA. They become billing charges automa</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
@@ -4987,6 +5502,9 @@
       <c r="H176" t="str">
         <v>option</v>
       </c>
+      <c r="I176" t="str">
+        <v>skipped — code fragment mis-extracted; the visible words in it are fine</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
@@ -5013,6 +5531,9 @@
       <c r="H177" t="str">
         <v>text</v>
       </c>
+      <c r="I177" t="str">
+        <v>applied: The PDF viewer failed to load.</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
@@ -5039,6 +5560,9 @@
       <c r="H178" t="str">
         <v>option</v>
       </c>
+      <c r="I178" t="str">
+        <v>skipped — code comment</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
@@ -5065,6 +5589,9 @@
       <c r="H179" t="str">
         <v>template-text</v>
       </c>
+      <c r="I179" t="str">
+        <v>skipped — code fragment mis-extracted; the visible words in it are fine</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
@@ -5091,6 +5618,9 @@
       <c r="H180" t="str">
         <v>template-text</v>
       </c>
+      <c r="I180" t="str">
+        <v>skipped — code fragment mis-extracted; the visible words in it are fine</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
@@ -5117,6 +5647,9 @@
       <c r="H181" t="str">
         <v>template-text</v>
       </c>
+      <c r="I181" t="str">
+        <v>skipped — code fragment mis-extracted; the visible words in it are fine</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
@@ -5143,6 +5676,9 @@
       <c r="H182" t="str">
         <v>template-text</v>
       </c>
+      <c r="I182" t="str">
+        <v>skipped — code fragment mis-extracted; the visible words in it are fine</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
@@ -5169,6 +5705,9 @@
       <c r="H183" t="str">
         <v>template-text</v>
       </c>
+      <c r="I183" t="str">
+        <v>skipped — code fragment mis-extracted; the visible words in it are fine</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
@@ -5195,6 +5734,9 @@
       <c r="H184" t="str">
         <v>template-text</v>
       </c>
+      <c r="I184" t="str">
+        <v>skipped — code fragment mis-extracted; the visible words in it are fine</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
@@ -5221,6 +5763,9 @@
       <c r="H185" t="str">
         <v>template-text</v>
       </c>
+      <c r="I185" t="str">
+        <v>skipped — code fragment mis-extracted; the visible words in it are fine</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
@@ -5247,6 +5792,9 @@
       <c r="H186" t="str">
         <v>template-text</v>
       </c>
+      <c r="I186" t="str">
+        <v>skipped — code fragment mis-extracted; the visible words in it are fine</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
@@ -5273,6 +5821,9 @@
       <c r="H187" t="str">
         <v>template-text</v>
       </c>
+      <c r="I187" t="str">
+        <v>skipped — code fragment mis-extracted; the visible words in it are fine</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
@@ -5299,6 +5850,9 @@
       <c r="H188" t="str">
         <v>template-text</v>
       </c>
+      <c r="I188" t="str">
+        <v>skipped — code fragment mis-extracted; the visible words in it are fine</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
@@ -5325,6 +5879,9 @@
       <c r="H189" t="str">
         <v>template-text</v>
       </c>
+      <c r="I189" t="str">
+        <v>skipped — code fragment mis-extracted; the visible words in it are fine</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
@@ -5351,6 +5908,9 @@
       <c r="H190" t="str">
         <v>template-text</v>
       </c>
+      <c r="I190" t="str">
+        <v>skipped — code fragment mis-extracted; the visible words in it are fine</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
@@ -5377,6 +5937,9 @@
       <c r="H191" t="str">
         <v>template-text</v>
       </c>
+      <c r="I191" t="str">
+        <v>skipped — code fragment mis-extracted; the visible words in it are fine</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
@@ -5403,6 +5966,9 @@
       <c r="H192" t="str">
         <v>template-text</v>
       </c>
+      <c r="I192" t="str">
+        <v>skipped — code fragment mis-extracted; the visible words in it are fine</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
@@ -5429,6 +5995,9 @@
       <c r="H193" t="str">
         <v>option</v>
       </c>
+      <c r="I193" t="str">
+        <v>skipped — code fragment mis-extracted; the visible words in it are fine</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
@@ -5455,6 +6024,9 @@
       <c r="H194" t="str">
         <v>option</v>
       </c>
+      <c r="I194" t="str">
+        <v>skipped — code fragment mis-extracted; the visible words in it are fine</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
@@ -5481,6 +6053,9 @@
       <c r="H195" t="str">
         <v>template-text</v>
       </c>
+      <c r="I195" t="str">
+        <v>skipped — code fragment mis-extracted; the visible words in it are fine</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
@@ -5507,6 +6082,9 @@
       <c r="H196" t="str">
         <v>template-text</v>
       </c>
+      <c r="I196" t="str">
+        <v>applied: Portal features are not available yet — the database update (095) has not been applied.</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
@@ -5533,6 +6111,9 @@
       <c r="H197" t="str">
         <v>option</v>
       </c>
+      <c r="I197" t="str">
+        <v>skipped — code fragment mis-extracted; the visible words in it are fine</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
@@ -5559,6 +6140,9 @@
       <c r="H198" t="str">
         <v>template-text</v>
       </c>
+      <c r="I198" t="str">
+        <v>skipped — code fragment mis-extracted; the visible words in it are fine</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
@@ -5585,6 +6169,9 @@
       <c r="H199" t="str">
         <v>template-text</v>
       </c>
+      <c r="I199" t="str">
+        <v>skipped — code fragment mis-extracted; the visible words in it are fine</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
@@ -5611,6 +6198,9 @@
       <c r="H200" t="str">
         <v>template-text</v>
       </c>
+      <c r="I200" t="str">
+        <v>skipped — code fragment mis-extracted; the visible words in it are fine</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
@@ -5637,6 +6227,9 @@
       <c r="H201" t="str">
         <v>option</v>
       </c>
+      <c r="I201" t="str">
+        <v>skipped — code fragment mis-extracted; the visible words in it are fine</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
@@ -5663,6 +6256,9 @@
       <c r="H202" t="str">
         <v>template-text</v>
       </c>
+      <c r="I202" t="str">
+        <v>applied: Roles are not available yet — the database updates (093/094) have not been applied.</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
@@ -5689,6 +6285,9 @@
       <c r="H203" t="str">
         <v>template-text</v>
       </c>
+      <c r="I203" t="str">
+        <v>skipped — code fragment mis-extracted; the visible words in it are fine</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
@@ -5715,6 +6314,9 @@
       <c r="H204" t="str">
         <v>toast</v>
       </c>
+      <c r="I204" t="str">
+        <v>skipped — code fragment mis-extracted; the visible words in it are fine</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
@@ -5741,6 +6343,9 @@
       <c r="H205" t="str">
         <v>template-text</v>
       </c>
+      <c r="I205" t="str">
+        <v>skipped — code fragment mis-extracted; the visible words in it are fine</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
@@ -5767,6 +6372,9 @@
       <c r="H206" t="str">
         <v>template-text</v>
       </c>
+      <c r="I206" t="str">
+        <v>skipped — code fragment mis-extracted; the visible words in it are fine</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
@@ -5793,6 +6401,9 @@
       <c r="H207" t="str">
         <v>template-text</v>
       </c>
+      <c r="I207" t="str">
+        <v>skipped — code fragment mis-extracted; the visible words in it are fine</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
@@ -5819,6 +6430,9 @@
       <c r="H208" t="str">
         <v>option</v>
       </c>
+      <c r="I208" t="str">
+        <v>applied: Match pattern (regular expression)</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
@@ -5845,6 +6459,9 @@
       <c r="H209" t="str">
         <v>option</v>
       </c>
+      <c r="I209" t="str">
+        <v>applied: Leave blank to treat the whole scanned text as one field.</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
@@ -5871,6 +6488,9 @@
       <c r="H210" t="str">
         <v>template-text</v>
       </c>
+      <c r="I210" t="str">
+        <v>skipped — code fragment mis-extracted; the visible words in it are fine</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
@@ -5897,6 +6517,9 @@
       <c r="H211" t="str">
         <v>api-error</v>
       </c>
+      <c r="I211" t="str">
+        <v>applied: Add at least one change.</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
@@ -5923,6 +6546,9 @@
       <c r="H212" t="str">
         <v>api-error</v>
       </c>
+      <c r="I212" t="str">
+        <v>applied: The permission "${c.key}" does not exist.</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="str">
@@ -5949,6 +6575,9 @@
       <c r="H213" t="str">
         <v>api-error</v>
       </c>
+      <c r="I213" t="str">
+        <v>applied: The "${P.labelOf(c.key)}" permission is admin-only and cannot be granted to ${c.role}.</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="str">
@@ -5975,6 +6604,9 @@
       <c r="H214" t="str">
         <v>api-error</v>
       </c>
+      <c r="I214" t="str">
+        <v>applied: The role "${c.role}" does not exist. Pick one from the list.</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="str">
@@ -6001,6 +6633,9 @@
       <c r="H215" t="str">
         <v>api-error</v>
       </c>
+      <c r="I215" t="str">
+        <v>applied: ${role.name} cannot be changed. Admin always has every permission.</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="str">
@@ -6027,6 +6662,9 @@
       <c r="H216" t="str">
         <v>api-error</v>
       </c>
+      <c r="I216" t="str">
+        <v>applied: The "${P.labelOf(c.key)}" permission is ${P.isPortalKey(c.key) ? 'a portal' : 'an ops'} pe</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="str">
@@ -6053,6 +6691,9 @@
       <c r="H217" t="str">
         <v>api-error</v>
       </c>
+      <c r="I217" t="str">
+        <v>applied: The name must be 2 to 60 characters.</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="str">
@@ -6079,6 +6720,9 @@
       <c r="H218" t="str">
         <v>api-error</v>
       </c>
+      <c r="I218" t="str">
+        <v>applied: The key must be 2 to 40 characters: lower-case letters, digits and underscores, starting w</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="str">
@@ -6105,6 +6749,9 @@
       <c r="H219" t="str">
         <v>api-error</v>
       </c>
+      <c r="I219" t="str">
+        <v>applied: The "${key}" role is built in and cannot be changed.</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="str">
@@ -6131,6 +6778,9 @@
       <c r="H220" t="str">
         <v>api-error</v>
       </c>
+      <c r="I220" t="str">
+        <v>applied: A role with the key "${key}" already exists.</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="str">
@@ -6157,6 +6807,9 @@
       <c r="H221" t="str">
         <v>api-error</v>
       </c>
+      <c r="I221" t="str">
+        <v>applied: A custom role cannot be copied from Admin.</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="str">
@@ -6183,6 +6836,9 @@
       <c r="H222" t="str">
         <v>api-error</v>
       </c>
+      <c r="I222" t="str">
+        <v>applied: ${users} user${users === 1 ? '' : 's'} still ${users === 1 ? 'has' : 'have'} the "${r.name</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="str">
@@ -6209,6 +6865,9 @@
       <c r="H223" t="str">
         <v>api-error</v>
       </c>
+      <c r="I223" t="str">
+        <v>applied: ${missing.length} of the selected shipments are not shipped orders of ${client.code}: ${mi</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
@@ -6235,6 +6894,9 @@
       <c r="H224" t="str">
         <v>api-error</v>
       </c>
+      <c r="I224" t="str">
+        <v>applied: The rule ${k} must be one of: ${(RULE_VALUES[k] || []).join('|')}.</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="str">
@@ -6261,6 +6923,9 @@
       <c r="H225" t="str">
         <v>api-error</v>
       </c>
+      <c r="I225" t="str">
+        <v>applied: Select at least one client.</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
@@ -6287,6 +6952,9 @@
       <c r="H226" t="str">
         <v>api-error</v>
       </c>
+      <c r="I226" t="str">
+        <v>kept — already follows the guide</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
@@ -6313,6 +6981,9 @@
       <c r="H227" t="str">
         <v>api-error</v>
       </c>
+      <c r="I227" t="str">
+        <v>applied: The replay interval must be between 5 and 1440 minutes.</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
@@ -6339,6 +7010,9 @@
       <c r="H228" t="str">
         <v>api-error</v>
       </c>
+      <c r="I228" t="str">
+        <v>applied: Enter the cursor as a date.</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
@@ -6365,6 +7039,9 @@
       <c r="H229" t="str">
         <v>api-error</v>
       </c>
+      <c r="I229" t="str">
+        <v>applied: ${c.code} is already live.</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
@@ -6391,6 +7068,9 @@
       <c r="H230" t="str">
         <v>api-error</v>
       </c>
+      <c r="I230" t="str">
+        <v>applied: Enter a valid client code.</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
@@ -6417,6 +7097,9 @@
       <c r="H231" t="str">
         <v>api-error</v>
       </c>
+      <c r="I231" t="str">
+        <v>applied: The client code ${c} is not valid.</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
@@ -6443,6 +7126,9 @@
       <c r="H232" t="str">
         <v>api-error</v>
       </c>
+      <c r="I232" t="str">
+        <v>applied: Enter a valid date.</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
@@ -6469,6 +7155,9 @@
       <c r="H233" t="str">
         <v>api-error</v>
       </c>
+      <c r="I233" t="str">
+        <v>applied: Map at least one column to a field.</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
@@ -6495,6 +7184,9 @@
       <c r="H234" t="str">
         <v>api-error</v>
       </c>
+      <c r="I234" t="str">
+        <v>applied: The field "${k}" does not exist (column "${h}").</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
@@ -6521,6 +7213,9 @@
       <c r="H235" t="str">
         <v>api-error</v>
       </c>
+      <c r="I235" t="str">
+        <v>applied: "${BY_KEY[k].label}" is mapped from two columns ("${used.get(k)}" and "${h}").</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
@@ -6547,6 +7242,9 @@
       <c r="H236" t="str">
         <v>api-error</v>
       </c>
+      <c r="I236" t="str">
+        <v>applied: "${BY_KEY[r].label}" must be mapped before validating.</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
@@ -6573,6 +7271,9 @@
       <c r="H237" t="str">
         <v>api-error</v>
       </c>
+      <c r="I237" t="str">
+        <v>applied: "${v}" is not a yes/no value (use yes/no, y/n, true/false, 1/0 or x).</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
@@ -6599,6 +7300,9 @@
       <c r="H238" t="str">
         <v>api-error</v>
       </c>
+      <c r="I238" t="str">
+        <v>applied: "${v}" is not a number.</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="str">
@@ -6625,6 +7329,9 @@
       <c r="H239" t="str">
         <v>api-error</v>
       </c>
+      <c r="I239" t="str">
+        <v>applied: "${v}" must be a whole number.</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
@@ -6651,6 +7358,9 @@
       <c r="H240" t="str">
         <v>api-error</v>
       </c>
+      <c r="I240" t="str">
+        <v>applied: "${v}" must be ${field.min} or more.</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="str">
@@ -6677,6 +7387,9 @@
       <c r="H241" t="str">
         <v>api-error</v>
       </c>
+      <c r="I241" t="str">
+        <v>applied: "${v}" is not an allowed value. Allowed: ${field.values.join(' / ')}.</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="str">
@@ -6703,6 +7416,9 @@
       <c r="H242" t="str">
         <v>api-error</v>
       </c>
+      <c r="I242" t="str">
+        <v>applied: "${v}" is not a 2-letter country code.</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="str">
@@ -6729,6 +7445,9 @@
       <c r="H243" t="str">
         <v>api-error</v>
       </c>
+      <c r="I243" t="str">
+        <v>applied: "${v}" is not numeric.</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="str">
@@ -6755,6 +7474,9 @@
       <c r="H244" t="str">
         <v>api-error</v>
       </c>
+      <c r="I244" t="str">
+        <v>kept — already follows the guide</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="str">
@@ -6781,6 +7503,9 @@
       <c r="H245" t="str">
         <v>api-error</v>
       </c>
+      <c r="I245" t="str">
+        <v>applied: ${d} has a bad check digit (should end in ${idn.gtinCheckDigit(d.slice(0, -1))}).</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
@@ -6807,6 +7532,9 @@
       <c r="H246" t="str">
         <v>api-error</v>
       </c>
+      <c r="I246" t="str">
+        <v>applied: "${v.slice(0, 20)}…" is longer than ${field.max} characters.</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="str">
@@ -6833,6 +7561,9 @@
       <c r="H247" t="str">
         <v>api-error</v>
       </c>
+      <c r="I247" t="str">
+        <v>applied: Choose a file to upload.</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="str">
@@ -6859,6 +7590,9 @@
       <c r="H248" t="str">
         <v>api-error</v>
       </c>
+      <c r="I248" t="str">
+        <v>applied: "${h}" is not a column of this file.</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="str">
@@ -6885,6 +7619,9 @@
       <c r="H249" t="str">
         <v>api-error</v>
       </c>
+      <c r="I249" t="str">
+        <v>applied: The type must be one of: ${IDENT_TYPES.join(', ')}.</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="str">
@@ -6911,6 +7648,9 @@
       <c r="H250" t="str">
         <v>api-error</v>
       </c>
+      <c r="I250" t="str">
+        <v>applied: Enter a value.</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="str">
@@ -6937,6 +7677,9 @@
       <c r="H251" t="str">
         <v>api-error</v>
       </c>
+      <c r="I251" t="str">
+        <v>kept — already follows the guide</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="str">
@@ -6963,6 +7706,9 @@
       <c r="H252" t="str">
         <v>api-error</v>
       </c>
+      <c r="I252" t="str">
+        <v>applied: Enter the country of origin as a 2-letter code (got "${v}").</v>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="str">
@@ -6989,6 +7735,9 @@
       <c r="H253" t="str">
         <v>api-error</v>
       </c>
+      <c r="I253" t="str">
+        <v>applied: Unit control must be one of: ${UNIT_CONTROL.join(', ')}.</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="str">
@@ -7015,6 +7764,9 @@
       <c r="H254" t="str">
         <v>api-error</v>
       </c>
+      <c r="I254" t="str">
+        <v>applied: Enter an item code.</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="str">
@@ -7041,6 +7793,9 @@
       <c r="H255" t="str">
         <v>api-error</v>
       </c>
+      <c r="I255" t="str">
+        <v>applied: Enter a name.</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="str">
@@ -7067,6 +7822,9 @@
       <c r="H256" t="str">
         <v>api-error</v>
       </c>
+      <c r="I256" t="str">
+        <v>applied: Enter a UN number for a hazmat item.</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="str">
@@ -7093,6 +7851,9 @@
       <c r="H257" t="str">
         <v>api-error</v>
       </c>
+      <c r="I257" t="str">
+        <v>applied: Enter a hazard class for a hazmat item.</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="str">
@@ -7119,6 +7880,9 @@
       <c r="H258" t="str">
         <v>api-error</v>
       </c>
+      <c r="I258" t="str">
+        <v>applied: Shelf life must be a whole number of days.</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="str">
@@ -7145,6 +7909,9 @@
       <c r="H259" t="str">
         <v>api-error</v>
       </c>
+      <c r="I259" t="str">
+        <v>applied: ${name} must be a positive number of inches.</v>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="str">
@@ -7171,6 +7938,9 @@
       <c r="H260" t="str">
         <v>api-error</v>
       </c>
+      <c r="I260" t="str">
+        <v>applied: Tare weight must be zero or a positive number of pounds.</v>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="str">
@@ -7197,6 +7967,9 @@
       <c r="H261" t="str">
         <v>api-error</v>
       </c>
+      <c r="I261" t="str">
+        <v>applied: Enter a name.</v>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="str">
@@ -7223,6 +7996,9 @@
       <c r="H262" t="str">
         <v>api-error</v>
       </c>
+      <c r="I262" t="str">
+        <v>applied: The name must be 80 characters or fewer.</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="str">
@@ -7249,6 +8025,9 @@
       <c r="H263" t="str">
         <v>api-error</v>
       </c>
+      <c r="I263" t="str">
+        <v>applied: Nothing was scanned.</v>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="str">
@@ -7275,6 +8054,9 @@
       <c r="H264" t="str">
         <v>api-error</v>
       </c>
+      <c r="I264" t="str">
+        <v>applied: ${t.client_code} requires item scans — scan the item.</v>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="str">
@@ -7301,6 +8083,9 @@
       <c r="H265" t="str">
         <v>api-error</v>
       </c>
+      <c r="I265" t="str">
+        <v>applied: Quantity must be between 0 and ${t.qty_required}.</v>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="str">
@@ -7327,6 +8112,9 @@
       <c r="H266" t="str">
         <v>api-error</v>
       </c>
+      <c r="I266" t="str">
+        <v>kept — already follows the guide</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="str">
@@ -7353,6 +8141,9 @@
       <c r="H267" t="str">
         <v>api-error</v>
       </c>
+      <c r="I267" t="str">
+        <v>applied: ${state.uids.length} unit scan(s) for ${state.qtyPicked} picked — unit-controlled picks ne</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="str">
@@ -7379,6 +8170,9 @@
       <c r="H268" t="str">
         <v>api-error</v>
       </c>
+      <c r="I268" t="str">
+        <v>applied: The type must be one of: ${EXCEPTION_TYPES.join(', ')}.</v>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="str">
@@ -7405,6 +8199,9 @@
       <c r="H269" t="str">
         <v>api-error</v>
       </c>
+      <c r="I269" t="str">
+        <v>applied: A short needs the quantity actually available, between 0 and ${t.qty_required - 1}.</v>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="str">
@@ -7431,6 +8228,9 @@
       <c r="H270" t="str">
         <v>api-error</v>
       </c>
+      <c r="I270" t="str">
+        <v>applied: Quantity ${n} is below what was already scanned (${t.qty_picked}).</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="str">
@@ -7457,6 +8257,9 @@
       <c r="H271" t="str">
         <v>api-error</v>
       </c>
+      <c r="I271" t="str">
+        <v>applied: Quantity must be a whole number.</v>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="str">
@@ -7483,6 +8286,9 @@
       <c r="H272" t="str">
         <v>api-error</v>
       </c>
+      <c r="I272" t="str">
+        <v>applied: Enter a note.</v>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="str">
@@ -7509,6 +8315,9 @@
       <c r="H273" t="str">
         <v>api-error</v>
       </c>
+      <c r="I273" t="str">
+        <v>applied: Enter a resolution.</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="str">
@@ -7535,6 +8344,9 @@
       <c r="H274" t="str">
         <v>api-error</v>
       </c>
+      <c r="I274" t="str">
+        <v>applied: Choose a filter: your picks or one order.</v>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="str">
@@ -7561,6 +8373,9 @@
       <c r="H275" t="str">
         <v>api-error</v>
       </c>
+      <c r="I275" t="str">
+        <v>applied: Status must be open or resolved.</v>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="str">
@@ -7587,6 +8402,9 @@
       <c r="H276" t="str">
         <v>api-error</v>
       </c>
+      <c r="I276" t="str">
+        <v>applied: Add at least one change.</v>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="str">
@@ -7613,6 +8431,9 @@
       <c r="H277" t="str">
         <v>api-error</v>
       </c>
+      <c r="I277" t="str">
+        <v>applied: The portal feature "${c.key}" does not exist.</v>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="str">
@@ -7639,6 +8460,9 @@
       <c r="H278" t="str">
         <v>api-error</v>
       </c>
+      <c r="I278" t="str">
+        <v>applied: Each feature must be turned on or off.</v>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="str">
@@ -7665,6 +8489,9 @@
       <c r="H279" t="str">
         <v>api-error</v>
       </c>
+      <c r="I279" t="str">
+        <v>applied: Mode must be view or act.</v>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="str">
@@ -7691,6 +8518,9 @@
       <c r="H280" t="str">
         <v>api-error</v>
       </c>
+      <c r="I280" t="str">
+        <v>applied: The role "${key}" does not exist. Pick one from the list.</v>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="str">
@@ -7717,6 +8547,9 @@
       <c r="H281" t="str">
         <v>api-error</v>
       </c>
+      <c r="I281" t="str">
+        <v>applied: ${role.name} is not a portal role.</v>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="str">
@@ -7743,6 +8576,9 @@
       <c r="H282" t="str">
         <v>api-error</v>
       </c>
+      <c r="I282" t="str">
+        <v>applied: Pick a role.</v>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="str">
@@ -7769,6 +8605,9 @@
       <c r="H283" t="str">
         <v>api-error</v>
       </c>
+      <c r="I283" t="str">
+        <v>applied: Add at least one rate.</v>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="str">
@@ -7795,6 +8634,9 @@
       <c r="H284" t="str">
         <v>api-error</v>
       </c>
+      <c r="I284" t="str">
+        <v>applied: Every rate needs a name and a type.</v>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="str">
@@ -7821,6 +8663,9 @@
       <c r="H285" t="str">
         <v>api-error</v>
       </c>
+      <c r="I285" t="str">
+        <v>kept — already follows the guide</v>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="str">
@@ -7847,6 +8692,9 @@
       <c r="H286" t="str">
         <v>api-error</v>
       </c>
+      <c r="I286" t="str">
+        <v>applied: ${c.code} is offboarded and read-only. Reactivate it first.</v>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="str">
@@ -7873,6 +8721,9 @@
       <c r="H287" t="str">
         <v>api-error</v>
       </c>
+      <c r="I287" t="str">
+        <v>applied: Status must be one of: ${STATUSES.join(' | ')}.</v>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="str">
@@ -7899,6 +8750,9 @@
       <c r="H288" t="str">
         <v>api-error</v>
       </c>
+      <c r="I288" t="str">
+        <v xml:space="preserve">applied: ${c.code} still has ${oh.qty} unit(s) on hand in ${oh.rows} inventory record(s) — ship or </v>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="str">
@@ -7925,6 +8779,9 @@
       <c r="H289" t="str">
         <v>api-error</v>
       </c>
+      <c r="I289" t="str">
+        <v>applied: Select at least one client.</v>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="str">
@@ -7951,6 +8808,9 @@
       <c r="H290" t="str">
         <v>api-error</v>
       </c>
+      <c r="I290" t="str">
+        <v>applied: Quantity ${line.quantity} does not match the ${unitList.length} unit scan(s) for ${uc.sku_</v>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="str">
@@ -7977,6 +8837,9 @@
       <c r="H291" t="str">
         <v>api-error</v>
       </c>
+      <c r="I291" t="str">
+        <v>applied: Add at least one row.</v>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="str">
@@ -8003,6 +8866,9 @@
       <c r="H292" t="str">
         <v>api-error</v>
       </c>
+      <c r="I292" t="str">
+        <v>applied: ${pending.rows[0].pending} allocation(s) are not picked yet.</v>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="str">
@@ -8029,6 +8895,9 @@
       <c r="H293" t="str">
         <v>api-error</v>
       </c>
+      <c r="I293" t="str">
+        <v>applied: Enter a code, a name and a category.</v>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="str">
@@ -8055,6 +8924,9 @@
       <c r="H294" t="str">
         <v>api-error</v>
       </c>
+      <c r="I294" t="str">
+        <v>applied: Tier ${i}: the rate must be 0 or more.</v>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="str">
@@ -8081,6 +8953,9 @@
       <c r="H295" t="str">
         <v>api-error</v>
       </c>
+      <c r="I295" t="str">
+        <v>applied: Tier ${i} overlaps the previous tier.</v>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="str">
@@ -8107,6 +8982,9 @@
       <c r="H296" t="str">
         <v>api-error</v>
       </c>
+      <c r="I296" t="str">
+        <v>applied: Only the last tier may be open-ended.</v>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="str">
@@ -8133,6 +9011,9 @@
       <c r="H297" t="str">
         <v>api-error</v>
       </c>
+      <c r="I297" t="str">
+        <v>applied: Escalation ${i}: the rate must be 0 or more.</v>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="str">
@@ -8159,6 +9040,9 @@
       <c r="H298" t="str">
         <v>api-error</v>
       </c>
+      <c r="I298" t="str">
+        <v>applied: The rate must be 0 or more.</v>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="str">
@@ -8185,6 +9069,9 @@
       <c r="H299" t="str">
         <v>api-error</v>
       </c>
+      <c r="I299" t="str">
+        <v>applied: Pick a unit.</v>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="str">
@@ -8211,6 +9098,9 @@
       <c r="H300" t="str">
         <v>api-error</v>
       </c>
+      <c r="I300" t="str">
+        <v>applied: Markup applies only to shipping charge codes.</v>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="str">
@@ -8237,6 +9127,9 @@
       <c r="H301" t="str">
         <v>api-error</v>
       </c>
+      <c r="I301" t="str">
+        <v>applied: Enter a name.</v>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="str">
@@ -8263,6 +9156,9 @@
       <c r="H302" t="str">
         <v>api-error</v>
       </c>
+      <c r="I302" t="str">
+        <v>applied: Enter an effective-from date (YYYY-MM-DD).</v>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="str">
@@ -8289,6 +9185,9 @@
       <c r="H303" t="str">
         <v>api-error</v>
       </c>
+      <c r="I303" t="str">
+        <v>applied: Add at least one line.</v>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="str">
@@ -8315,6 +9214,9 @@
       <c r="H304" t="str">
         <v>api-error</v>
       </c>
+      <c r="I304" t="str">
+        <v>applied: A rate card cannot have zero lines. Archive the card instead.</v>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="str">
@@ -8341,6 +9243,9 @@
       <c r="H305" t="str">
         <v>api-error</v>
       </c>
+      <c r="I305" t="str">
+        <v>applied: Enter a value for ${prm.label}.</v>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="str">
@@ -8367,6 +9272,9 @@
       <c r="H306" t="str">
         <v>api-error</v>
       </c>
+      <c r="I306" t="str">
+        <v>applied: Enter a license plate, lot number or customer name.</v>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="str">
@@ -8393,6 +9301,9 @@
       <c r="H307" t="str">
         <v>api-error</v>
       </c>
+      <c r="I307" t="str">
+        <v>applied: Select at least one order.</v>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="str">
@@ -8419,6 +9330,9 @@
       <c r="H308" t="str">
         <v>api-error</v>
       </c>
+      <c r="I308" t="str">
+        <v>applied: Enter the period as YYYY-MM.</v>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="str">
@@ -8445,6 +9359,9 @@
       <c r="H309" t="str">
         <v>api-error</v>
       </c>
+      <c r="I309" t="str">
+        <v>applied: Enter the snapshot date as YYYY-MM-DD.</v>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="str">
@@ -8471,6 +9388,9 @@
       <c r="H310" t="str">
         <v>api-error</v>
       </c>
+      <c r="I310" t="str">
+        <v>applied: Format must be CSV, XLSX or PDF.</v>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="str">
@@ -8497,6 +9417,9 @@
       <c r="H311" t="str">
         <v>api-error</v>
       </c>
+      <c r="I311" t="str">
+        <v>applied: Enter a valid date.</v>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="str">
@@ -8523,6 +9446,9 @@
       <c r="H312" t="str">
         <v>api-error</v>
       </c>
+      <c r="I312" t="str">
+        <v>applied: Pick a report.</v>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="str">
@@ -8549,6 +9475,9 @@
       <c r="H313" t="str">
         <v>api-error</v>
       </c>
+      <c r="I313" t="str">
+        <v>applied: Enter a name.</v>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="str">
@@ -8575,6 +9504,9 @@
       <c r="H314" t="str">
         <v>api-error</v>
       </c>
+      <c r="I314" t="str">
+        <v>applied: The name must be 80 characters or fewer.</v>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="str">
@@ -8601,6 +9533,9 @@
       <c r="H315" t="str">
         <v>api-error</v>
       </c>
+      <c r="I315" t="str">
+        <v>applied: "${r}" is not an email address.</v>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="str">
@@ -8627,6 +9562,9 @@
       <c r="H316" t="str">
         <v>api-error</v>
       </c>
+      <c r="I316" t="str">
+        <v>applied: You do not have access to this.</v>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="str">
@@ -8653,6 +9591,9 @@
       <c r="H317" t="str">
         <v>api-error</v>
       </c>
+      <c r="I317" t="str">
+        <v>applied: Pick a status.</v>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="str">
@@ -8679,6 +9620,9 @@
       <c r="H318" t="str">
         <v>api-error</v>
       </c>
+      <c r="I318" t="str">
+        <v>applied: Add at least one allocation.</v>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="str">
@@ -8705,6 +9649,9 @@
       <c r="H319" t="str">
         <v>api-error</v>
       </c>
+      <c r="I319" t="str">
+        <v>applied: Attach a photo.</v>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="str">
@@ -8731,6 +9678,9 @@
       <c r="H320" t="str">
         <v>api-error</v>
       </c>
+      <c r="I320" t="str">
+        <v>applied: Enter a reason.</v>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="str">
@@ -8757,6 +9707,9 @@
       <c r="H321" t="str">
         <v>api-error</v>
       </c>
+      <c r="I321" t="str">
+        <v>applied: The PIN must be 4 to 8 digits.</v>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="str">
@@ -8783,6 +9736,9 @@
       <c r="H322" t="str">
         <v>api-error</v>
       </c>
+      <c r="I322" t="str">
+        <v>applied: Quantity must be greater than 0.</v>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="str">
@@ -8809,6 +9765,9 @@
       <c r="H323" t="str">
         <v>api-error</v>
       </c>
+      <c r="I323" t="str">
+        <v>applied: Enter a quantity.</v>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="str">
@@ -8835,6 +9794,9 @@
       <c r="H324" t="str">
         <v>api-error</v>
       </c>
+      <c r="I324" t="str">
+        <v>applied: Choose a file to upload.</v>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="str">
@@ -8861,6 +9823,9 @@
       <c r="H325" t="str">
         <v>api-error</v>
       </c>
+      <c r="I325" t="str">
+        <v>applied: Add at least one line.</v>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="str">
@@ -8887,6 +9852,9 @@
       <c r="H326" t="str">
         <v>api-error</v>
       </c>
+      <c r="I326" t="str">
+        <v>applied: The edited data is missing.</v>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="str">
@@ -8913,6 +9881,9 @@
       <c r="H327" t="str">
         <v>api-error</v>
       </c>
+      <c r="I327" t="str">
+        <v>applied: Enter a name.</v>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="str">
@@ -8939,6 +9910,9 @@
       <c r="H328" t="str">
         <v>api-error</v>
       </c>
+      <c r="I328" t="str">
+        <v>applied: Add at least one handling unit.</v>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="str">
@@ -8965,6 +9939,9 @@
       <c r="H329" t="str">
         <v>api-error</v>
       </c>
+      <c r="I329" t="str">
+        <v>applied: Enter a UN number for a hazmat item.</v>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="str">
@@ -8991,6 +9968,9 @@
       <c r="H330" t="str">
         <v>api-error</v>
       </c>
+      <c r="I330" t="str">
+        <v>applied: Enter a hazard class for a hazmat item.</v>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="str">
@@ -9017,6 +9997,9 @@
       <c r="H331" t="str">
         <v>api-error</v>
       </c>
+      <c r="I331" t="str">
+        <v>applied: Enter a code and a name.</v>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="str">
@@ -9043,6 +10026,9 @@
       <c r="H332" t="str">
         <v>api-error</v>
       </c>
+      <c r="I332" t="str">
+        <v>applied: Enter the period as YYYY-MM.</v>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="str">
@@ -9069,6 +10055,9 @@
       <c r="H333" t="str">
         <v>api-error</v>
       </c>
+      <c r="I333" t="str">
+        <v>applied: Pick a status.</v>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="str">
@@ -9095,6 +10084,9 @@
       <c r="H334" t="str">
         <v>api-error</v>
       </c>
+      <c r="I334" t="str">
+        <v>applied: Nothing was scanned.</v>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="str">
@@ -9121,6 +10113,9 @@
       <c r="H335" t="str">
         <v>api-error</v>
       </c>
+      <c r="I335" t="str">
+        <v>applied: Workflow must be one of: ${WORKFLOWS.join('|')}.</v>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="str">
@@ -9147,6 +10142,9 @@
       <c r="H336" t="str">
         <v>api-error</v>
       </c>
+      <c r="I336" t="str">
+        <v>applied: The scanned unit list is not in the expected shape.</v>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="str">
@@ -9173,6 +10171,9 @@
       <c r="H337" t="str">
         <v>api-error</v>
       </c>
+      <c r="I337" t="str">
+        <v>applied: ${pending.rows[0].pending} allocation(s) are not picked yet.</v>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="str">
@@ -9199,6 +10200,9 @@
       <c r="H338" t="str">
         <v>api-error</v>
       </c>
+      <c r="I338" t="str">
+        <v>applied: ${wantCarrier || 'that carrier'} ${wantService || ''} was not offered for this box.</v>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="str">
@@ -9225,6 +10229,9 @@
       <c r="H339" t="str">
         <v>api-error</v>
       </c>
+      <c r="I339" t="str">
+        <v>applied: ${err.message} (label refunded).</v>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="str">
@@ -9251,6 +10258,9 @@
       <c r="H340" t="str">
         <v>api-error</v>
       </c>
+      <c r="I340" t="str">
+        <v>applied: ${pending.rows[0].n} allocation(s) are not picked yet.</v>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="str">
@@ -9277,6 +10287,9 @@
       <c r="H341" t="str">
         <v>api-error</v>
       </c>
+      <c r="I341" t="str">
+        <v>applied: Nothing was scanned.</v>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="str">
@@ -9303,6 +10316,9 @@
       <c r="H342" t="str">
         <v>api-error</v>
       </c>
+      <c r="I342" t="str">
+        <v>applied: ${pkg.package_number} is voided.</v>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="str">
@@ -9329,6 +10345,9 @@
       <c r="H343" t="str">
         <v>api-error</v>
       </c>
+      <c r="I343" t="str">
+        <v>kept — already follows the guide</v>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="str">
@@ -9355,6 +10374,9 @@
       <c r="H344" t="str">
         <v>api-error</v>
       </c>
+      <c r="I344" t="str">
+        <v>applied: ${pkg.package_number} is ${packStatus(pkg)} — only a closed, unlabeled package can be reop</v>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="str">
@@ -9381,6 +10403,9 @@
       <c r="H345" t="str">
         <v>api-error</v>
       </c>
+      <c r="I345" t="str">
+        <v>applied: ${pkg.packageNumber} is still open — close it (weight + dims) before buying a label.</v>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="str">
@@ -9407,6 +10432,9 @@
       <c r="H346" t="str">
         <v>api-error</v>
       </c>
+      <c r="I346" t="str">
+        <v>applied: ${pkg.packageNumber} already has a label (${pkg.trackingNumber}) — void the package to rep</v>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="str">
@@ -9433,6 +10461,9 @@
       <c r="H347" t="str">
         <v>api-error</v>
       </c>
+      <c r="I347" t="str">
+        <v>applied: ${pkg.package_number} belongs to order ${pkg.order_number}, not this pick.</v>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="str">
@@ -9459,6 +10490,9 @@
       <c r="H348" t="str">
         <v>api-error</v>
       </c>
+      <c r="I348" t="str">
+        <v>applied: ${pkg.package_number} is ${packStatus(pkg)} — open a new package.</v>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="str">
@@ -9485,6 +10519,9 @@
       <c r="H349" t="str">
         <v>api-error</v>
       </c>
+      <c r="I349" t="str">
+        <v>kept — already follows the guide</v>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="str">
@@ -9511,6 +10548,9 @@
       <c r="H350" t="str">
         <v>api-error</v>
       </c>
+      <c r="I350" t="str">
+        <v>applied: Pick a carrier and service.</v>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="str">
@@ -9537,6 +10577,9 @@
       <c r="H351" t="str">
         <v>api-error</v>
       </c>
+      <c r="I351" t="str">
+        <v>applied: ${p.package_number} is voided.</v>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="str">
@@ -9563,6 +10606,9 @@
       <c r="H352" t="str">
         <v>api-error</v>
       </c>
+      <c r="I352" t="str">
+        <v>applied: ${p.package_number} is still open — close it (weight + dims) before creating a label.</v>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="str">
@@ -9589,6 +10635,9 @@
       <c r="H353" t="str">
         <v>api-error</v>
       </c>
+      <c r="I353" t="str">
+        <v>applied: ${p.package_number} already has a label (${p.tracking_number}) — void it first.</v>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="str">
@@ -9615,6 +10664,9 @@
       <c r="H354" t="str">
         <v>api-error</v>
       </c>
+      <c r="I354" t="str">
+        <v>kept — already follows the guide</v>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="str">
@@ -9641,6 +10693,9 @@
       <c r="H355" t="str">
         <v>api-error</v>
       </c>
+      <c r="I355" t="str">
+        <v>applied: Enter a tracking number.</v>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="str">
@@ -9667,6 +10722,9 @@
       <c r="H356" t="str">
         <v>api-error</v>
       </c>
+      <c r="I356" t="str">
+        <v>applied: ${p.order_number} has shipped — the label cannot be voided from the WMS.</v>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="str">
@@ -9693,6 +10751,9 @@
       <c r="H357" t="str">
         <v>api-error</v>
       </c>
+      <c r="I357" t="str">
+        <v>applied: Event must be one of: ORDER_NOTIFY, SHIP_NOTIFY, ITEM_ORDER_NOTIFY, ITEM_SHIP_NOTIFY.</v>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="str">
@@ -9719,6 +10780,9 @@
       <c r="H358" t="str">
         <v>api-error</v>
       </c>
+      <c r="I358" t="str">
+        <v>applied: Enter a tracking number or an order number.</v>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="str">
@@ -9745,6 +10809,9 @@
       <c r="H359" t="str">
         <v>api-error</v>
       </c>
+      <c r="I359" t="str">
+        <v>applied: Select at least one order.</v>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="str">
@@ -9771,6 +10838,9 @@
       <c r="H360" t="str">
         <v>api-error</v>
       </c>
+      <c r="I360" t="str">
+        <v>applied: Status must be one of: PLANNING, RELEASED, IN_PROGRESS, COMPLETED, CANCELLED.</v>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="str">
@@ -9797,6 +10867,9 @@
       <c r="H361" t="str">
         <v>api-error</v>
       </c>
+      <c r="I361" t="str">
+        <v>applied: You do not have access to this.</v>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="str">
@@ -9823,6 +10896,9 @@
       <c r="H362" t="str">
         <v>api-error</v>
       </c>
+      <c r="I362" t="str">
+        <v>applied: Every unit needs a unit ID.</v>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="str">
@@ -9849,6 +10925,9 @@
       <c r="H363" t="str">
         <v>api-error</v>
       </c>
+      <c r="I363" t="str">
+        <v>applied: Unit ID ${uid} appears twice in this receipt.</v>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="str">
@@ -9875,6 +10954,9 @@
       <c r="H364" t="str">
         <v>api-error</v>
       </c>
+      <c r="I364" t="str">
+        <v>applied: Pick a license plate or a location.</v>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="str">
@@ -9901,6 +10983,9 @@
       <c r="H365" t="str">
         <v>api-error</v>
       </c>
+      <c r="I365" t="str">
+        <v>applied: Enter a unit ID.</v>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="str">
@@ -9927,6 +11012,9 @@
       <c r="H366" t="str">
         <v>api-error</v>
       </c>
+      <c r="I366" t="str">
+        <v>applied: ${r.count} units carry ${uid}. Pick a client.</v>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="str">
@@ -9953,6 +11041,9 @@
       <c r="H367" t="str">
         <v>api-error</v>
       </c>
+      <c r="I367" t="str">
+        <v>applied: You do not have access to this.</v>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="str">
@@ -9979,6 +11070,9 @@
       <c r="H368" t="str">
         <v>api-error</v>
       </c>
+      <c r="I368" t="str">
+        <v>applied: The role "${roleKey}" does not exist. Pick one from the list.</v>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="str">
@@ -10005,6 +11099,9 @@
       <c r="H369" t="str">
         <v>api-error</v>
       </c>
+      <c r="I369" t="str">
+        <v>applied: Pick a role.</v>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="str">
@@ -10031,6 +11128,9 @@
       <c r="H370" t="str">
         <v>api-error</v>
       </c>
+      <c r="I370" t="str">
+        <v>applied: That client could not be found.</v>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="str">
@@ -10057,6 +11157,9 @@
       <c r="H371" t="str">
         <v>api-error</v>
       </c>
+      <c r="I371" t="str">
+        <v>applied: That warehouse could not be found.</v>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="str">
@@ -10083,6 +11186,9 @@
       <c r="H372" t="str">
         <v>api-error</v>
       </c>
+      <c r="I372" t="str">
+        <v>applied: Add at least one change.</v>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="str">
@@ -10109,6 +11215,9 @@
       <c r="H373" t="str">
         <v>api-error</v>
       </c>
+      <c r="I373" t="str">
+        <v>applied: The permission "${c.key}" does not exist.</v>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="str">
@@ -10135,6 +11244,9 @@
       <c r="H374" t="str">
         <v>api-error</v>
       </c>
+      <c r="I374" t="str">
+        <v>applied: The "${P.labelOf(c.key)}" permission is admin-only and cannot be granted per user.</v>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="str">
@@ -10161,6 +11273,9 @@
       <c r="H375" t="str">
         <v>api-error</v>
       </c>
+      <c r="I375" t="str">
+        <v>skipped — server log line, not user-facing</v>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="str">
@@ -10187,6 +11302,9 @@
       <c r="H376" t="str">
         <v>api-error</v>
       </c>
+      <c r="I376" t="str">
+        <v>skipped — server log line, not user-facing</v>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="str">
@@ -10213,6 +11331,9 @@
       <c r="H377" t="str">
         <v>api-error</v>
       </c>
+      <c r="I377" t="str">
+        <v>skipped — server log line, not user-facing</v>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="str">
@@ -10239,6 +11360,9 @@
       <c r="H378" t="str">
         <v>toast</v>
       </c>
+      <c r="I378" t="str">
+        <v/>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="str">
@@ -10265,6 +11389,9 @@
       <c r="H379" t="str">
         <v>template-text</v>
       </c>
+      <c r="I379" t="str">
+        <v/>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="str">
@@ -10291,6 +11418,9 @@
       <c r="H380" t="str">
         <v>toast</v>
       </c>
+      <c r="I380" t="str">
+        <v/>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="str">
@@ -10317,6 +11447,9 @@
       <c r="H381" t="str">
         <v>text</v>
       </c>
+      <c r="I381" t="str">
+        <v/>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="str">
@@ -10343,6 +11476,9 @@
       <c r="H382" t="str">
         <v>option</v>
       </c>
+      <c r="I382" t="str">
+        <v/>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="str">
@@ -10369,6 +11505,9 @@
       <c r="H383" t="str">
         <v>option</v>
       </c>
+      <c r="I383" t="str">
+        <v/>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="str">
@@ -10395,6 +11534,9 @@
       <c r="H384" t="str">
         <v>template-text</v>
       </c>
+      <c r="I384" t="str">
+        <v/>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
@@ -10421,6 +11563,9 @@
       <c r="H385" t="str">
         <v>template-text</v>
       </c>
+      <c r="I385" t="str">
+        <v/>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
@@ -10447,6 +11592,9 @@
       <c r="H386" t="str">
         <v>option</v>
       </c>
+      <c r="I386" t="str">
+        <v/>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="str">
@@ -10473,6 +11621,9 @@
       <c r="H387" t="str">
         <v>option</v>
       </c>
+      <c r="I387" t="str">
+        <v/>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="str">
@@ -10499,6 +11650,9 @@
       <c r="H388" t="str">
         <v>toast</v>
       </c>
+      <c r="I388" t="str">
+        <v/>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="str">
@@ -10525,6 +11679,9 @@
       <c r="H389" t="str">
         <v>toast</v>
       </c>
+      <c r="I389" t="str">
+        <v/>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="str">
@@ -10551,6 +11708,9 @@
       <c r="H390" t="str">
         <v>toast</v>
       </c>
+      <c r="I390" t="str">
+        <v/>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="str">
@@ -10577,6 +11737,9 @@
       <c r="H391" t="str">
         <v>option</v>
       </c>
+      <c r="I391" t="str">
+        <v/>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="str">
@@ -10603,6 +11766,9 @@
       <c r="H392" t="str">
         <v>option</v>
       </c>
+      <c r="I392" t="str">
+        <v/>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="str">
@@ -10629,6 +11795,9 @@
       <c r="H393" t="str">
         <v>text</v>
       </c>
+      <c r="I393" t="str">
+        <v/>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="str">
@@ -10655,6 +11824,9 @@
       <c r="H394" t="str">
         <v>toast</v>
       </c>
+      <c r="I394" t="str">
+        <v/>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="str">
@@ -10681,6 +11853,9 @@
       <c r="H395" t="str">
         <v>template-text</v>
       </c>
+      <c r="I395" t="str">
+        <v/>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="str">
@@ -10707,6 +11882,9 @@
       <c r="H396" t="str">
         <v>toast</v>
       </c>
+      <c r="I396" t="str">
+        <v/>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="str">
@@ -10733,6 +11911,9 @@
       <c r="H397" t="str">
         <v>template-text</v>
       </c>
+      <c r="I397" t="str">
+        <v/>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="str">
@@ -10759,6 +11940,9 @@
       <c r="H398" t="str">
         <v>template-text</v>
       </c>
+      <c r="I398" t="str">
+        <v/>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="str">
@@ -10785,6 +11969,9 @@
       <c r="H399" t="str">
         <v>template-text</v>
       </c>
+      <c r="I399" t="str">
+        <v/>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="str">
@@ -10811,6 +11998,9 @@
       <c r="H400" t="str">
         <v>option</v>
       </c>
+      <c r="I400" t="str">
+        <v/>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="str">
@@ -10837,6 +12027,9 @@
       <c r="H401" t="str">
         <v>api-error</v>
       </c>
+      <c r="I401" t="str">
+        <v>applied (no tooltip: plain string, not an element): ${c.code} is not mapped to a legacy-system client. There is nothing to catch up.</v>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="str">
@@ -10863,6 +12056,9 @@
       <c r="H402" t="str">
         <v>api-error</v>
       </c>
+      <c r="I402" t="str">
+        <v>applied (no tooltip: plain string, not an element): ${c.code} is still mirrored from the legacy system, which is its system of record. Catch-u</v>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="str">
@@ -10889,6 +12085,9 @@
       <c r="H403" t="str">
         <v>api-error</v>
       </c>
+      <c r="I403" t="str">
+        <v>applied (no tooltip: plain string, not an element): Catch-up is not available yet — the database update (099) has not been applied.</v>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="str">
@@ -10915,6 +12114,9 @@
       <c r="H404" t="str">
         <v>api-error</v>
       </c>
+      <c r="I404" t="str">
+        <v>applied (no tooltip: plain string, not an element): The legacy-system client ${code} has not appeared in any preview run.</v>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="str">
@@ -10941,6 +12143,9 @@
       <c r="H405" t="str">
         <v>api-error</v>
       </c>
+      <c r="I405" t="str">
+        <v>applied (no tooltip: plain string, not an element): The legacy-system client ${code} is already mapped.</v>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
@@ -10967,6 +12172,9 @@
       <c r="H406" t="str">
         <v>api-error</v>
       </c>
+      <c r="I406" t="str">
+        <v>applied (no tooltip: plain string, not an element): The legacy-system client ${code} is not mapped. Pick a WMS client before committing.</v>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
@@ -10993,6 +12201,9 @@
       <c r="H407" t="str">
         <v>api-error</v>
       </c>
+      <c r="I407" t="str">
+        <v>applied (no tooltip: plain string, not an element): The legacy system is not configured. Missing settings: ${odata.missing().join(', ')}.</v>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
@@ -11019,6 +12230,9 @@
       <c r="H408" t="str">
         <v>api-error</v>
       </c>
+      <c r="I408" t="str">
+        <v>applied: No replay cursor yet — run the baseline (scripts/baseline-apply.js) or set the cursor unde</v>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
@@ -11045,6 +12259,9 @@
       <c r="H409" t="str">
         <v>api-error</v>
       </c>
+      <c r="I409" t="str">
+        <v>applied (no tooltip: plain string, not an element): ${c.code} is not mapped to a legacy-system client.</v>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
@@ -11071,6 +12288,9 @@
       <c r="H410" t="str">
         <v>api-error</v>
       </c>
+      <c r="I410" t="str">
+        <v>applied (no tooltip: plain string, not an element): ${c.code} cannot go live: the legacy system and the WMS differ on ${real.length} line(s) —</v>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="str">
@@ -11097,6 +12317,9 @@
       <c r="H411" t="str">
         <v>api-error</v>
       </c>
+      <c r="I411" t="str">
+        <v>applied (no tooltip: plain string, not an element): ${c.code} is already mirroring the legacy system.</v>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="str">
@@ -11123,6 +12346,9 @@
       <c r="H412" t="str">
         <v>api-error</v>
       </c>
+      <c r="I412" t="str">
+        <v>applied (no tooltip: plain string, not an element): ${c.code} is not mapped to a legacy-system client. Map it under Settings → Migration first</v>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="str">
@@ -11149,6 +12375,9 @@
       <c r="H413" t="str">
         <v>api-error</v>
       </c>
+      <c r="I413" t="str">
+        <v>applied (no tooltip: plain string, not an element): The legacy system is not configured. Missing settings: ${odata.missing().join(', ')}.</v>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="str">
@@ -11175,6 +12404,9 @@
       <c r="H414" t="str">
         <v>api-error</v>
       </c>
+      <c r="I414" t="str">
+        <v>applied (no tooltip: plain string, not an element): ${err.message} (LABEL BOUGHT BUT NOT RECORDED — refund failed; label provider ${bought.id}</v>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="str">
@@ -11201,6 +12433,9 @@
       <c r="H415" t="str">
         <v>api-error</v>
       </c>
+      <c r="I415" t="str">
+        <v>applied (no tooltip: plain string, not an element): The shipping system lookup failed — ${err.message}</v>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="str">
@@ -11227,6 +12462,9 @@
       <c r="H416" t="str">
         <v>api-error</v>
       </c>
+      <c r="I416" t="str">
+        <v>applied (no tooltip: plain string, not an element): The shipping system has no label with that number.</v>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="str">
@@ -11253,6 +12491,9 @@
       <c r="H417" t="str">
         <v>api-error</v>
       </c>
+      <c r="I417" t="str">
+        <v>applied (no tooltip: plain string, not an element): That label is for order ${sh.orderNumber || sh.orderId} in the shipping system, which is n</v>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="str">
@@ -11279,6 +12520,9 @@
       <c r="H418" t="str">
         <v>api-error</v>
       </c>
+      <c r="I418" t="str">
+        <v>applied (no tooltip: plain string, not an element): ${out.message} · ${pkg.packageNumber} needs a weight — neither the shipping system nor the</v>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="str">
@@ -11305,6 +12549,9 @@
       <c r="H419" t="str">
         <v>api-error</v>
       </c>
+      <c r="I419" t="str">
+        <v>applied (no tooltip: plain string, not an element): ${p.order_number} did not come from the shipping system. Use the label provider instead.</v>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="str">
@@ -11331,6 +12578,9 @@
       <c r="H420" t="str">
         <v>api-error</v>
       </c>
+      <c r="I420" t="str">
+        <v>applied (no tooltip: plain string, not an element): No carrier/service mapped for requested service "${p.requested_service || '(none)'}" — pic</v>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="str">
@@ -11357,6 +12607,9 @@
       <c r="H421" t="str">
         <v>api-error</v>
       </c>
+      <c r="I421" t="str">
+        <v>applied (no tooltip: plain string, not an element): The shipping system returned no tracking number.</v>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="str">
@@ -11383,6 +12636,9 @@
       <c r="H422" t="str">
         <v>api-error</v>
       </c>
+      <c r="I422" t="str">
+        <v>applied (no tooltip: plain string, not an element): This label was printed in the shipping system (${l.tracking_number}), which does not retur</v>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="str">
@@ -11409,6 +12665,9 @@
       <c r="H423" t="str">
         <v>api-error</v>
       </c>
+      <c r="I423" t="str">
+        <v>applied (no tooltip: plain string, not an element): ${p.order_number} did not come from the shipping system.</v>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="str">
@@ -11435,6 +12694,9 @@
       <c r="H424" t="str">
         <v>api-error</v>
       </c>
+      <c r="I424" t="str">
+        <v>applied (no tooltip: plain string, not an element): This package has no live label from the shipping system.</v>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="str">
@@ -11461,6 +12723,9 @@
       <c r="H425" t="str">
         <v>api-error</v>
       </c>
+      <c r="I425" t="str">
+        <v>skipped — code fragment mis-extracted; the visible words in it are fine</v>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="str">
@@ -11487,6 +12752,9 @@
       <c r="H426" t="str">
         <v>api-error</v>
       </c>
+      <c r="I426" t="str">
+        <v>applied (no tooltip: plain string, not an element): The shipping system is not configured. Missing settings: ${ss.missing().join(', ')}.</v>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="str">
@@ -11513,6 +12781,9 @@
       <c r="H427" t="str">
         <v>api-error</v>
       </c>
+      <c r="I427" t="str">
+        <v>applied (no tooltip: plain string, not an element): Connect the shipping system to a warehouse first.</v>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="str">
@@ -11539,6 +12810,9 @@
       <c r="H428" t="str">
         <v>api-error</v>
       </c>
+      <c r="I428" t="str">
+        <v xml:space="preserve">applied (no tooltip: plain string, not an element): This order did not come from the shipping system. Close the package and use its own label </v>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="str">
@@ -11565,6 +12839,9 @@
       <c r="H429" t="str">
         <v>api-error</v>
       </c>
+      <c r="I429" t="str">
+        <v>applied (no tooltip: plain string, not an element): The shipping system is not connected. Save the warehouse under Settings → Integrations.</v>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="str">
@@ -11591,6 +12868,9 @@
       <c r="H430" t="str">
         <v>html-text</v>
       </c>
+      <c r="I430" t="str">
+        <v>applied + tooltip: Label batches from the shipping system and manual waves</v>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="str">
@@ -11617,6 +12897,9 @@
       <c r="H431" t="str">
         <v>html-text</v>
       </c>
+      <c r="I431" t="str">
+        <v>applied + tooltip: Excalibur catch-up</v>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="str">
@@ -11643,6 +12926,9 @@
       <c r="H432" t="str">
         <v>html-text</v>
       </c>
+      <c r="I432" t="str">
+        <v>applied + tooltip: Integrations — ShipStation</v>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="str">
@@ -11669,6 +12955,9 @@
       <c r="H433" t="str">
         <v>html-text</v>
       </c>
+      <c r="I433" t="str">
+        <v>applied + tooltip: Migration — Excalibur</v>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
@@ -11695,6 +12984,9 @@
       <c r="H434" t="str">
         <v>html-text</v>
       </c>
+      <c r="I434" t="str">
+        <v>applied: SDS review queue · per-field confidence and audit log</v>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
@@ -11721,6 +13013,9 @@
       <c r="H435" t="str">
         <v>toast</v>
       </c>
+      <c r="I435" t="str">
+        <v>applied (no tooltip: plain string, not an element): ${c.code} is mirroring the legacy system again</v>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
@@ -11747,6 +13042,9 @@
       <c r="H436" t="str">
         <v>option</v>
       </c>
+      <c r="I436" t="str">
+        <v>applied (no tooltip: plain string, not an element): Label first — the office prints in the shipping system before picking (default)</v>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
@@ -11773,6 +13071,9 @@
       <c r="H437" t="str">
         <v>template-text</v>
       </c>
+      <c r="I437" t="str">
+        <v xml:space="preserve">applied + tooltip: Shipments the WMS completed since ${esc(d.client.code)} went live with no matching posted </v>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
@@ -11799,6 +13100,9 @@
       <c r="H438" t="str">
         <v>template-text</v>
       </c>
+      <c r="I438" t="str">
+        <v>applied + tooltip: Legacy-system drift unavailable — ${esc(dr.reason || 'no live comparison')}.</v>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
@@ -11825,6 +13129,9 @@
       <c r="H439" t="str">
         <v>template-text</v>
       </c>
+      <c r="I439" t="str">
+        <v>applied + tooltip: The legacy system holds ${esc(dr.excaliburQty)} units vs ${esc(dr.wmsQty)} in the WMS; the</v>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
@@ -11851,6 +13158,9 @@
       <c r="H440" t="str">
         <v>toast</v>
       </c>
+      <c r="I440" t="str">
+        <v>applied (no tooltip: plain string, not an element): The legacy system could not be read — ${res.reason || 'unavailable'}</v>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
@@ -11877,6 +13187,9 @@
       <c r="H441" t="str">
         <v>toast</v>
       </c>
+      <c r="I441" t="str">
+        <v xml:space="preserve">applied (no tooltip: plain string, not an element): Checked the legacy system: ${res.fetched} posted shipment${res.fetched === 1 ? '' : 's'}, </v>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
@@ -11903,6 +13216,9 @@
       <c r="H442" t="str">
         <v>empty-state</v>
       </c>
+      <c r="I442" t="str">
+        <v>applied (no tooltip: plain string, not an element): Everything shipped since go-live has been keyed into the legacy system.</v>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
@@ -11929,6 +13245,9 @@
       <c r="H443" t="str">
         <v>option</v>
       </c>
+      <c r="I443" t="str">
+        <v>applied (no tooltip: plain string, not an element): Mark ${_ecSelected.size} shipment${_ecSelected.size === 1 ? '' : 's'} as keyed in the lega</v>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
@@ -11955,6 +13274,9 @@
       <c r="H444" t="str">
         <v>option</v>
       </c>
+      <c r="I444" t="str">
+        <v>applied (no tooltip: plain string, not an element): Legacy-system document # (optional)</v>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
@@ -11981,6 +13303,9 @@
       <c r="H445" t="str">
         <v>option</v>
       </c>
+      <c r="I445" t="str">
+        <v>kept — vendor is the subject of this title</v>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="str">
@@ -12007,6 +13332,9 @@
       <c r="H446" t="str">
         <v>text</v>
       </c>
+      <c r="I446" t="str">
+        <v>applied (no tooltip: plain string, not an element): ${d.unkeyed} un-keyed shipment${d.unkeyed === 1 ? '' : 's'} · ${d.units} unit${d.units ===</v>
+      </c>
     </row>
     <row r="447">
       <c r="A447" t="str">
@@ -12033,6 +13361,9 @@
       <c r="H447" t="str">
         <v>template-attr</v>
       </c>
+      <c r="I447" t="str">
+        <v>applied: Per-field SDS extraction: versions the SDS, per-field confidence, audit log, queues review</v>
+      </c>
     </row>
     <row r="448">
       <c r="A448" t="str">
@@ -12059,6 +13390,9 @@
       <c r="H448" t="str">
         <v>template-text</v>
       </c>
+      <c r="I448" t="str">
+        <v>kept — vendor is the subject of this settings page</v>
+      </c>
     </row>
     <row r="449">
       <c r="A449" t="str">
@@ -12085,6 +13419,9 @@
       <c r="H449" t="str">
         <v>template-text</v>
       </c>
+      <c r="I449" t="str">
+        <v>kept — vendor is the subject of this settings page</v>
+      </c>
     </row>
     <row r="450">
       <c r="A450" t="str">
@@ -12111,6 +13448,9 @@
       <c r="H450" t="str">
         <v>template-text</v>
       </c>
+      <c r="I450" t="str">
+        <v>kept — vendor is the subject of this settings page</v>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="str">
@@ -12137,6 +13477,9 @@
       <c r="H451" t="str">
         <v>template-text</v>
       </c>
+      <c r="I451" t="str">
+        <v>kept — vendor is the subject of this settings page</v>
+      </c>
     </row>
     <row r="452">
       <c r="A452" t="str">
@@ -12163,6 +13506,9 @@
       <c r="H452" t="str">
         <v>template-text</v>
       </c>
+      <c r="I452" t="str">
+        <v>kept — vendor is the subject of this settings page</v>
+      </c>
     </row>
     <row r="453">
       <c r="A453" t="str">
@@ -12189,6 +13535,9 @@
       <c r="H453" t="str">
         <v>template-text</v>
       </c>
+      <c r="I453" t="str">
+        <v>skipped — code fragment mis-extracted; the visible words in it are fine</v>
+      </c>
     </row>
     <row r="454">
       <c r="A454" t="str">
@@ -12215,6 +13564,9 @@
       <c r="H454" t="str">
         <v>template-text</v>
       </c>
+      <c r="I454" t="str">
+        <v>kept — vendor is the subject of this settings page</v>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="str">
@@ -12241,6 +13593,9 @@
       <c r="H455" t="str">
         <v>template-text</v>
       </c>
+      <c r="I455" t="str">
+        <v>kept — vendor is the subject of this settings page</v>
+      </c>
     </row>
     <row r="456">
       <c r="A456" t="str">
@@ -12267,6 +13622,9 @@
       <c r="H456" t="str">
         <v>template-text</v>
       </c>
+      <c r="I456" t="str">
+        <v>kept — vendor is the subject of this settings page</v>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="str">
@@ -12293,6 +13651,9 @@
       <c r="H457" t="str">
         <v>template-text</v>
       </c>
+      <c r="I457" t="str">
+        <v>kept — vendor is the subject of this settings page</v>
+      </c>
     </row>
     <row r="458">
       <c r="A458" t="str">
@@ -12319,6 +13680,9 @@
       <c r="H458" t="str">
         <v>toast</v>
       </c>
+      <c r="I458" t="str">
+        <v>kept — vendor is the subject of this settings page</v>
+      </c>
     </row>
     <row r="459">
       <c r="A459" t="str">
@@ -12345,6 +13709,9 @@
       <c r="H459" t="str">
         <v>empty-state</v>
       </c>
+      <c r="I459" t="str">
+        <v>kept — vendor is the subject of this settings page</v>
+      </c>
     </row>
     <row r="460">
       <c r="A460" t="str">
@@ -12371,6 +13738,9 @@
       <c r="H460" t="str">
         <v>option</v>
       </c>
+      <c r="I460" t="str">
+        <v>kept — vendor is the subject of this settings page</v>
+      </c>
     </row>
     <row r="461">
       <c r="A461" t="str">
@@ -12397,6 +13767,9 @@
       <c r="H461" t="str">
         <v>option</v>
       </c>
+      <c r="I461" t="str">
+        <v>kept — vendor is the subject of this settings page</v>
+      </c>
     </row>
     <row r="462">
       <c r="A462" t="str">
@@ -12423,6 +13796,9 @@
       <c r="H462" t="str">
         <v>option</v>
       </c>
+      <c r="I462" t="str">
+        <v>kept — vendor is the subject of this settings page</v>
+      </c>
     </row>
     <row r="463">
       <c r="A463" t="str">
@@ -12449,6 +13825,9 @@
       <c r="H463" t="str">
         <v>option</v>
       </c>
+      <c r="I463" t="str">
+        <v>kept — vendor is the subject of this settings page</v>
+      </c>
     </row>
     <row r="464">
       <c r="A464" t="str">
@@ -12475,6 +13854,9 @@
       <c r="H464" t="str">
         <v>option</v>
       </c>
+      <c r="I464" t="str">
+        <v>kept — vendor is the subject of this title</v>
+      </c>
     </row>
     <row r="465">
       <c r="A465" t="str">
@@ -12501,6 +13883,9 @@
       <c r="H465" t="str">
         <v>template-text</v>
       </c>
+      <c r="I465" t="str">
+        <v>applied + tooltip: Scan the label printed in the shipping system — it attaches to this box. Ship stays off un</v>
+      </c>
     </row>
     <row r="466">
       <c r="A466" t="str">
@@ -12527,6 +13912,9 @@
       <c r="H466" t="str">
         <v>template-text</v>
       </c>
+      <c r="I466" t="str">
+        <v>applied + tooltip: Typed dims instead of a box scan. Closing buys the shipping system label with these number</v>
+      </c>
     </row>
     <row r="467">
       <c r="A467" t="str">
@@ -12553,6 +13941,9 @@
       <c r="H467" t="str">
         <v>toast</v>
       </c>
+      <c r="I467" t="str">
+        <v>applied (no tooltip: plain string, not an element): Label voided in the shipping system</v>
+      </c>
     </row>
     <row r="468">
       <c r="A468" t="str">
@@ -12579,6 +13970,9 @@
       <c r="H468" t="str">
         <v>option</v>
       </c>
+      <c r="I468" t="str">
+        <v>applied (no tooltip: plain string, not an element): Shipping-system label for ${pkg.packageNumber}</v>
+      </c>
     </row>
     <row r="469">
       <c r="A469" t="str">
@@ -12605,6 +13999,9 @@
       <c r="H469" t="str">
         <v>attr</v>
       </c>
+      <c r="I469" t="str">
+        <v>applied (no tooltip: plain string, not an element): Writes to the shipping system are locked (the longer fs-locked hint on the same line was reworded too)</v>
+      </c>
     </row>
     <row r="470">
       <c r="A470" t="str">
@@ -12631,6 +14028,9 @@
       <c r="H470" t="str">
         <v>template-text</v>
       </c>
+      <c r="I470" t="str">
+        <v>kept — vendor is the subject of this settings page</v>
+      </c>
     </row>
     <row r="471">
       <c r="A471" t="str">
@@ -12657,6 +14057,9 @@
       <c r="H471" t="str">
         <v>template-text</v>
       </c>
+      <c r="I471" t="str">
+        <v>kept — vendor is the subject of this settings page</v>
+      </c>
     </row>
     <row r="472">
       <c r="A472" t="str">
@@ -12683,6 +14086,9 @@
       <c r="H472" t="str">
         <v>toast</v>
       </c>
+      <c r="I472" t="str">
+        <v>kept — vendor is the subject of this settings page</v>
+      </c>
     </row>
     <row r="473">
       <c r="A473" t="str">
@@ -12709,6 +14115,9 @@
       <c r="H473" t="str">
         <v>toast</v>
       </c>
+      <c r="I473" t="str">
+        <v>kept — vendor is the subject of this settings page</v>
+      </c>
     </row>
     <row r="474">
       <c r="A474" t="str">
@@ -12735,6 +14144,9 @@
       <c r="H474" t="str">
         <v>option</v>
       </c>
+      <c r="I474" t="str">
+        <v>kept — vendor is the subject of this settings page</v>
+      </c>
     </row>
     <row r="475">
       <c r="A475" t="str">
@@ -12761,6 +14173,9 @@
       <c r="H475" t="str">
         <v>template-text</v>
       </c>
+      <c r="I475" t="str">
+        <v>applied + tooltip: Each label batch from the shipping system becomes a wave automatically. Build a manual wav</v>
+      </c>
     </row>
     <row r="476">
       <c r="A476" t="str">
@@ -12787,6 +14202,9 @@
       <c r="H476" t="str">
         <v>option</v>
       </c>
+      <c r="I476" t="str">
+        <v>applied (no tooltip: plain string, not an element): Label batch #</v>
+      </c>
     </row>
     <row r="477">
       <c r="A477" t="str">
@@ -12813,6 +14231,9 @@
       <c r="H477" t="str">
         <v>api-error</v>
       </c>
+      <c r="I477" t="str">
+        <v/>
+      </c>
     </row>
     <row r="478">
       <c r="A478" t="str">
@@ -12839,6 +14260,9 @@
       <c r="H478" t="str">
         <v>api-error</v>
       </c>
+      <c r="I478" t="str">
+        <v/>
+      </c>
     </row>
     <row r="479">
       <c r="A479" t="str">
@@ -12865,6 +14289,9 @@
       <c r="H479" t="str">
         <v>api-error</v>
       </c>
+      <c r="I479" t="str">
+        <v/>
+      </c>
     </row>
     <row r="480">
       <c r="A480" t="str">
@@ -12891,6 +14318,9 @@
       <c r="H480" t="str">
         <v>api-error</v>
       </c>
+      <c r="I480" t="str">
+        <v/>
+      </c>
     </row>
     <row r="481">
       <c r="A481" t="str">
@@ -12917,6 +14347,9 @@
       <c r="H481" t="str">
         <v>api-error</v>
       </c>
+      <c r="I481" t="str">
+        <v/>
+      </c>
     </row>
     <row r="482">
       <c r="A482" t="str">
@@ -12943,6 +14376,9 @@
       <c r="H482" t="str">
         <v>api-error</v>
       </c>
+      <c r="I482" t="str">
+        <v/>
+      </c>
     </row>
     <row r="483">
       <c r="A483" t="str">
@@ -12969,6 +14405,9 @@
       <c r="H483" t="str">
         <v>api-error</v>
       </c>
+      <c r="I483" t="str">
+        <v/>
+      </c>
     </row>
     <row r="484">
       <c r="A484" t="str">
@@ -12995,6 +14434,9 @@
       <c r="H484" t="str">
         <v>api-error</v>
       </c>
+      <c r="I484" t="str">
+        <v/>
+      </c>
     </row>
     <row r="485">
       <c r="A485" t="str">
@@ -13021,6 +14463,9 @@
       <c r="H485" t="str">
         <v>api-error</v>
       </c>
+      <c r="I485" t="str">
+        <v/>
+      </c>
     </row>
     <row r="486">
       <c r="A486" t="str">
@@ -13047,6 +14492,9 @@
       <c r="H486" t="str">
         <v>api-error</v>
       </c>
+      <c r="I486" t="str">
+        <v/>
+      </c>
     </row>
     <row r="487">
       <c r="A487" t="str">
@@ -13073,6 +14521,9 @@
       <c r="H487" t="str">
         <v>api-error</v>
       </c>
+      <c r="I487" t="str">
+        <v/>
+      </c>
     </row>
     <row r="488">
       <c r="A488" t="str">
@@ -13099,6 +14550,9 @@
       <c r="H488" t="str">
         <v>api-error</v>
       </c>
+      <c r="I488" t="str">
+        <v/>
+      </c>
     </row>
     <row r="489">
       <c r="A489" t="str">
@@ -13125,6 +14579,9 @@
       <c r="H489" t="str">
         <v>api-error</v>
       </c>
+      <c r="I489" t="str">
+        <v/>
+      </c>
     </row>
     <row r="490">
       <c r="A490" t="str">
@@ -13151,6 +14608,9 @@
       <c r="H490" t="str">
         <v>api-error</v>
       </c>
+      <c r="I490" t="str">
+        <v/>
+      </c>
     </row>
     <row r="491">
       <c r="A491" t="str">
@@ -13177,6 +14637,9 @@
       <c r="H491" t="str">
         <v>api-error</v>
       </c>
+      <c r="I491" t="str">
+        <v/>
+      </c>
     </row>
     <row r="492">
       <c r="A492" t="str">
@@ -13203,6 +14666,9 @@
       <c r="H492" t="str">
         <v>api-error</v>
       </c>
+      <c r="I492" t="str">
+        <v/>
+      </c>
     </row>
     <row r="493">
       <c r="A493" t="str">
@@ -13229,6 +14695,9 @@
       <c r="H493" t="str">
         <v>api-error</v>
       </c>
+      <c r="I493" t="str">
+        <v/>
+      </c>
     </row>
     <row r="494">
       <c r="A494" t="str">
@@ -13255,6 +14724,9 @@
       <c r="H494" t="str">
         <v>api-error</v>
       </c>
+      <c r="I494" t="str">
+        <v/>
+      </c>
     </row>
     <row r="495">
       <c r="A495" t="str">
@@ -13281,6 +14753,9 @@
       <c r="H495" t="str">
         <v>api-error</v>
       </c>
+      <c r="I495" t="str">
+        <v/>
+      </c>
     </row>
     <row r="496">
       <c r="A496" t="str">
@@ -13307,6 +14782,9 @@
       <c r="H496" t="str">
         <v>api-error</v>
       </c>
+      <c r="I496" t="str">
+        <v/>
+      </c>
     </row>
     <row r="497">
       <c r="A497" t="str">
@@ -13333,6 +14811,9 @@
       <c r="H497" t="str">
         <v>api-error</v>
       </c>
+      <c r="I497" t="str">
+        <v/>
+      </c>
     </row>
     <row r="498">
       <c r="A498" t="str">
@@ -13359,6 +14840,9 @@
       <c r="H498" t="str">
         <v>api-error</v>
       </c>
+      <c r="I498" t="str">
+        <v/>
+      </c>
     </row>
     <row r="499">
       <c r="A499" t="str">
@@ -13385,6 +14869,9 @@
       <c r="H499" t="str">
         <v>api-error</v>
       </c>
+      <c r="I499" t="str">
+        <v/>
+      </c>
     </row>
     <row r="500">
       <c r="A500" t="str">
@@ -13411,6 +14898,9 @@
       <c r="H500" t="str">
         <v>api-error</v>
       </c>
+      <c r="I500" t="str">
+        <v/>
+      </c>
     </row>
     <row r="501">
       <c r="A501" t="str">
@@ -13437,6 +14927,9 @@
       <c r="H501" t="str">
         <v>api-error</v>
       </c>
+      <c r="I501" t="str">
+        <v/>
+      </c>
     </row>
     <row r="502">
       <c r="A502" t="str">
@@ -13463,6 +14956,9 @@
       <c r="H502" t="str">
         <v>api-error</v>
       </c>
+      <c r="I502" t="str">
+        <v/>
+      </c>
     </row>
     <row r="503">
       <c r="A503" t="str">
@@ -13489,6 +14985,9 @@
       <c r="H503" t="str">
         <v>api-error</v>
       </c>
+      <c r="I503" t="str">
+        <v/>
+      </c>
     </row>
     <row r="504">
       <c r="A504" t="str">
@@ -13515,6 +15014,9 @@
       <c r="H504" t="str">
         <v>html-text</v>
       </c>
+      <c r="I504" t="str">
+        <v/>
+      </c>
     </row>
     <row r="505">
       <c r="A505" t="str">
@@ -13541,6 +15043,9 @@
       <c r="H505" t="str">
         <v>html-text</v>
       </c>
+      <c r="I505" t="str">
+        <v/>
+      </c>
     </row>
     <row r="506">
       <c r="A506" t="str">
@@ -13550,7 +15055,7 @@
         <v>index.html:274 #submitReceiveBtn &lt;button&gt;</v>
       </c>
       <c r="C506" t="str">
-        <v>submitReceive())"&gt;Receive &amp;amp; create LPs</v>
+        <v>submitReceive())"&gt;Receive &amp; create LPs</v>
       </c>
       <c r="D506" t="str">
         <v>terminology</v>
@@ -13559,13 +15064,16 @@
         <v>Synonym in use (canonical in UI-COPY.md): LPs → license plate</v>
       </c>
       <c r="F506" t="str">
-        <v>submitReceive())"&gt;Receive &amp;amp; create license plates</v>
+        <v>submitReceive())"&gt;Receive &amp; create license plates</v>
       </c>
       <c r="G506" t="str">
         <v/>
       </c>
       <c r="H506" t="str">
         <v>html-text</v>
+      </c>
+      <c r="I506" t="str">
+        <v/>
       </c>
     </row>
     <row r="507">
@@ -13593,6 +15101,9 @@
       <c r="H507" t="str">
         <v>html-text</v>
       </c>
+      <c r="I507" t="str">
+        <v/>
+      </c>
     </row>
     <row r="508">
       <c r="A508" t="str">
@@ -13619,6 +15130,9 @@
       <c r="H508" t="str">
         <v>html-text</v>
       </c>
+      <c r="I508" t="str">
+        <v/>
+      </c>
     </row>
     <row r="509">
       <c r="A509" t="str">
@@ -13645,6 +15159,9 @@
       <c r="H509" t="str">
         <v>html-text</v>
       </c>
+      <c r="I509" t="str">
+        <v/>
+      </c>
     </row>
     <row r="510">
       <c r="A510" t="str">
@@ -13671,6 +15188,9 @@
       <c r="H510" t="str">
         <v>html-text</v>
       </c>
+      <c r="I510" t="str">
+        <v/>
+      </c>
     </row>
     <row r="511">
       <c r="A511" t="str">
@@ -13697,6 +15217,9 @@
       <c r="H511" t="str">
         <v>html-text</v>
       </c>
+      <c r="I511" t="str">
+        <v/>
+      </c>
     </row>
     <row r="512">
       <c r="A512" t="str">
@@ -13723,6 +15246,9 @@
       <c r="H512" t="str">
         <v>html-text</v>
       </c>
+      <c r="I512" t="str">
+        <v/>
+      </c>
     </row>
     <row r="513">
       <c r="A513" t="str">
@@ -13749,6 +15275,9 @@
       <c r="H513" t="str">
         <v>html-text</v>
       </c>
+      <c r="I513" t="str">
+        <v/>
+      </c>
     </row>
     <row r="514">
       <c r="A514" t="str">
@@ -13775,6 +15304,9 @@
       <c r="H514" t="str">
         <v>html-text</v>
       </c>
+      <c r="I514" t="str">
+        <v/>
+      </c>
     </row>
     <row r="515">
       <c r="A515" t="str">
@@ -13801,6 +15333,9 @@
       <c r="H515" t="str">
         <v>html-attr</v>
       </c>
+      <c r="I515" t="str">
+        <v/>
+      </c>
     </row>
     <row r="516">
       <c r="A516" t="str">
@@ -13827,6 +15362,9 @@
       <c r="H516" t="str">
         <v>html-text</v>
       </c>
+      <c r="I516" t="str">
+        <v/>
+      </c>
     </row>
     <row r="517">
       <c r="A517" t="str">
@@ -13853,6 +15391,9 @@
       <c r="H517" t="str">
         <v>html-text</v>
       </c>
+      <c r="I517" t="str">
+        <v/>
+      </c>
     </row>
     <row r="518">
       <c r="A518" t="str">
@@ -13879,6 +15420,9 @@
       <c r="H518" t="str">
         <v>html-text</v>
       </c>
+      <c r="I518" t="str">
+        <v/>
+      </c>
     </row>
     <row r="519">
       <c r="A519" t="str">
@@ -13905,6 +15449,9 @@
       <c r="H519" t="str">
         <v>html-attr</v>
       </c>
+      <c r="I519" t="str">
+        <v/>
+      </c>
     </row>
     <row r="520">
       <c r="A520" t="str">
@@ -13931,6 +15478,9 @@
       <c r="H520" t="str">
         <v>html-text</v>
       </c>
+      <c r="I520" t="str">
+        <v/>
+      </c>
     </row>
     <row r="521">
       <c r="A521" t="str">
@@ -13957,6 +15507,9 @@
       <c r="H521" t="str">
         <v>html-text</v>
       </c>
+      <c r="I521" t="str">
+        <v/>
+      </c>
     </row>
     <row r="522">
       <c r="A522" t="str">
@@ -13983,6 +15536,9 @@
       <c r="H522" t="str">
         <v>html-text</v>
       </c>
+      <c r="I522" t="str">
+        <v/>
+      </c>
     </row>
     <row r="523">
       <c r="A523" t="str">
@@ -14009,6 +15565,9 @@
       <c r="H523" t="str">
         <v>html-text</v>
       </c>
+      <c r="I523" t="str">
+        <v/>
+      </c>
     </row>
     <row r="524">
       <c r="A524" t="str">
@@ -14035,6 +15594,9 @@
       <c r="H524" t="str">
         <v>html-text</v>
       </c>
+      <c r="I524" t="str">
+        <v/>
+      </c>
     </row>
     <row r="525">
       <c r="A525" t="str">
@@ -14061,6 +15623,9 @@
       <c r="H525" t="str">
         <v>html-text</v>
       </c>
+      <c r="I525" t="str">
+        <v/>
+      </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
@@ -14087,6 +15652,9 @@
       <c r="H526" t="str">
         <v>html-text</v>
       </c>
+      <c r="I526" t="str">
+        <v/>
+      </c>
     </row>
     <row r="527">
       <c r="A527" t="str">
@@ -14113,6 +15681,9 @@
       <c r="H527" t="str">
         <v>html-attr</v>
       </c>
+      <c r="I527" t="str">
+        <v/>
+      </c>
     </row>
     <row r="528">
       <c r="A528" t="str">
@@ -14139,6 +15710,9 @@
       <c r="H528" t="str">
         <v>html-text</v>
       </c>
+      <c r="I528" t="str">
+        <v/>
+      </c>
     </row>
     <row r="529">
       <c r="A529" t="str">
@@ -14165,6 +15739,9 @@
       <c r="H529" t="str">
         <v>html-text</v>
       </c>
+      <c r="I529" t="str">
+        <v/>
+      </c>
     </row>
     <row r="530">
       <c r="A530" t="str">
@@ -14191,6 +15768,9 @@
       <c r="H530" t="str">
         <v>html-text</v>
       </c>
+      <c r="I530" t="str">
+        <v/>
+      </c>
     </row>
     <row r="531">
       <c r="A531" t="str">
@@ -14217,6 +15797,9 @@
       <c r="H531" t="str">
         <v>html-text</v>
       </c>
+      <c r="I531" t="str">
+        <v/>
+      </c>
     </row>
     <row r="532">
       <c r="A532" t="str">
@@ -14243,6 +15826,9 @@
       <c r="H532" t="str">
         <v>html-text</v>
       </c>
+      <c r="I532" t="str">
+        <v/>
+      </c>
     </row>
     <row r="533">
       <c r="A533" t="str">
@@ -14269,6 +15855,9 @@
       <c r="H533" t="str">
         <v>html-text</v>
       </c>
+      <c r="I533" t="str">
+        <v/>
+      </c>
     </row>
     <row r="534">
       <c r="A534" t="str">
@@ -14295,6 +15884,9 @@
       <c r="H534" t="str">
         <v>html-text</v>
       </c>
+      <c r="I534" t="str">
+        <v/>
+      </c>
     </row>
     <row r="535">
       <c r="A535" t="str">
@@ -14321,6 +15913,9 @@
       <c r="H535" t="str">
         <v>html-attr</v>
       </c>
+      <c r="I535" t="str">
+        <v/>
+      </c>
     </row>
     <row r="536">
       <c r="A536" t="str">
@@ -14347,6 +15942,9 @@
       <c r="H536" t="str">
         <v>template-text</v>
       </c>
+      <c r="I536" t="str">
+        <v/>
+      </c>
     </row>
     <row r="537">
       <c r="A537" t="str">
@@ -14373,6 +15971,9 @@
       <c r="H537" t="str">
         <v>option</v>
       </c>
+      <c r="I537" t="str">
+        <v/>
+      </c>
     </row>
     <row r="538">
       <c r="A538" t="str">
@@ -14399,6 +16000,9 @@
       <c r="H538" t="str">
         <v>option</v>
       </c>
+      <c r="I538" t="str">
+        <v/>
+      </c>
     </row>
     <row r="539">
       <c r="A539" t="str">
@@ -14425,6 +16029,9 @@
       <c r="H539" t="str">
         <v>template-text</v>
       </c>
+      <c r="I539" t="str">
+        <v/>
+      </c>
     </row>
     <row r="540">
       <c r="A540" t="str">
@@ -14451,6 +16058,9 @@
       <c r="H540" t="str">
         <v>template-text</v>
       </c>
+      <c r="I540" t="str">
+        <v/>
+      </c>
     </row>
     <row r="541">
       <c r="A541" t="str">
@@ -14477,6 +16087,9 @@
       <c r="H541" t="str">
         <v>template-text</v>
       </c>
+      <c r="I541" t="str">
+        <v/>
+      </c>
     </row>
     <row r="542">
       <c r="A542" t="str">
@@ -14503,6 +16116,9 @@
       <c r="H542" t="str">
         <v>template-text</v>
       </c>
+      <c r="I542" t="str">
+        <v/>
+      </c>
     </row>
     <row r="543">
       <c r="A543" t="str">
@@ -14529,6 +16145,9 @@
       <c r="H543" t="str">
         <v>option</v>
       </c>
+      <c r="I543" t="str">
+        <v/>
+      </c>
     </row>
     <row r="544">
       <c r="A544" t="str">
@@ -14555,6 +16174,9 @@
       <c r="H544" t="str">
         <v>option</v>
       </c>
+      <c r="I544" t="str">
+        <v/>
+      </c>
     </row>
     <row r="545">
       <c r="A545" t="str">
@@ -14581,6 +16203,9 @@
       <c r="H545" t="str">
         <v>option</v>
       </c>
+      <c r="I545" t="str">
+        <v/>
+      </c>
     </row>
     <row r="546">
       <c r="A546" t="str">
@@ -14607,6 +16232,9 @@
       <c r="H546" t="str">
         <v>option</v>
       </c>
+      <c r="I546" t="str">
+        <v/>
+      </c>
     </row>
     <row r="547">
       <c r="A547" t="str">
@@ -14633,6 +16261,9 @@
       <c r="H547" t="str">
         <v>toast</v>
       </c>
+      <c r="I547" t="str">
+        <v/>
+      </c>
     </row>
     <row r="548">
       <c r="A548" t="str">
@@ -14659,6 +16290,9 @@
       <c r="H548" t="str">
         <v>option</v>
       </c>
+      <c r="I548" t="str">
+        <v/>
+      </c>
     </row>
     <row r="549">
       <c r="A549" t="str">
@@ -14685,6 +16319,9 @@
       <c r="H549" t="str">
         <v>option</v>
       </c>
+      <c r="I549" t="str">
+        <v/>
+      </c>
     </row>
     <row r="550">
       <c r="A550" t="str">
@@ -14711,6 +16348,9 @@
       <c r="H550" t="str">
         <v>option</v>
       </c>
+      <c r="I550" t="str">
+        <v/>
+      </c>
     </row>
     <row r="551">
       <c r="A551" t="str">
@@ -14737,6 +16377,9 @@
       <c r="H551" t="str">
         <v>option</v>
       </c>
+      <c r="I551" t="str">
+        <v/>
+      </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
@@ -14763,6 +16406,9 @@
       <c r="H552" t="str">
         <v>option</v>
       </c>
+      <c r="I552" t="str">
+        <v/>
+      </c>
     </row>
     <row r="553">
       <c r="A553" t="str">
@@ -14789,6 +16435,9 @@
       <c r="H553" t="str">
         <v>option</v>
       </c>
+      <c r="I553" t="str">
+        <v/>
+      </c>
     </row>
     <row r="554">
       <c r="A554" t="str">
@@ -14815,6 +16464,9 @@
       <c r="H554" t="str">
         <v>option</v>
       </c>
+      <c r="I554" t="str">
+        <v/>
+      </c>
     </row>
     <row r="555">
       <c r="A555" t="str">
@@ -14841,6 +16493,9 @@
       <c r="H555" t="str">
         <v>option</v>
       </c>
+      <c r="I555" t="str">
+        <v/>
+      </c>
     </row>
     <row r="556">
       <c r="A556" t="str">
@@ -14867,6 +16522,9 @@
       <c r="H556" t="str">
         <v>template-text</v>
       </c>
+      <c r="I556" t="str">
+        <v/>
+      </c>
     </row>
     <row r="557">
       <c r="A557" t="str">
@@ -14893,6 +16551,9 @@
       <c r="H557" t="str">
         <v>template-text</v>
       </c>
+      <c r="I557" t="str">
+        <v/>
+      </c>
     </row>
     <row r="558">
       <c r="A558" t="str">
@@ -14919,6 +16580,9 @@
       <c r="H558" t="str">
         <v>template-text</v>
       </c>
+      <c r="I558" t="str">
+        <v/>
+      </c>
     </row>
     <row r="559">
       <c r="A559" t="str">
@@ -14945,6 +16609,9 @@
       <c r="H559" t="str">
         <v>template-text</v>
       </c>
+      <c r="I559" t="str">
+        <v/>
+      </c>
     </row>
     <row r="560">
       <c r="A560" t="str">
@@ -14971,6 +16638,9 @@
       <c r="H560" t="str">
         <v>template-attr</v>
       </c>
+      <c r="I560" t="str">
+        <v/>
+      </c>
     </row>
     <row r="561">
       <c r="A561" t="str">
@@ -14997,6 +16667,9 @@
       <c r="H561" t="str">
         <v>toast</v>
       </c>
+      <c r="I561" t="str">
+        <v/>
+      </c>
     </row>
     <row r="562">
       <c r="A562" t="str">
@@ -15023,6 +16696,9 @@
       <c r="H562" t="str">
         <v>toast</v>
       </c>
+      <c r="I562" t="str">
+        <v/>
+      </c>
     </row>
     <row r="563">
       <c r="A563" t="str">
@@ -15049,6 +16725,9 @@
       <c r="H563" t="str">
         <v>toast</v>
       </c>
+      <c r="I563" t="str">
+        <v/>
+      </c>
     </row>
     <row r="564">
       <c r="A564" t="str">
@@ -15075,6 +16754,9 @@
       <c r="H564" t="str">
         <v>toast</v>
       </c>
+      <c r="I564" t="str">
+        <v/>
+      </c>
     </row>
     <row r="565">
       <c r="A565" t="str">
@@ -15101,6 +16783,9 @@
       <c r="H565" t="str">
         <v>toast</v>
       </c>
+      <c r="I565" t="str">
+        <v/>
+      </c>
     </row>
     <row r="566">
       <c r="A566" t="str">
@@ -15127,6 +16812,9 @@
       <c r="H566" t="str">
         <v>empty-state</v>
       </c>
+      <c r="I566" t="str">
+        <v/>
+      </c>
     </row>
     <row r="567">
       <c r="A567" t="str">
@@ -15153,6 +16841,9 @@
       <c r="H567" t="str">
         <v>empty-state</v>
       </c>
+      <c r="I567" t="str">
+        <v/>
+      </c>
     </row>
     <row r="568">
       <c r="A568" t="str">
@@ -15179,6 +16870,9 @@
       <c r="H568" t="str">
         <v>option</v>
       </c>
+      <c r="I568" t="str">
+        <v/>
+      </c>
     </row>
     <row r="569">
       <c r="A569" t="str">
@@ -15205,6 +16899,9 @@
       <c r="H569" t="str">
         <v>option</v>
       </c>
+      <c r="I569" t="str">
+        <v/>
+      </c>
     </row>
     <row r="570">
       <c r="A570" t="str">
@@ -15231,6 +16928,9 @@
       <c r="H570" t="str">
         <v>option</v>
       </c>
+      <c r="I570" t="str">
+        <v/>
+      </c>
     </row>
     <row r="571">
       <c r="A571" t="str">
@@ -15257,6 +16957,9 @@
       <c r="H571" t="str">
         <v>option</v>
       </c>
+      <c r="I571" t="str">
+        <v/>
+      </c>
     </row>
     <row r="572">
       <c r="A572" t="str">
@@ -15283,6 +16986,9 @@
       <c r="H572" t="str">
         <v>option</v>
       </c>
+      <c r="I572" t="str">
+        <v/>
+      </c>
     </row>
     <row r="573">
       <c r="A573" t="str">
@@ -15309,6 +17015,9 @@
       <c r="H573" t="str">
         <v>option</v>
       </c>
+      <c r="I573" t="str">
+        <v/>
+      </c>
     </row>
     <row r="574">
       <c r="A574" t="str">
@@ -15335,6 +17044,9 @@
       <c r="H574" t="str">
         <v>option</v>
       </c>
+      <c r="I574" t="str">
+        <v/>
+      </c>
     </row>
     <row r="575">
       <c r="A575" t="str">
@@ -15361,6 +17073,9 @@
       <c r="H575" t="str">
         <v>option</v>
       </c>
+      <c r="I575" t="str">
+        <v/>
+      </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
@@ -15387,6 +17102,9 @@
       <c r="H576" t="str">
         <v>option</v>
       </c>
+      <c r="I576" t="str">
+        <v/>
+      </c>
     </row>
     <row r="577">
       <c r="A577" t="str">
@@ -15413,6 +17131,9 @@
       <c r="H577" t="str">
         <v>option</v>
       </c>
+      <c r="I577" t="str">
+        <v/>
+      </c>
     </row>
     <row r="578">
       <c r="A578" t="str">
@@ -15439,6 +17160,9 @@
       <c r="H578" t="str">
         <v>error-state</v>
       </c>
+      <c r="I578" t="str">
+        <v/>
+      </c>
     </row>
     <row r="579">
       <c r="A579" t="str">
@@ -15465,6 +17189,9 @@
       <c r="H579" t="str">
         <v>template-text</v>
       </c>
+      <c r="I579" t="str">
+        <v/>
+      </c>
     </row>
     <row r="580">
       <c r="A580" t="str">
@@ -15491,6 +17218,9 @@
       <c r="H580" t="str">
         <v>toast</v>
       </c>
+      <c r="I580" t="str">
+        <v/>
+      </c>
     </row>
     <row r="581">
       <c r="A581" t="str">
@@ -15517,6 +17247,9 @@
       <c r="H581" t="str">
         <v>template-attr</v>
       </c>
+      <c r="I581" t="str">
+        <v/>
+      </c>
     </row>
     <row r="582">
       <c r="A582" t="str">
@@ -15543,6 +17276,9 @@
       <c r="H582" t="str">
         <v>template-text</v>
       </c>
+      <c r="I582" t="str">
+        <v/>
+      </c>
     </row>
     <row r="583">
       <c r="A583" t="str">
@@ -15569,6 +17305,9 @@
       <c r="H583" t="str">
         <v>template-attr</v>
       </c>
+      <c r="I583" t="str">
+        <v/>
+      </c>
     </row>
     <row r="584">
       <c r="A584" t="str">
@@ -15595,6 +17334,9 @@
       <c r="H584" t="str">
         <v>template-text</v>
       </c>
+      <c r="I584" t="str">
+        <v/>
+      </c>
     </row>
     <row r="585">
       <c r="A585" t="str">
@@ -15621,6 +17363,9 @@
       <c r="H585" t="str">
         <v>template-text</v>
       </c>
+      <c r="I585" t="str">
+        <v/>
+      </c>
     </row>
     <row r="586">
       <c r="A586" t="str">
@@ -15647,6 +17392,9 @@
       <c r="H586" t="str">
         <v>template-text</v>
       </c>
+      <c r="I586" t="str">
+        <v/>
+      </c>
     </row>
     <row r="587">
       <c r="A587" t="str">
@@ -15673,6 +17421,9 @@
       <c r="H587" t="str">
         <v>template-text</v>
       </c>
+      <c r="I587" t="str">
+        <v/>
+      </c>
     </row>
     <row r="588">
       <c r="A588" t="str">
@@ -15699,6 +17450,9 @@
       <c r="H588" t="str">
         <v>template-text</v>
       </c>
+      <c r="I588" t="str">
+        <v/>
+      </c>
     </row>
     <row r="589">
       <c r="A589" t="str">
@@ -15725,6 +17479,9 @@
       <c r="H589" t="str">
         <v>template-text</v>
       </c>
+      <c r="I589" t="str">
+        <v/>
+      </c>
     </row>
     <row r="590">
       <c r="A590" t="str">
@@ -15751,6 +17508,9 @@
       <c r="H590" t="str">
         <v>template-text</v>
       </c>
+      <c r="I590" t="str">
+        <v/>
+      </c>
     </row>
     <row r="591">
       <c r="A591" t="str">
@@ -15777,6 +17537,9 @@
       <c r="H591" t="str">
         <v>template-text</v>
       </c>
+      <c r="I591" t="str">
+        <v/>
+      </c>
     </row>
     <row r="592">
       <c r="A592" t="str">
@@ -15803,6 +17566,9 @@
       <c r="H592" t="str">
         <v>template-text</v>
       </c>
+      <c r="I592" t="str">
+        <v/>
+      </c>
     </row>
     <row r="593">
       <c r="A593" t="str">
@@ -15829,6 +17595,9 @@
       <c r="H593" t="str">
         <v>template-text</v>
       </c>
+      <c r="I593" t="str">
+        <v/>
+      </c>
     </row>
     <row r="594">
       <c r="A594" t="str">
@@ -15855,6 +17624,9 @@
       <c r="H594" t="str">
         <v>toast</v>
       </c>
+      <c r="I594" t="str">
+        <v/>
+      </c>
     </row>
     <row r="595">
       <c r="A595" t="str">
@@ -15881,6 +17653,9 @@
       <c r="H595" t="str">
         <v>toast</v>
       </c>
+      <c r="I595" t="str">
+        <v/>
+      </c>
     </row>
     <row r="596">
       <c r="A596" t="str">
@@ -15907,6 +17682,9 @@
       <c r="H596" t="str">
         <v>toast</v>
       </c>
+      <c r="I596" t="str">
+        <v/>
+      </c>
     </row>
     <row r="597">
       <c r="A597" t="str">
@@ -15933,6 +17711,9 @@
       <c r="H597" t="str">
         <v>toast</v>
       </c>
+      <c r="I597" t="str">
+        <v/>
+      </c>
     </row>
     <row r="598">
       <c r="A598" t="str">
@@ -15959,6 +17740,9 @@
       <c r="H598" t="str">
         <v>empty-state</v>
       </c>
+      <c r="I598" t="str">
+        <v/>
+      </c>
     </row>
     <row r="599">
       <c r="A599" t="str">
@@ -15985,6 +17769,9 @@
       <c r="H599" t="str">
         <v>empty-state</v>
       </c>
+      <c r="I599" t="str">
+        <v/>
+      </c>
     </row>
     <row r="600">
       <c r="A600" t="str">
@@ -16011,6 +17798,9 @@
       <c r="H600" t="str">
         <v>option</v>
       </c>
+      <c r="I600" t="str">
+        <v/>
+      </c>
     </row>
     <row r="601">
       <c r="A601" t="str">
@@ -16037,6 +17827,9 @@
       <c r="H601" t="str">
         <v>option</v>
       </c>
+      <c r="I601" t="str">
+        <v/>
+      </c>
     </row>
     <row r="602">
       <c r="A602" t="str">
@@ -16063,6 +17856,9 @@
       <c r="H602" t="str">
         <v>option</v>
       </c>
+      <c r="I602" t="str">
+        <v/>
+      </c>
     </row>
     <row r="603">
       <c r="A603" t="str">
@@ -16089,6 +17885,9 @@
       <c r="H603" t="str">
         <v>option</v>
       </c>
+      <c r="I603" t="str">
+        <v/>
+      </c>
     </row>
     <row r="604">
       <c r="A604" t="str">
@@ -16115,6 +17914,9 @@
       <c r="H604" t="str">
         <v>option</v>
       </c>
+      <c r="I604" t="str">
+        <v/>
+      </c>
     </row>
     <row r="605">
       <c r="A605" t="str">
@@ -16141,6 +17943,9 @@
       <c r="H605" t="str">
         <v>option</v>
       </c>
+      <c r="I605" t="str">
+        <v/>
+      </c>
     </row>
     <row r="606">
       <c r="A606" t="str">
@@ -16167,6 +17972,9 @@
       <c r="H606" t="str">
         <v>option</v>
       </c>
+      <c r="I606" t="str">
+        <v/>
+      </c>
     </row>
     <row r="607">
       <c r="A607" t="str">
@@ -16193,6 +18001,9 @@
       <c r="H607" t="str">
         <v>option</v>
       </c>
+      <c r="I607" t="str">
+        <v/>
+      </c>
     </row>
     <row r="608">
       <c r="A608" t="str">
@@ -16219,6 +18030,9 @@
       <c r="H608" t="str">
         <v>option</v>
       </c>
+      <c r="I608" t="str">
+        <v/>
+      </c>
     </row>
     <row r="609">
       <c r="A609" t="str">
@@ -16245,6 +18059,9 @@
       <c r="H609" t="str">
         <v>option</v>
       </c>
+      <c r="I609" t="str">
+        <v/>
+      </c>
     </row>
     <row r="610">
       <c r="A610" t="str">
@@ -16271,6 +18088,9 @@
       <c r="H610" t="str">
         <v>field-error</v>
       </c>
+      <c r="I610" t="str">
+        <v/>
+      </c>
     </row>
     <row r="611">
       <c r="A611" t="str">
@@ -16297,6 +18117,9 @@
       <c r="H611" t="str">
         <v>template-text</v>
       </c>
+      <c r="I611" t="str">
+        <v/>
+      </c>
     </row>
     <row r="612">
       <c r="A612" t="str">
@@ -16323,6 +18146,9 @@
       <c r="H612" t="str">
         <v>template-text</v>
       </c>
+      <c r="I612" t="str">
+        <v/>
+      </c>
     </row>
     <row r="613">
       <c r="A613" t="str">
@@ -16349,6 +18175,9 @@
       <c r="H613" t="str">
         <v>template-text</v>
       </c>
+      <c r="I613" t="str">
+        <v/>
+      </c>
     </row>
     <row r="614">
       <c r="A614" t="str">
@@ -16375,6 +18204,9 @@
       <c r="H614" t="str">
         <v>template-attr</v>
       </c>
+      <c r="I614" t="str">
+        <v/>
+      </c>
     </row>
     <row r="615">
       <c r="A615" t="str">
@@ -16401,6 +18233,9 @@
       <c r="H615" t="str">
         <v>template-text</v>
       </c>
+      <c r="I615" t="str">
+        <v/>
+      </c>
     </row>
     <row r="616">
       <c r="A616" t="str">
@@ -16427,6 +18262,9 @@
       <c r="H616" t="str">
         <v>template-text</v>
       </c>
+      <c r="I616" t="str">
+        <v/>
+      </c>
     </row>
     <row r="617">
       <c r="A617" t="str">
@@ -16453,6 +18291,9 @@
       <c r="H617" t="str">
         <v>template-attr</v>
       </c>
+      <c r="I617" t="str">
+        <v/>
+      </c>
     </row>
     <row r="618">
       <c r="A618" t="str">
@@ -16479,6 +18320,9 @@
       <c r="H618" t="str">
         <v>template-attr</v>
       </c>
+      <c r="I618" t="str">
+        <v/>
+      </c>
     </row>
     <row r="619">
       <c r="A619" t="str">
@@ -16505,6 +18349,9 @@
       <c r="H619" t="str">
         <v>toast</v>
       </c>
+      <c r="I619" t="str">
+        <v/>
+      </c>
     </row>
     <row r="620">
       <c r="A620" t="str">
@@ -16531,6 +18378,9 @@
       <c r="H620" t="str">
         <v>empty-state</v>
       </c>
+      <c r="I620" t="str">
+        <v/>
+      </c>
     </row>
     <row r="621">
       <c r="A621" t="str">
@@ -16557,6 +18407,9 @@
       <c r="H621" t="str">
         <v>empty-state</v>
       </c>
+      <c r="I621" t="str">
+        <v/>
+      </c>
     </row>
     <row r="622">
       <c r="A622" t="str">
@@ -16583,6 +18436,9 @@
       <c r="H622" t="str">
         <v>empty-state</v>
       </c>
+      <c r="I622" t="str">
+        <v/>
+      </c>
     </row>
     <row r="623">
       <c r="A623" t="str">
@@ -16609,6 +18465,9 @@
       <c r="H623" t="str">
         <v>option</v>
       </c>
+      <c r="I623" t="str">
+        <v/>
+      </c>
     </row>
     <row r="624">
       <c r="A624" t="str">
@@ -16635,6 +18494,9 @@
       <c r="H624" t="str">
         <v>option</v>
       </c>
+      <c r="I624" t="str">
+        <v/>
+      </c>
     </row>
     <row r="625">
       <c r="A625" t="str">
@@ -16661,6 +18523,9 @@
       <c r="H625" t="str">
         <v>option</v>
       </c>
+      <c r="I625" t="str">
+        <v/>
+      </c>
     </row>
     <row r="626">
       <c r="A626" t="str">
@@ -16687,6 +18552,9 @@
       <c r="H626" t="str">
         <v>option</v>
       </c>
+      <c r="I626" t="str">
+        <v/>
+      </c>
     </row>
     <row r="627">
       <c r="A627" t="str">
@@ -16713,6 +18581,9 @@
       <c r="H627" t="str">
         <v>template-text</v>
       </c>
+      <c r="I627" t="str">
+        <v/>
+      </c>
     </row>
     <row r="628">
       <c r="A628" t="str">
@@ -16739,6 +18610,9 @@
       <c r="H628" t="str">
         <v>text</v>
       </c>
+      <c r="I628" t="str">
+        <v/>
+      </c>
     </row>
     <row r="629">
       <c r="A629" t="str">
@@ -16765,6 +18639,9 @@
       <c r="H629" t="str">
         <v>template-text</v>
       </c>
+      <c r="I629" t="str">
+        <v/>
+      </c>
     </row>
     <row r="630">
       <c r="A630" t="str">
@@ -16791,6 +18668,9 @@
       <c r="H630" t="str">
         <v>toast</v>
       </c>
+      <c r="I630" t="str">
+        <v/>
+      </c>
     </row>
     <row r="631">
       <c r="A631" t="str">
@@ -16817,6 +18697,9 @@
       <c r="H631" t="str">
         <v>toast</v>
       </c>
+      <c r="I631" t="str">
+        <v/>
+      </c>
     </row>
     <row r="632">
       <c r="A632" t="str">
@@ -16843,6 +18726,9 @@
       <c r="H632" t="str">
         <v>empty-state</v>
       </c>
+      <c r="I632" t="str">
+        <v/>
+      </c>
     </row>
     <row r="633">
       <c r="A633" t="str">
@@ -16869,6 +18755,9 @@
       <c r="H633" t="str">
         <v>option</v>
       </c>
+      <c r="I633" t="str">
+        <v/>
+      </c>
     </row>
     <row r="634">
       <c r="A634" t="str">
@@ -16895,6 +18784,9 @@
       <c r="H634" t="str">
         <v>option</v>
       </c>
+      <c r="I634" t="str">
+        <v/>
+      </c>
     </row>
     <row r="635">
       <c r="A635" t="str">
@@ -16921,6 +18813,9 @@
       <c r="H635" t="str">
         <v>option</v>
       </c>
+      <c r="I635" t="str">
+        <v/>
+      </c>
     </row>
     <row r="636">
       <c r="A636" t="str">
@@ -16947,6 +18842,9 @@
       <c r="H636" t="str">
         <v>option</v>
       </c>
+      <c r="I636" t="str">
+        <v/>
+      </c>
     </row>
     <row r="637">
       <c r="A637" t="str">
@@ -16973,6 +18871,9 @@
       <c r="H637" t="str">
         <v>option</v>
       </c>
+      <c r="I637" t="str">
+        <v/>
+      </c>
     </row>
     <row r="638">
       <c r="A638" t="str">
@@ -16999,6 +18900,9 @@
       <c r="H638" t="str">
         <v>template-text</v>
       </c>
+      <c r="I638" t="str">
+        <v/>
+      </c>
     </row>
     <row r="639">
       <c r="A639" t="str">
@@ -17025,6 +18929,9 @@
       <c r="H639" t="str">
         <v>option</v>
       </c>
+      <c r="I639" t="str">
+        <v/>
+      </c>
     </row>
     <row r="640">
       <c r="A640" t="str">
@@ -17051,6 +18958,9 @@
       <c r="H640" t="str">
         <v>option</v>
       </c>
+      <c r="I640" t="str">
+        <v/>
+      </c>
     </row>
     <row r="641">
       <c r="A641" t="str">
@@ -17077,6 +18987,9 @@
       <c r="H641" t="str">
         <v>option</v>
       </c>
+      <c r="I641" t="str">
+        <v/>
+      </c>
     </row>
     <row r="642">
       <c r="A642" t="str">
@@ -17103,6 +19016,9 @@
       <c r="H642" t="str">
         <v>option</v>
       </c>
+      <c r="I642" t="str">
+        <v/>
+      </c>
     </row>
     <row r="643">
       <c r="A643" t="str">
@@ -17129,6 +19045,9 @@
       <c r="H643" t="str">
         <v>text</v>
       </c>
+      <c r="I643" t="str">
+        <v/>
+      </c>
     </row>
     <row r="644">
       <c r="A644" t="str">
@@ -17155,6 +19074,9 @@
       <c r="H644" t="str">
         <v>text</v>
       </c>
+      <c r="I644" t="str">
+        <v/>
+      </c>
     </row>
     <row r="645">
       <c r="A645" t="str">
@@ -17181,6 +19103,9 @@
       <c r="H645" t="str">
         <v>text</v>
       </c>
+      <c r="I645" t="str">
+        <v/>
+      </c>
     </row>
     <row r="646">
       <c r="A646" t="str">
@@ -17207,6 +19132,9 @@
       <c r="H646" t="str">
         <v>text</v>
       </c>
+      <c r="I646" t="str">
+        <v/>
+      </c>
     </row>
     <row r="647">
       <c r="A647" t="str">
@@ -17233,6 +19161,9 @@
       <c r="H647" t="str">
         <v>text</v>
       </c>
+      <c r="I647" t="str">
+        <v/>
+      </c>
     </row>
     <row r="648">
       <c r="A648" t="str">
@@ -17259,6 +19190,9 @@
       <c r="H648" t="str">
         <v>option</v>
       </c>
+      <c r="I648" t="str">
+        <v/>
+      </c>
     </row>
     <row r="649">
       <c r="A649" t="str">
@@ -17285,6 +19219,9 @@
       <c r="H649" t="str">
         <v>option</v>
       </c>
+      <c r="I649" t="str">
+        <v/>
+      </c>
     </row>
     <row r="650">
       <c r="A650" t="str">
@@ -17311,6 +19248,9 @@
       <c r="H650" t="str">
         <v>option</v>
       </c>
+      <c r="I650" t="str">
+        <v/>
+      </c>
     </row>
     <row r="651">
       <c r="A651" t="str">
@@ -17337,6 +19277,9 @@
       <c r="H651" t="str">
         <v>toast</v>
       </c>
+      <c r="I651" t="str">
+        <v/>
+      </c>
     </row>
     <row r="652">
       <c r="A652" t="str">
@@ -17363,6 +19306,9 @@
       <c r="H652" t="str">
         <v>toast</v>
       </c>
+      <c r="I652" t="str">
+        <v/>
+      </c>
     </row>
     <row r="653">
       <c r="A653" t="str">
@@ -17389,6 +19335,9 @@
       <c r="H653" t="str">
         <v>api-error</v>
       </c>
+      <c r="I653" t="str">
+        <v/>
+      </c>
     </row>
     <row r="654">
       <c r="A654" t="str">
@@ -17415,6 +19364,9 @@
       <c r="H654" t="str">
         <v>api-error</v>
       </c>
+      <c r="I654" t="str">
+        <v/>
+      </c>
     </row>
     <row r="655">
       <c r="A655" t="str">
@@ -17441,6 +19393,9 @@
       <c r="H655" t="str">
         <v>api-error</v>
       </c>
+      <c r="I655" t="str">
+        <v/>
+      </c>
     </row>
     <row r="656">
       <c r="A656" t="str">
@@ -17467,6 +19422,9 @@
       <c r="H656" t="str">
         <v>api-error</v>
       </c>
+      <c r="I656" t="str">
+        <v/>
+      </c>
     </row>
     <row r="657">
       <c r="A657" t="str">
@@ -17493,6 +19451,9 @@
       <c r="H657" t="str">
         <v>api-error</v>
       </c>
+      <c r="I657" t="str">
+        <v/>
+      </c>
     </row>
     <row r="658">
       <c r="A658" t="str">
@@ -17519,6 +19480,9 @@
       <c r="H658" t="str">
         <v>api-error</v>
       </c>
+      <c r="I658" t="str">
+        <v/>
+      </c>
     </row>
     <row r="659">
       <c r="A659" t="str">
@@ -17545,6 +19509,9 @@
       <c r="H659" t="str">
         <v>api-error</v>
       </c>
+      <c r="I659" t="str">
+        <v/>
+      </c>
     </row>
     <row r="660">
       <c r="A660" t="str">
@@ -17571,6 +19538,9 @@
       <c r="H660" t="str">
         <v>api-error</v>
       </c>
+      <c r="I660" t="str">
+        <v/>
+      </c>
     </row>
     <row r="661">
       <c r="A661" t="str">
@@ -17597,6 +19567,9 @@
       <c r="H661" t="str">
         <v>api-error</v>
       </c>
+      <c r="I661" t="str">
+        <v/>
+      </c>
     </row>
     <row r="662">
       <c r="A662" t="str">
@@ -17623,6 +19596,9 @@
       <c r="H662" t="str">
         <v>api-error</v>
       </c>
+      <c r="I662" t="str">
+        <v/>
+      </c>
     </row>
     <row r="663">
       <c r="A663" t="str">
@@ -17649,6 +19625,9 @@
       <c r="H663" t="str">
         <v>api-error</v>
       </c>
+      <c r="I663" t="str">
+        <v/>
+      </c>
     </row>
     <row r="664">
       <c r="A664" t="str">
@@ -17675,6 +19654,9 @@
       <c r="H664" t="str">
         <v>api-error</v>
       </c>
+      <c r="I664" t="str">
+        <v/>
+      </c>
     </row>
     <row r="665">
       <c r="A665" t="str">
@@ -17701,6 +19683,9 @@
       <c r="H665" t="str">
         <v>api-error</v>
       </c>
+      <c r="I665" t="str">
+        <v/>
+      </c>
     </row>
     <row r="666">
       <c r="A666" t="str">
@@ -17727,6 +19712,9 @@
       <c r="H666" t="str">
         <v>api-error</v>
       </c>
+      <c r="I666" t="str">
+        <v/>
+      </c>
     </row>
     <row r="667">
       <c r="A667" t="str">
@@ -17753,6 +19741,9 @@
       <c r="H667" t="str">
         <v>api-error</v>
       </c>
+      <c r="I667" t="str">
+        <v/>
+      </c>
     </row>
     <row r="668">
       <c r="A668" t="str">
@@ -17779,6 +19770,9 @@
       <c r="H668" t="str">
         <v>api-error</v>
       </c>
+      <c r="I668" t="str">
+        <v/>
+      </c>
     </row>
     <row r="669">
       <c r="A669" t="str">
@@ -17805,6 +19799,9 @@
       <c r="H669" t="str">
         <v>api-error</v>
       </c>
+      <c r="I669" t="str">
+        <v/>
+      </c>
     </row>
     <row r="670">
       <c r="A670" t="str">
@@ -17831,6 +19828,9 @@
       <c r="H670" t="str">
         <v>html-text</v>
       </c>
+      <c r="I670" t="str">
+        <v/>
+      </c>
     </row>
     <row r="671">
       <c r="A671" t="str">
@@ -17857,6 +19857,9 @@
       <c r="H671" t="str">
         <v>html-text</v>
       </c>
+      <c r="I671" t="str">
+        <v/>
+      </c>
     </row>
     <row r="672">
       <c r="A672" t="str">
@@ -17866,7 +19869,7 @@
         <v>index.html:206 .card-title &lt;div&gt;</v>
       </c>
       <c r="C672" t="str">
-        <v>Packages &amp;amp; shipment verification</v>
+        <v>Packages &amp; shipment verification</v>
       </c>
       <c r="D672" t="str">
         <v>terminology-review</v>
@@ -17882,6 +19885,9 @@
       </c>
       <c r="H672" t="str">
         <v>html-text</v>
+      </c>
+      <c r="I672" t="str">
+        <v/>
       </c>
     </row>
     <row r="673">
@@ -17909,6 +19915,9 @@
       <c r="H673" t="str">
         <v>html-text</v>
       </c>
+      <c r="I673" t="str">
+        <v/>
+      </c>
     </row>
     <row r="674">
       <c r="A674" t="str">
@@ -17935,6 +19944,9 @@
       <c r="H674" t="str">
         <v>html-text</v>
       </c>
+      <c r="I674" t="str">
+        <v/>
+      </c>
     </row>
     <row r="675">
       <c r="A675" t="str">
@@ -17961,6 +19973,9 @@
       <c r="H675" t="str">
         <v>html-text</v>
       </c>
+      <c r="I675" t="str">
+        <v/>
+      </c>
     </row>
     <row r="676">
       <c r="A676" t="str">
@@ -17987,6 +20002,9 @@
       <c r="H676" t="str">
         <v>html-text</v>
       </c>
+      <c r="I676" t="str">
+        <v/>
+      </c>
     </row>
     <row r="677">
       <c r="A677" t="str">
@@ -18013,6 +20031,9 @@
       <c r="H677" t="str">
         <v>html-text</v>
       </c>
+      <c r="I677" t="str">
+        <v/>
+      </c>
     </row>
     <row r="678">
       <c r="A678" t="str">
@@ -18039,6 +20060,9 @@
       <c r="H678" t="str">
         <v>html-text</v>
       </c>
+      <c r="I678" t="str">
+        <v/>
+      </c>
     </row>
     <row r="679">
       <c r="A679" t="str">
@@ -18065,6 +20089,9 @@
       <c r="H679" t="str">
         <v>html-text</v>
       </c>
+      <c r="I679" t="str">
+        <v/>
+      </c>
     </row>
     <row r="680">
       <c r="A680" t="str">
@@ -18091,6 +20118,9 @@
       <c r="H680" t="str">
         <v>html-text</v>
       </c>
+      <c r="I680" t="str">
+        <v/>
+      </c>
     </row>
     <row r="681">
       <c r="A681" t="str">
@@ -18117,6 +20147,9 @@
       <c r="H681" t="str">
         <v>html-text</v>
       </c>
+      <c r="I681" t="str">
+        <v/>
+      </c>
     </row>
     <row r="682">
       <c r="A682" t="str">
@@ -18143,6 +20176,9 @@
       <c r="H682" t="str">
         <v>html-text</v>
       </c>
+      <c r="I682" t="str">
+        <v/>
+      </c>
     </row>
     <row r="683">
       <c r="A683" t="str">
@@ -18169,6 +20205,9 @@
       <c r="H683" t="str">
         <v>html-text</v>
       </c>
+      <c r="I683" t="str">
+        <v/>
+      </c>
     </row>
     <row r="684">
       <c r="A684" t="str">
@@ -18195,6 +20234,9 @@
       <c r="H684" t="str">
         <v>html-text</v>
       </c>
+      <c r="I684" t="str">
+        <v/>
+      </c>
     </row>
     <row r="685">
       <c r="A685" t="str">
@@ -18221,6 +20263,9 @@
       <c r="H685" t="str">
         <v>html-text</v>
       </c>
+      <c r="I685" t="str">
+        <v/>
+      </c>
     </row>
     <row r="686">
       <c r="A686" t="str">
@@ -18247,6 +20292,9 @@
       <c r="H686" t="str">
         <v>html-text</v>
       </c>
+      <c r="I686" t="str">
+        <v/>
+      </c>
     </row>
     <row r="687">
       <c r="A687" t="str">
@@ -18273,6 +20321,9 @@
       <c r="H687" t="str">
         <v>option</v>
       </c>
+      <c r="I687" t="str">
+        <v/>
+      </c>
     </row>
     <row r="688">
       <c r="A688" t="str">
@@ -18299,6 +20350,9 @@
       <c r="H688" t="str">
         <v>template-text</v>
       </c>
+      <c r="I688" t="str">
+        <v/>
+      </c>
     </row>
     <row r="689">
       <c r="A689" t="str">
@@ -18325,6 +20379,9 @@
       <c r="H689" t="str">
         <v>empty-state</v>
       </c>
+      <c r="I689" t="str">
+        <v/>
+      </c>
     </row>
     <row r="690">
       <c r="A690" t="str">
@@ -18351,6 +20408,9 @@
       <c r="H690" t="str">
         <v>template-text</v>
       </c>
+      <c r="I690" t="str">
+        <v/>
+      </c>
     </row>
     <row r="691">
       <c r="A691" t="str">
@@ -18377,6 +20437,9 @@
       <c r="H691" t="str">
         <v>toast</v>
       </c>
+      <c r="I691" t="str">
+        <v/>
+      </c>
     </row>
     <row r="692">
       <c r="A692" t="str">
@@ -18403,6 +20466,9 @@
       <c r="H692" t="str">
         <v>template-text</v>
       </c>
+      <c r="I692" t="str">
+        <v/>
+      </c>
     </row>
     <row r="693">
       <c r="A693" t="str">
@@ -18429,6 +20495,9 @@
       <c r="H693" t="str">
         <v>template-text</v>
       </c>
+      <c r="I693" t="str">
+        <v/>
+      </c>
     </row>
     <row r="694">
       <c r="A694" t="str">
@@ -18455,6 +20524,9 @@
       <c r="H694" t="str">
         <v>option</v>
       </c>
+      <c r="I694" t="str">
+        <v/>
+      </c>
     </row>
     <row r="695">
       <c r="A695" t="str">
@@ -18481,6 +20553,9 @@
       <c r="H695" t="str">
         <v>option</v>
       </c>
+      <c r="I695" t="str">
+        <v/>
+      </c>
     </row>
     <row r="696">
       <c r="A696" t="str">
@@ -18507,6 +20582,9 @@
       <c r="H696" t="str">
         <v>template-text</v>
       </c>
+      <c r="I696" t="str">
+        <v/>
+      </c>
     </row>
     <row r="697">
       <c r="A697" t="str">
@@ -18533,6 +20611,9 @@
       <c r="H697" t="str">
         <v>template-text</v>
       </c>
+      <c r="I697" t="str">
+        <v/>
+      </c>
     </row>
     <row r="698">
       <c r="A698" t="str">
@@ -18559,6 +20640,9 @@
       <c r="H698" t="str">
         <v>option</v>
       </c>
+      <c r="I698" t="str">
+        <v/>
+      </c>
     </row>
     <row r="699">
       <c r="A699" t="str">
@@ -18585,6 +20669,9 @@
       <c r="H699" t="str">
         <v>template-text</v>
       </c>
+      <c r="I699" t="str">
+        <v/>
+      </c>
     </row>
     <row r="700">
       <c r="A700" t="str">
@@ -18611,6 +20698,9 @@
       <c r="H700" t="str">
         <v>template-text</v>
       </c>
+      <c r="I700" t="str">
+        <v/>
+      </c>
     </row>
     <row r="701">
       <c r="A701" t="str">
@@ -18637,6 +20727,9 @@
       <c r="H701" t="str">
         <v>template-text</v>
       </c>
+      <c r="I701" t="str">
+        <v/>
+      </c>
     </row>
     <row r="702">
       <c r="A702" t="str">
@@ -18663,6 +20756,9 @@
       <c r="H702" t="str">
         <v>template-text</v>
       </c>
+      <c r="I702" t="str">
+        <v/>
+      </c>
     </row>
     <row r="703">
       <c r="A703" t="str">
@@ -18689,6 +20785,9 @@
       <c r="H703" t="str">
         <v>toast</v>
       </c>
+      <c r="I703" t="str">
+        <v/>
+      </c>
     </row>
     <row r="704">
       <c r="A704" t="str">
@@ -18715,6 +20814,9 @@
       <c r="H704" t="str">
         <v>option</v>
       </c>
+      <c r="I704" t="str">
+        <v/>
+      </c>
     </row>
     <row r="705">
       <c r="A705" t="str">
@@ -18741,6 +20843,9 @@
       <c r="H705" t="str">
         <v>option</v>
       </c>
+      <c r="I705" t="str">
+        <v/>
+      </c>
     </row>
     <row r="706">
       <c r="A706" t="str">
@@ -18767,6 +20872,9 @@
       <c r="H706" t="str">
         <v>option</v>
       </c>
+      <c r="I706" t="str">
+        <v/>
+      </c>
     </row>
     <row r="707">
       <c r="A707" t="str">
@@ -18793,6 +20901,9 @@
       <c r="H707" t="str">
         <v>option</v>
       </c>
+      <c r="I707" t="str">
+        <v/>
+      </c>
     </row>
     <row r="708">
       <c r="A708" t="str">
@@ -18819,6 +20930,9 @@
       <c r="H708" t="str">
         <v>option</v>
       </c>
+      <c r="I708" t="str">
+        <v/>
+      </c>
     </row>
     <row r="709">
       <c r="A709" t="str">
@@ -18845,6 +20959,9 @@
       <c r="H709" t="str">
         <v>template-text</v>
       </c>
+      <c r="I709" t="str">
+        <v/>
+      </c>
     </row>
     <row r="710">
       <c r="A710" t="str">
@@ -18871,6 +20988,9 @@
       <c r="H710" t="str">
         <v>option</v>
       </c>
+      <c r="I710" t="str">
+        <v/>
+      </c>
     </row>
     <row r="711">
       <c r="A711" t="str">
@@ -18897,6 +21017,9 @@
       <c r="H711" t="str">
         <v>option</v>
       </c>
+      <c r="I711" t="str">
+        <v/>
+      </c>
     </row>
     <row r="712">
       <c r="A712" t="str">
@@ -18923,6 +21046,9 @@
       <c r="H712" t="str">
         <v>empty-state</v>
       </c>
+      <c r="I712" t="str">
+        <v/>
+      </c>
     </row>
     <row r="713">
       <c r="A713" t="str">
@@ -18949,6 +21075,9 @@
       <c r="H713" t="str">
         <v>option</v>
       </c>
+      <c r="I713" t="str">
+        <v/>
+      </c>
     </row>
     <row r="714">
       <c r="A714" t="str">
@@ -18975,6 +21104,9 @@
       <c r="H714" t="str">
         <v>option</v>
       </c>
+      <c r="I714" t="str">
+        <v/>
+      </c>
     </row>
     <row r="715">
       <c r="A715" t="str">
@@ -19001,6 +21133,9 @@
       <c r="H715" t="str">
         <v>option</v>
       </c>
+      <c r="I715" t="str">
+        <v/>
+      </c>
     </row>
     <row r="716">
       <c r="A716" t="str">
@@ -19027,6 +21162,9 @@
       <c r="H716" t="str">
         <v>text</v>
       </c>
+      <c r="I716" t="str">
+        <v/>
+      </c>
     </row>
     <row r="717">
       <c r="A717" t="str">
@@ -19053,6 +21191,9 @@
       <c r="H717" t="str">
         <v>template-text</v>
       </c>
+      <c r="I717" t="str">
+        <v/>
+      </c>
     </row>
     <row r="718">
       <c r="A718" t="str">
@@ -19079,6 +21220,9 @@
       <c r="H718" t="str">
         <v>template-text</v>
       </c>
+      <c r="I718" t="str">
+        <v/>
+      </c>
     </row>
     <row r="719">
       <c r="A719" t="str">
@@ -19105,6 +21249,9 @@
       <c r="H719" t="str">
         <v>template-text</v>
       </c>
+      <c r="I719" t="str">
+        <v/>
+      </c>
     </row>
     <row r="720">
       <c r="A720" t="str">
@@ -19131,6 +21278,9 @@
       <c r="H720" t="str">
         <v>option</v>
       </c>
+      <c r="I720" t="str">
+        <v/>
+      </c>
     </row>
     <row r="721">
       <c r="A721" t="str">
@@ -19157,6 +21307,9 @@
       <c r="H721" t="str">
         <v>attr</v>
       </c>
+      <c r="I721" t="str">
+        <v/>
+      </c>
     </row>
     <row r="722">
       <c r="A722" t="str">
@@ -19183,6 +21336,9 @@
       <c r="H722" t="str">
         <v>option</v>
       </c>
+      <c r="I722" t="str">
+        <v/>
+      </c>
     </row>
     <row r="723">
       <c r="A723" t="str">
@@ -19209,6 +21365,9 @@
       <c r="H723" t="str">
         <v>template-text</v>
       </c>
+      <c r="I723" t="str">
+        <v>applied by hand: Enter your email. A link to set a new password is sent to that address. The link expires in 60 minutes.</v>
+      </c>
     </row>
     <row r="724">
       <c r="A724" t="str">
@@ -19235,10 +21394,13 @@
       <c r="H724" t="str">
         <v>option</v>
       </c>
+      <c r="I724" t="str">
+        <v>applied — same string as the row above</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H724"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I724"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -19246,13 +21408,6 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E3283"/>
-  <cols>
-    <col min="1" max="1" width="22.83203125" customWidth="1"/>
-    <col min="2" max="2" width="46.83203125" customWidth="1"/>
-    <col min="3" max="3" width="80.83203125" customWidth="1"/>
-    <col min="4" max="4" width="16.83203125" customWidth="1"/>
-    <col min="5" max="5" width="14.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -20486,7 +22641,7 @@
         <v>index.html:206 .card-title &lt;div&gt;</v>
       </c>
       <c r="C73" t="str">
-        <v>Packages &amp;amp; shipment verification</v>
+        <v>Packages &amp; shipment verification</v>
       </c>
       <c r="D73" t="str">
         <v>terminology-review</v>
@@ -20775,7 +22930,7 @@
         <v>index.html:274 #submitReceiveBtn &lt;button&gt;</v>
       </c>
       <c r="C90" t="str">
-        <v>submitReceive())"&gt;Receive &amp;amp; create LPs</v>
+        <v>submitReceive())"&gt;Receive &amp; create LPs</v>
       </c>
       <c r="D90" t="str">
         <v>terminology</v>
@@ -21030,7 +23185,7 @@
         <v>index.html:349 .ui-btn &lt;button&gt;</v>
       </c>
       <c r="C105" t="str">
-        <v>approveIntakeDoc())" id="intakeApproveBtn"&gt;Approve &amp;amp; create</v>
+        <v>approveIntakeDoc())" id="intakeApproveBtn"&gt;Approve &amp; create</v>
       </c>
       <c r="D105" t="str">
         <v>ok</v>
@@ -21251,7 +23406,7 @@
         <v>index.html:405 .floor-card-title &lt;div&gt;</v>
       </c>
       <c r="C118" t="str">
-        <v>Pack &amp;amp; Ship</v>
+        <v>Pack &amp; Ship</v>
       </c>
       <c r="D118" t="str">
         <v>ok</v>
@@ -22713,7 +24868,7 @@
         <v>index.html:847 .page-subtitle &lt;div&gt;</v>
       </c>
       <c r="C204" t="str">
-        <v>Warehouse configuration &amp;amp; reference data</v>
+        <v>Warehouse configuration &amp; reference data</v>
       </c>
       <c r="D204" t="str">
         <v>ok</v>
@@ -22883,7 +25038,7 @@
         <v>index.html:900 .card-title &lt;div&gt;</v>
       </c>
       <c r="C214" t="str">
-        <v>Roles &amp;amp; permissions</v>
+        <v>Roles &amp; permissions</v>
       </c>
       <c r="D214" t="str">
         <v>ok</v>
@@ -24362,7 +26517,7 @@
         <v>index.html:1214 &lt;div&gt;</v>
       </c>
       <c r="C301" t="str">
-        <v>&amp;lt; 75%</v>
+        <v>&lt; 75%</v>
       </c>
       <c r="D301" t="str">
         <v>ok</v>
@@ -25178,7 +27333,7 @@
         <v>index.html:1430 #pickerOvSubmitBtn &lt;button&gt;</v>
       </c>
       <c r="C349" t="str">
-        <v>⚠ Override &amp;amp; Confirm</v>
+        <v>⚠ Override &amp; Confirm</v>
       </c>
       <c r="D349" t="str">
         <v>ok</v>
@@ -28000,7 +30155,7 @@
         <v>js/clients.js:706 &lt;div&gt;</v>
       </c>
       <c r="C515" t="str">
-        <v>SLA Rules &amp;amp; Exception Fees</v>
+        <v>SLA Rules &amp; Exception Fees</v>
       </c>
       <c r="D515" t="str">
         <v>ok</v>
@@ -35497,7 +37652,7 @@
         <v>js/inventory.js:466 .ui-label &lt;div&gt;</v>
       </c>
       <c r="C956" t="str">
-        <v>Identifiers &amp;amp; pack levels</v>
+        <v>Identifiers &amp; pack levels</v>
       </c>
       <c r="D956" t="str">
         <v>ok</v>
@@ -75075,12 +77230,6 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D34"/>
-  <cols>
-    <col min="1" max="1" width="12.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="20.83203125" customWidth="1"/>
-    <col min="4" max="4" width="12.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">

--- a/docs/COPY-AUDIT.xlsx
+++ b/docs/COPY-AUDIT.xlsx
@@ -14203,7 +14203,7 @@
         <v>option</v>
       </c>
       <c r="I476" t="str">
-        <v>applied (no tooltip: plain string, not an element): Label batch #</v>
+        <v>applied: External order # (same label as the orders page)</v>
       </c>
     </row>
     <row r="477">

--- a/docs/COPY-AUDIT.xlsx
+++ b/docs/COPY-AUDIT.xlsx
@@ -515,7 +515,7 @@
         <v>html-text</v>
       </c>
       <c r="I4" t="str">
-        <v/>
+        <v>kept — product name; replaced by the tenant name after sign-in</v>
       </c>
     </row>
     <row r="5">
@@ -544,7 +544,7 @@
         <v>html-text</v>
       </c>
       <c r="I5" t="str">
-        <v/>
+        <v>applied: Upload docs</v>
       </c>
     </row>
     <row r="6">
@@ -573,7 +573,7 @@
         <v>html-text</v>
       </c>
       <c r="I6" t="str">
-        <v/>
+        <v>applied: Sign out</v>
       </c>
     </row>
     <row r="7">
@@ -602,7 +602,7 @@
         <v>html-text</v>
       </c>
       <c r="I7" t="str">
-        <v/>
+        <v>applied: Order queue</v>
       </c>
     </row>
     <row r="8">
@@ -631,7 +631,7 @@
         <v>html-text</v>
       </c>
       <c r="I8" t="str">
-        <v/>
+        <v>applied: Pick waves</v>
       </c>
     </row>
     <row r="9">
@@ -660,7 +660,7 @@
         <v>html-text</v>
       </c>
       <c r="I9" t="str">
-        <v/>
+        <v>applied: Dock schedule</v>
       </c>
     </row>
     <row r="10">
@@ -689,7 +689,7 @@
         <v>html-text</v>
       </c>
       <c r="I10" t="str">
-        <v/>
+        <v>applied: Warehouse floor</v>
       </c>
     </row>
     <row r="11">
@@ -718,7 +718,7 @@
         <v>html-text</v>
       </c>
       <c r="I11" t="str">
-        <v/>
+        <v>applied: Aa large</v>
       </c>
     </row>
     <row r="12">
@@ -747,7 +747,7 @@
         <v>html-text</v>
       </c>
       <c r="I12" t="str">
-        <v/>
+        <v>applied: Orders to pick</v>
       </c>
     </row>
     <row r="13">
@@ -776,7 +776,7 @@
         <v>html-text</v>
       </c>
       <c r="I13" t="str">
-        <v/>
+        <v>kept — caption under a number, reads as one phrase ("12 ready to pick")</v>
       </c>
     </row>
     <row r="14">
@@ -805,7 +805,7 @@
         <v>html-text</v>
       </c>
       <c r="I14" t="str">
-        <v/>
+        <v>kept — caption under a number</v>
       </c>
     </row>
     <row r="15">
@@ -834,7 +834,7 @@
         <v>html-text</v>
       </c>
       <c r="I15" t="str">
-        <v/>
+        <v>applied: Move inventory</v>
       </c>
     </row>
     <row r="16">
@@ -863,7 +863,7 @@
         <v>html-text</v>
       </c>
       <c r="I16" t="str">
-        <v/>
+        <v>applied: Place an order</v>
       </c>
     </row>
     <row r="17">
@@ -892,7 +892,7 @@
         <v>html-text</v>
       </c>
       <c r="I17" t="str">
-        <v/>
+        <v>applied: Upload documents</v>
       </c>
     </row>
     <row r="18">
@@ -921,7 +921,7 @@
         <v>html-text</v>
       </c>
       <c r="I18" t="str">
-        <v/>
+        <v>applied: Current performance</v>
       </c>
     </row>
     <row r="19">
@@ -950,7 +950,7 @@
         <v>html-text</v>
       </c>
       <c r="I19" t="str">
-        <v/>
+        <v>applied: Who can do what &amp;middot; admin only</v>
       </c>
     </row>
     <row r="20">
@@ -979,7 +979,7 @@
         <v>html-text</v>
       </c>
       <c r="I20" t="str">
-        <v/>
+        <v>applied: Billable service catalog</v>
       </c>
     </row>
     <row r="21">
@@ -1008,7 +1008,7 @@
         <v>html-text</v>
       </c>
       <c r="I21" t="str">
-        <v/>
+        <v>applied: Accrual runs</v>
       </c>
     </row>
     <row r="22">
@@ -1037,7 +1037,7 @@
         <v>html-text</v>
       </c>
       <c r="I22" t="str">
-        <v/>
+        <v>applied: Parcel quotes</v>
       </c>
     </row>
     <row r="23">
@@ -1066,7 +1066,7 @@
         <v>html-text</v>
       </c>
       <c r="I23" t="str">
-        <v/>
+        <v>applied: Total qty</v>
       </c>
     </row>
     <row r="24">
@@ -1095,7 +1095,7 @@
         <v>html-text</v>
       </c>
       <c r="I24" t="str">
-        <v/>
+        <v>applied: Received qty</v>
       </c>
     </row>
     <row r="25">
@@ -1124,7 +1124,7 @@
         <v>html-text</v>
       </c>
       <c r="I25" t="str">
-        <v/>
+        <v>applied: Received by</v>
       </c>
     </row>
     <row r="26">
@@ -1153,7 +1153,7 @@
         <v>html-text</v>
       </c>
       <c r="I26" t="str">
-        <v/>
+        <v>kept — product name (BRAND.long)</v>
       </c>
     </row>
     <row r="27">
@@ -1182,7 +1182,7 @@
         <v>html-text</v>
       </c>
       <c r="I27" t="str">
-        <v/>
+        <v>applied: Sign in</v>
       </c>
     </row>
     <row r="28">
@@ -1211,7 +1211,7 @@
         <v>html-text</v>
       </c>
       <c r="I28" t="str">
-        <v/>
+        <v>applied: Picker override settings</v>
       </c>
     </row>
     <row r="29">
@@ -1240,7 +1240,7 @@
         <v>option</v>
       </c>
       <c r="I29" t="str">
-        <v/>
+        <v>applied: Accrual runs</v>
       </c>
     </row>
     <row r="30">
@@ -1269,7 +1269,7 @@
         <v>template-text</v>
       </c>
       <c r="I30" t="str">
-        <v/>
+        <v>kept — inline after a status chip</v>
       </c>
     </row>
     <row r="31">
@@ -1298,7 +1298,7 @@
         <v>template-text</v>
       </c>
       <c r="I31" t="str">
-        <v/>
+        <v>applied: Exception charge</v>
       </c>
     </row>
     <row r="32">
@@ -1327,7 +1327,7 @@
         <v>option</v>
       </c>
       <c r="I32" t="str">
-        <v/>
+        <v>kept — document name keeps its capitals</v>
       </c>
     </row>
     <row r="33">
@@ -1356,7 +1356,7 @@
         <v>template-text</v>
       </c>
       <c r="I33" t="str">
-        <v/>
+        <v>kept — select option; options may start lower case</v>
       </c>
     </row>
     <row r="34">
@@ -1385,7 +1385,7 @@
         <v>template-text</v>
       </c>
       <c r="I34" t="str">
-        <v/>
+        <v>applied: Uploads on Save</v>
       </c>
     </row>
     <row r="35">
@@ -1414,7 +1414,7 @@
         <v>template-text</v>
       </c>
       <c r="I35" t="str">
-        <v/>
+        <v>applied: Barcodes on each handling level</v>
       </c>
     </row>
     <row r="36">
@@ -1443,7 +1443,7 @@
         <v>template-text</v>
       </c>
       <c r="I36" t="str">
-        <v/>
+        <v>kept — document name keeps its capitals (like Bill of Lading)</v>
       </c>
     </row>
     <row r="37">
@@ -1472,7 +1472,7 @@
         <v>template-text</v>
       </c>
       <c r="I37" t="str">
-        <v/>
+        <v>kept — inline continuation of the card title</v>
       </c>
     </row>
     <row r="38">
@@ -1501,7 +1501,7 @@
         <v>template-text</v>
       </c>
       <c r="I38" t="str">
-        <v/>
+        <v>kept — select option</v>
       </c>
     </row>
     <row r="39">
@@ -1530,7 +1530,7 @@
         <v>template-text</v>
       </c>
       <c r="I39" t="str">
-        <v/>
+        <v>applied: Update mapped fields</v>
       </c>
     </row>
     <row r="40">
@@ -1559,7 +1559,7 @@
         <v>template-text</v>
       </c>
       <c r="I40" t="str">
-        <v/>
+        <v>applied: Skip them</v>
       </c>
     </row>
     <row r="41">
@@ -1588,7 +1588,7 @@
         <v>template-text</v>
       </c>
       <c r="I41" t="str">
-        <v/>
+        <v>applied: Update mapped fields (blank cells leave a field unchanged)</v>
       </c>
     </row>
     <row r="42">
@@ -1617,7 +1617,7 @@
         <v>template-text</v>
       </c>
       <c r="I42" t="str">
-        <v/>
+        <v>kept — table value placeholder</v>
       </c>
     </row>
     <row r="43">
@@ -1646,7 +1646,7 @@
         <v>template-text</v>
       </c>
       <c r="I43" t="str">
-        <v/>
+        <v>kept — table value placeholder</v>
       </c>
     </row>
     <row r="44">
@@ -1675,7 +1675,7 @@
         <v>template-text</v>
       </c>
       <c r="I44" t="str">
-        <v/>
+        <v>kept — mid-sentence emphasis</v>
       </c>
     </row>
     <row r="45">
@@ -1704,7 +1704,7 @@
         <v>template-text</v>
       </c>
       <c r="I45" t="str">
-        <v/>
+        <v>kept — chip value</v>
       </c>
     </row>
     <row r="46">
@@ -1733,7 +1733,7 @@
         <v>template-text</v>
       </c>
       <c r="I46" t="str">
-        <v/>
+        <v>kept — inline meta after the package number</v>
       </c>
     </row>
     <row r="47">
@@ -1762,7 +1762,7 @@
         <v>template-text</v>
       </c>
       <c r="I47" t="str">
-        <v/>
+        <v>kept — mid-sentence emphasis</v>
       </c>
     </row>
     <row r="48">
@@ -1791,7 +1791,7 @@
         <v>field-error</v>
       </c>
       <c r="I48" t="str">
-        <v/>
+        <v>applied: Required for short</v>
       </c>
     </row>
     <row r="49">
@@ -1820,7 +1820,7 @@
         <v>template-text</v>
       </c>
       <c r="I49" t="str">
-        <v/>
+        <v>applied: License plate</v>
       </c>
     </row>
     <row r="50">
@@ -1849,7 +1849,7 @@
         <v>template-text</v>
       </c>
       <c r="I50" t="str">
-        <v/>
+        <v>applied: Exit picker</v>
       </c>
     </row>
     <row r="51">
@@ -1878,7 +1878,7 @@
         <v>template-text</v>
       </c>
       <c r="I51" t="str">
-        <v/>
+        <v>applied: No order lines</v>
       </c>
     </row>
     <row r="52">
@@ -1907,7 +1907,7 @@
         <v>template-text</v>
       </c>
       <c r="I52" t="str">
-        <v/>
+        <v>applied: Not allocated yet</v>
       </c>
     </row>
     <row r="53">
@@ -1936,7 +1936,7 @@
         <v>template-text</v>
       </c>
       <c r="I53" t="str">
-        <v/>
+        <v>applied: Allocations cancelled</v>
       </c>
     </row>
     <row r="54">
@@ -1965,7 +1965,7 @@
         <v>template-text</v>
       </c>
       <c r="I54" t="str">
-        <v/>
+        <v>applied: Waiting on allocation</v>
       </c>
     </row>
     <row r="55">
@@ -1994,7 +1994,7 @@
         <v>template-text</v>
       </c>
       <c r="I55" t="str">
-        <v/>
+        <v>applied: Unexpected state</v>
       </c>
     </row>
     <row r="56">
@@ -2023,7 +2023,7 @@
         <v>template-text</v>
       </c>
       <c r="I56" t="str">
-        <v/>
+        <v>applied: Picking complete</v>
       </c>
     </row>
     <row r="57">
@@ -2052,7 +2052,7 @@
         <v>text</v>
       </c>
       <c r="I57" t="str">
-        <v/>
+        <v>applied: Retry photo</v>
       </c>
     </row>
     <row r="58">
@@ -2081,7 +2081,7 @@
         <v>text</v>
       </c>
       <c r="I58" t="str">
-        <v/>
+        <v>applied: Retake photo</v>
       </c>
     </row>
     <row r="59">
@@ -2110,7 +2110,7 @@
         <v>text</v>
       </c>
       <c r="I59" t="str">
-        <v/>
+        <v>applied: Supervisor approval required</v>
       </c>
     </row>
     <row r="60">
@@ -2139,7 +2139,7 @@
         <v>template-text</v>
       </c>
       <c r="I60" t="str">
-        <v/>
+        <v>applied: Temporary password — must be changed at next sign-in</v>
       </c>
     </row>
     <row r="61">
@@ -2168,7 +2168,7 @@
         <v>template-text</v>
       </c>
       <c r="I61" t="str">
-        <v/>
+        <v>applied: License plate</v>
       </c>
     </row>
     <row r="62">
@@ -2197,7 +2197,7 @@
         <v>template-text</v>
       </c>
       <c r="I62" t="str">
-        <v/>
+        <v>applied: Order info</v>
       </c>
     </row>
     <row r="63">
@@ -2226,7 +2226,7 @@
         <v>template-text</v>
       </c>
       <c r="I63" t="str">
-        <v/>
+        <v>applied: Required ship date</v>
       </c>
     </row>
     <row r="64">
@@ -2255,7 +2255,7 @@
         <v>template-text</v>
       </c>
       <c r="I64" t="str">
-        <v/>
+        <v>applied: Total units</v>
       </c>
     </row>
     <row r="65">
@@ -2284,7 +2284,7 @@
         <v>template-text</v>
       </c>
       <c r="I65" t="str">
-        <v/>
+        <v>applied: Time completed</v>
       </c>
     </row>
     <row r="66">
@@ -2313,7 +2313,7 @@
         <v>template-text</v>
       </c>
       <c r="I66" t="str">
-        <v/>
+        <v>applied: Packing slip</v>
       </c>
     </row>
     <row r="67">
@@ -2342,7 +2342,7 @@
         <v>template-text</v>
       </c>
       <c r="I67" t="str">
-        <v/>
+        <v>applied: Order number</v>
       </c>
     </row>
     <row r="68">
@@ -2371,7 +2371,7 @@
         <v>template-text</v>
       </c>
       <c r="I68" t="str">
-        <v/>
+        <v>applied: Order date</v>
       </c>
     </row>
     <row r="69">
@@ -2400,7 +2400,7 @@
         <v>template-text</v>
       </c>
       <c r="I69" t="str">
-        <v/>
+        <v>applied: Ship date</v>
       </c>
     </row>
     <row r="70">
@@ -2429,7 +2429,7 @@
         <v>template-text</v>
       </c>
       <c r="I70" t="str">
-        <v/>
+        <v>applied: Ship from</v>
       </c>
     </row>
     <row r="71">
@@ -2458,7 +2458,7 @@
         <v>template-text</v>
       </c>
       <c r="I71" t="str">
-        <v/>
+        <v>applied: Total lines</v>
       </c>
     </row>
     <row r="72">
@@ -2487,7 +2487,7 @@
         <v>text</v>
       </c>
       <c r="I72" t="str">
-        <v/>
+        <v>applied: Item history</v>
       </c>
     </row>
     <row r="73">
@@ -2516,7 +2516,7 @@
         <v>template-text</v>
       </c>
       <c r="I73" t="str">
-        <v/>
+        <v>kept — inline continuation after the box name</v>
       </c>
     </row>
     <row r="74">
@@ -2545,7 +2545,7 @@
         <v>option</v>
       </c>
       <c r="I74" t="str">
-        <v/>
+        <v>applied: Accrual runs</v>
       </c>
     </row>
     <row r="75">
@@ -11361,7 +11361,7 @@
         <v>toast</v>
       </c>
       <c r="I378" t="str">
-        <v/>
+        <v>skipped — code fragment mis-extracted; the visible words in it are covered by their own rows</v>
       </c>
     </row>
     <row r="379">
@@ -11390,7 +11390,7 @@
         <v>template-text</v>
       </c>
       <c r="I379" t="str">
-        <v/>
+        <v>kept — meta line</v>
       </c>
     </row>
     <row r="380">
@@ -11419,7 +11419,7 @@
         <v>toast</v>
       </c>
       <c r="I380" t="str">
-        <v/>
+        <v>applied: ${done} accepted, ${failed.length} failed: ${failed.join(', ')}. Review them individually.</v>
       </c>
     </row>
     <row r="381">
@@ -11448,7 +11448,7 @@
         <v>text</v>
       </c>
       <c r="I381" t="str">
-        <v/>
+        <v>kept — meta line, not an error</v>
       </c>
     </row>
     <row r="382">
@@ -11477,7 +11477,7 @@
         <v>option</v>
       </c>
       <c r="I382" t="str">
-        <v/>
+        <v>kept — tile caption</v>
       </c>
     </row>
     <row r="383">
@@ -11506,7 +11506,7 @@
         <v>option</v>
       </c>
       <c r="I383" t="str">
-        <v/>
+        <v>kept — status value</v>
       </c>
     </row>
     <row r="384">
@@ -11535,7 +11535,7 @@
         <v>template-text</v>
       </c>
       <c r="I384" t="str">
-        <v/>
+        <v>skipped — code fragment mis-extracted; the visible words in it are covered by their own rows</v>
       </c>
     </row>
     <row r="385">
@@ -11564,7 +11564,7 @@
         <v>template-text</v>
       </c>
       <c r="I385" t="str">
-        <v/>
+        <v>skipped — code fragment mis-extracted; the visible words in it are covered by their own rows</v>
       </c>
     </row>
     <row r="386">
@@ -11593,7 +11593,7 @@
         <v>option</v>
       </c>
       <c r="I386" t="str">
-        <v/>
+        <v>kept — status value</v>
       </c>
     </row>
     <row r="387">
@@ -11622,7 +11622,7 @@
         <v>option</v>
       </c>
       <c r="I387" t="str">
-        <v/>
+        <v>skipped — code fragment mis-extracted; the visible words in it are covered by their own rows</v>
       </c>
     </row>
     <row r="388">
@@ -11651,7 +11651,7 @@
         <v>toast</v>
       </c>
       <c r="I388" t="str">
-        <v/>
+        <v>applied: ${line?.sku_code || 'Line'}: cannot allocate ${q}. Only ${inv[j].available_qty} available.</v>
       </c>
     </row>
     <row r="389">
@@ -11680,7 +11680,7 @@
         <v>toast</v>
       </c>
       <c r="I389" t="str">
-        <v/>
+        <v>kept — names the order and carries the server's reason</v>
       </c>
     </row>
     <row r="390">
@@ -11709,7 +11709,7 @@
         <v>toast</v>
       </c>
       <c r="I390" t="str">
-        <v/>
+        <v>applied: ${f.name} — network error. Check the connection and try again.</v>
       </c>
     </row>
     <row r="391">
@@ -11738,7 +11738,7 @@
         <v>option</v>
       </c>
       <c r="I391" t="str">
-        <v/>
+        <v>skipped — code fragment mis-extracted; the visible words in it are covered by their own rows</v>
       </c>
     </row>
     <row r="392">
@@ -11767,7 +11767,7 @@
         <v>option</v>
       </c>
       <c r="I392" t="str">
-        <v/>
+        <v>skipped — code fragment mis-extracted; the visible words in it are covered by their own rows</v>
       </c>
     </row>
     <row r="393">
@@ -11796,7 +11796,7 @@
         <v>text</v>
       </c>
       <c r="I393" t="str">
-        <v/>
+        <v>applied: ⚠ Approval required</v>
       </c>
     </row>
     <row r="394">
@@ -11825,7 +11825,7 @@
         <v>toast</v>
       </c>
       <c r="I394" t="str">
-        <v/>
+        <v>applied: ${file.name} did not upload — network error. Try again.</v>
       </c>
     </row>
     <row r="395">
@@ -11854,7 +11854,7 @@
         <v>template-text</v>
       </c>
       <c r="I395" t="str">
-        <v/>
+        <v>kept — print document, regulatory wording</v>
       </c>
     </row>
     <row r="396">
@@ -11883,7 +11883,7 @@
         <v>toast</v>
       </c>
       <c r="I396" t="str">
-        <v/>
+        <v>applied: Enter a value for ${missing.map(m =&gt; m.label).join(' and ')}.</v>
       </c>
     </row>
     <row r="397">
@@ -11912,7 +11912,7 @@
         <v>template-text</v>
       </c>
       <c r="I397" t="str">
-        <v/>
+        <v>skipped — code fragment mis-extracted; the visible words in it are covered by their own rows</v>
       </c>
     </row>
     <row r="398">
@@ -11941,7 +11941,7 @@
         <v>template-text</v>
       </c>
       <c r="I398" t="str">
-        <v/>
+        <v>skipped — code fragment mis-extracted; the visible words in it are covered by their own rows</v>
       </c>
     </row>
     <row r="399">
@@ -11970,7 +11970,7 @@
         <v>template-text</v>
       </c>
       <c r="I399" t="str">
-        <v/>
+        <v>applied: Errors: ${esc(last.counts.errors)}</v>
       </c>
     </row>
     <row r="400">
@@ -11999,7 +11999,7 @@
         <v>option</v>
       </c>
       <c r="I400" t="str">
-        <v/>
+        <v>kept — status value</v>
       </c>
     </row>
     <row r="401">
@@ -14232,7 +14232,7 @@
         <v>api-error</v>
       </c>
       <c r="I477" t="str">
-        <v/>
+        <v>applied: Item not found.</v>
       </c>
     </row>
     <row r="478">
@@ -14261,7 +14261,7 @@
         <v>api-error</v>
       </c>
       <c r="I478" t="str">
-        <v/>
+        <v>applied: Item not found.</v>
       </c>
     </row>
     <row r="479">
@@ -14290,7 +14290,7 @@
         <v>api-error</v>
       </c>
       <c r="I479" t="str">
-        <v/>
+        <v>applied: SKU code "${skuCode}" already exists for this client.</v>
       </c>
     </row>
     <row r="480">
@@ -14319,7 +14319,7 @@
         <v>api-error</v>
       </c>
       <c r="I480" t="str">
-        <v/>
+        <v>applied: Item not found.</v>
       </c>
     </row>
     <row r="481">
@@ -14348,7 +14348,7 @@
         <v>api-error</v>
       </c>
       <c r="I481" t="str">
-        <v/>
+        <v>applied: Receipt not found.</v>
       </c>
     </row>
     <row r="482">
@@ -14377,7 +14377,7 @@
         <v>api-error</v>
       </c>
       <c r="I482" t="str">
-        <v/>
+        <v>applied: Receipt not found or already being received.</v>
       </c>
     </row>
     <row r="483">
@@ -14406,7 +14406,7 @@
         <v>api-error</v>
       </c>
       <c r="I483" t="str">
-        <v/>
+        <v>applied: Receipt not found.</v>
       </c>
     </row>
     <row r="484">
@@ -14435,7 +14435,7 @@
         <v>api-error</v>
       </c>
       <c r="I484" t="str">
-        <v/>
+        <v>applied: Receipt is closed or cancelled.</v>
       </c>
     </row>
     <row r="485">
@@ -14464,7 +14464,7 @@
         <v>api-error</v>
       </c>
       <c r="I485" t="str">
-        <v/>
+        <v>applied: Receipt line ${line.poLineId} not found.</v>
       </c>
     </row>
     <row r="486">
@@ -14493,7 +14493,7 @@
         <v>api-error</v>
       </c>
       <c r="I486" t="str">
-        <v/>
+        <v>applied: Receipt not found or not in receiving status.</v>
       </c>
     </row>
     <row r="487">
@@ -14522,7 +14522,7 @@
         <v>api-error</v>
       </c>
       <c r="I487" t="str">
-        <v/>
+        <v>applied: Unknown SKU code(s) for this client: ${missing.join(', ')}. Create the item(s) first or ed</v>
       </c>
     </row>
     <row r="488">
@@ -14551,7 +14551,7 @@
         <v>api-error</v>
       </c>
       <c r="I488" t="str">
-        <v/>
+        <v>applied: Item not found.</v>
       </c>
     </row>
     <row r="489">
@@ -14580,7 +14580,7 @@
         <v>api-error</v>
       </c>
       <c r="I489" t="str">
-        <v/>
+        <v>applied: Item ${caseSku.sku_code} is not a CASE type (type: ${caseSku.sku_type}).</v>
       </c>
     </row>
     <row r="490">
@@ -14609,7 +14609,7 @@
         <v>api-error</v>
       </c>
       <c r="I490" t="str">
-        <v/>
+        <v>applied: No EACH child item found for case ${caseSku.sku_code}.</v>
       </c>
     </row>
     <row r="491">
@@ -14638,7 +14638,7 @@
         <v>api-error</v>
       </c>
       <c r="I491" t="str">
-        <v/>
+        <v>applied: License plate ${caseLp.lp_number} only has ${caseLp.quantity} cases, requested ${caseQuant</v>
       </c>
     </row>
     <row r="492">
@@ -14667,7 +14667,7 @@
         <v>api-error</v>
       </c>
       <c r="I492" t="str">
-        <v/>
+        <v>applied: The license-plate occupancy unit must be one of: ${LP_UNITS.join('/')} (the measure within</v>
       </c>
     </row>
     <row r="493">
@@ -14696,7 +14696,7 @@
         <v>api-error</v>
       </c>
       <c r="I493" t="str">
-        <v/>
+        <v>applied: Item not found.</v>
       </c>
     </row>
     <row r="494">
@@ -14725,7 +14725,7 @@
         <v>api-error</v>
       </c>
       <c r="I494" t="str">
-        <v/>
+        <v xml:space="preserve">applied: Cannot withdraw — ${applied.rows[0].n} field(s) from this extraction were already applied </v>
       </c>
     </row>
     <row r="495">
@@ -14754,7 +14754,7 @@
         <v>api-error</v>
       </c>
       <c r="I495" t="str">
-        <v/>
+        <v>applied: Item not found.</v>
       </c>
     </row>
     <row r="496">
@@ -14783,7 +14783,7 @@
         <v>api-error</v>
       </c>
       <c r="I496" t="str">
-        <v/>
+        <v>kept — already follows the guide</v>
       </c>
     </row>
     <row r="497">
@@ -14812,7 +14812,7 @@
         <v>api-error</v>
       </c>
       <c r="I497" t="str">
-        <v/>
+        <v>applied: Item not found.</v>
       </c>
     </row>
     <row r="498">
@@ -14841,7 +14841,7 @@
         <v>api-error</v>
       </c>
       <c r="I498" t="str">
-        <v/>
+        <v>kept — already follows the guide</v>
       </c>
     </row>
     <row r="499">
@@ -14870,7 +14870,7 @@
         <v>api-error</v>
       </c>
       <c r="I499" t="str">
-        <v/>
+        <v>applied: Item ${skuId} not found.</v>
       </c>
     </row>
     <row r="500">
@@ -14899,7 +14899,7 @@
         <v>api-error</v>
       </c>
       <c r="I500" t="str">
-        <v/>
+        <v>applied: Destination license plate not found.</v>
       </c>
     </row>
     <row r="501">
@@ -14928,7 +14928,7 @@
         <v>api-error</v>
       </c>
       <c r="I501" t="str">
-        <v/>
+        <v>applied: That license plate belongs to another client.</v>
       </c>
     </row>
     <row r="502">
@@ -14957,7 +14957,7 @@
         <v>api-error</v>
       </c>
       <c r="I502" t="str">
-        <v/>
+        <v>applied: Unit ${unit.uid} is already on that license plate / location.</v>
       </c>
     </row>
     <row r="503">
@@ -14986,7 +14986,7 @@
         <v>api-error</v>
       </c>
       <c r="I503" t="str">
-        <v/>
+        <v>applied: License plate not found.</v>
       </c>
     </row>
     <row r="504">
@@ -15015,7 +15015,7 @@
         <v>html-text</v>
       </c>
       <c r="I504" t="str">
-        <v/>
+        <v>applied: Receipt lines</v>
       </c>
     </row>
     <row r="505">
@@ -15044,7 +15044,7 @@
         <v>html-text</v>
       </c>
       <c r="I505" t="str">
-        <v/>
+        <v>applied: Assigns a license plate and a location to each line</v>
       </c>
     </row>
     <row r="506">
@@ -15073,7 +15073,7 @@
         <v>html-text</v>
       </c>
       <c r="I506" t="str">
-        <v/>
+        <v>applied by hand: Receive and create license plates</v>
       </c>
     </row>
     <row r="507">
@@ -15102,7 +15102,7 @@
         <v>html-text</v>
       </c>
       <c r="I507" t="str">
-        <v/>
+        <v>applied: Complete receipt</v>
       </c>
     </row>
     <row r="508">
@@ -15131,7 +15131,7 @@
         <v>html-text</v>
       </c>
       <c r="I508" t="str">
-        <v/>
+        <v>kept — PO here is the client's purchase order document being uploaded</v>
       </c>
     </row>
     <row r="509">
@@ -15160,7 +15160,7 @@
         <v>html-text</v>
       </c>
       <c r="I509" t="str">
-        <v/>
+        <v>kept — the client's purchase order document</v>
       </c>
     </row>
     <row r="510">
@@ -15189,7 +15189,7 @@
         <v>html-text</v>
       </c>
       <c r="I510" t="str">
-        <v/>
+        <v>applied: Move a license plate between locations</v>
       </c>
     </row>
     <row r="511">
@@ -15218,7 +15218,7 @@
         <v>html-text</v>
       </c>
       <c r="I511" t="str">
-        <v/>
+        <v>kept — physical pallet</v>
       </c>
     </row>
     <row r="512">
@@ -15247,7 +15247,7 @@
         <v>html-text</v>
       </c>
       <c r="I512" t="str">
-        <v/>
+        <v>human — "customer POs" on an order: the ship-to customer's PO or the client's? Left as is</v>
       </c>
     </row>
     <row r="513">
@@ -15276,7 +15276,7 @@
         <v>html-text</v>
       </c>
       <c r="I513" t="str">
-        <v/>
+        <v>applied: Drop a PDF — our AI extracts the data and our ops team reviews it and creates the order or</v>
       </c>
     </row>
     <row r="514">
@@ -15305,7 +15305,7 @@
         <v>html-text</v>
       </c>
       <c r="I514" t="str">
-        <v/>
+        <v>kept — the client's purchase order document</v>
       </c>
     </row>
     <row r="515">
@@ -15334,7 +15334,7 @@
         <v>html-attr</v>
       </c>
       <c r="I515" t="str">
-        <v/>
+        <v>applied: Search item, UPC or name…</v>
       </c>
     </row>
     <row r="516">
@@ -15363,7 +15363,7 @@
         <v>html-text</v>
       </c>
       <c r="I516" t="str">
-        <v/>
+        <v>applied: search item or lot · click a row to follow license plates</v>
       </c>
     </row>
     <row r="517">
@@ -15392,7 +15392,7 @@
         <v>html-text</v>
       </c>
       <c r="I517" t="str">
-        <v/>
+        <v>kept — "SKU" allowed as the code label</v>
       </c>
     </row>
     <row r="518">
@@ -15421,7 +15421,7 @@
         <v>html-text</v>
       </c>
       <c r="I518" t="str">
-        <v/>
+        <v>applied: License plate trace</v>
       </c>
     </row>
     <row r="519">
@@ -15450,7 +15450,7 @@
         <v>html-attr</v>
       </c>
       <c r="I519" t="str">
-        <v/>
+        <v>applied: Look up a specific license plate…</v>
       </c>
     </row>
     <row r="520">
@@ -15479,7 +15479,7 @@
         <v>html-text</v>
       </c>
       <c r="I520" t="str">
-        <v/>
+        <v>applied: Trace license plate</v>
       </c>
     </row>
     <row r="521">
@@ -15508,7 +15508,7 @@
         <v>html-text</v>
       </c>
       <c r="I521" t="str">
-        <v/>
+        <v>applied: License plate family</v>
       </c>
     </row>
     <row r="522">
@@ -15537,7 +15537,7 @@
         <v>html-text</v>
       </c>
       <c r="I522" t="str">
-        <v/>
+        <v>applied: License plate family</v>
       </c>
     </row>
     <row r="523">
@@ -15566,7 +15566,7 @@
         <v>html-text</v>
       </c>
       <c r="I523" t="str">
-        <v/>
+        <v>kept — LP allowed in column headers</v>
       </c>
     </row>
     <row r="524">
@@ -15595,7 +15595,7 @@
         <v>html-text</v>
       </c>
       <c r="I524" t="str">
-        <v/>
+        <v>applied: Item</v>
       </c>
     </row>
     <row r="525">
@@ -15624,7 +15624,7 @@
         <v>html-text</v>
       </c>
       <c r="I525" t="str">
-        <v/>
+        <v>applied: Receipt for every original license plate in the family</v>
       </c>
     </row>
     <row r="526">
@@ -15653,7 +15653,7 @@
         <v>html-text</v>
       </c>
       <c r="I526" t="str">
-        <v/>
+        <v>applied: Receipt #</v>
       </c>
     </row>
     <row r="527">
@@ -15682,7 +15682,7 @@
         <v>html-attr</v>
       </c>
       <c r="I527" t="str">
-        <v/>
+        <v>kept — "SKU code" is the code label</v>
       </c>
     </row>
     <row r="528">
@@ -15711,7 +15711,7 @@
         <v>html-text</v>
       </c>
       <c r="I528" t="str">
-        <v/>
+        <v>applied by hand: … applied to the item master (every remaining "SKU master" in the dashboard was changed the same way)</v>
       </c>
     </row>
     <row r="529">
@@ -15740,7 +15740,7 @@
         <v>html-text</v>
       </c>
       <c r="I529" t="str">
-        <v/>
+        <v>applied: Create item</v>
       </c>
     </row>
     <row r="530">
@@ -15769,7 +15769,7 @@
         <v>html-text</v>
       </c>
       <c r="I530" t="str">
-        <v/>
+        <v>applied: Item not found for this client. Create it now to continue.</v>
       </c>
     </row>
     <row r="531">
@@ -15798,7 +15798,7 @@
         <v>html-text</v>
       </c>
       <c r="I531" t="str">
-        <v/>
+        <v>applied: SKU code *</v>
       </c>
     </row>
     <row r="532">
@@ -15827,7 +15827,7 @@
         <v>html-text</v>
       </c>
       <c r="I532" t="str">
-        <v/>
+        <v>applied: Create item</v>
       </c>
     </row>
     <row r="533">
@@ -15856,7 +15856,7 @@
         <v>html-text</v>
       </c>
       <c r="I533" t="str">
-        <v/>
+        <v>kept — "product" here is the physical goods, not the item record</v>
       </c>
     </row>
     <row r="534">
@@ -15885,7 +15885,7 @@
         <v>html-text</v>
       </c>
       <c r="I534" t="str">
-        <v/>
+        <v>applied: Spelling/typo in item master matched the product</v>
       </c>
     </row>
     <row r="535">
@@ -15914,7 +15914,7 @@
         <v>html-attr</v>
       </c>
       <c r="I535" t="str">
-        <v/>
+        <v>applied: e.g. The label says PROPANE but the item master is misspelled PROPAINE — same product.</v>
       </c>
     </row>
     <row r="536">
@@ -15943,7 +15943,7 @@
         <v>template-text</v>
       </c>
       <c r="I536" t="str">
-        <v/>
+        <v xml:space="preserve">applied: ⚠ Unbilled occupancies — ${esc(sum.unpriced_count)} license plate(s) occupy space with NO </v>
       </c>
     </row>
     <row r="537">
@@ -15972,7 +15972,7 @@
         <v>option</v>
       </c>
       <c r="I537" t="str">
-        <v/>
+        <v>applied: Ageless license plates</v>
       </c>
     </row>
     <row r="538">
@@ -16001,7 +16001,7 @@
         <v>option</v>
       </c>
       <c r="I538" t="str">
-        <v/>
+        <v>kept — LP allowed in column headers</v>
       </c>
     </row>
     <row r="539">
@@ -16030,7 +16030,7 @@
         <v>template-text</v>
       </c>
       <c r="I539" t="str">
-        <v/>
+        <v>applied: Per-item hazmat fields (UN #, hazard class, packing group, ground-only) are set on each it</v>
       </c>
     </row>
     <row r="540">
@@ -16059,7 +16059,7 @@
         <v>template-text</v>
       </c>
       <c r="I540" t="str">
-        <v/>
+        <v>skipped — code fragment mis-extracted; the visible words in it are covered by their own rows</v>
       </c>
     </row>
     <row r="541">
@@ -16088,7 +16088,7 @@
         <v>template-text</v>
       </c>
       <c r="I541" t="str">
-        <v/>
+        <v>applied: Items ship as-is by default (each item can override)</v>
       </c>
     </row>
     <row r="542">
@@ -16117,7 +16117,7 @@
         <v>template-text</v>
       </c>
       <c r="I542" t="str">
-        <v/>
+        <v>applied: Allow carton confirm (scan a license plate to count its units)</v>
       </c>
     </row>
     <row r="543">
@@ -16146,7 +16146,7 @@
         <v>option</v>
       </c>
       <c r="I543" t="str">
-        <v/>
+        <v>applied: Detailed — one line per license plate</v>
       </c>
     </row>
     <row r="544">
@@ -16175,7 +16175,7 @@
         <v>option</v>
       </c>
       <c r="I544" t="str">
-        <v/>
+        <v>applied: In tap mode every unit or carton scan is still checked against the location it is recorded</v>
       </c>
     </row>
     <row r="545">
@@ -16204,7 +16204,7 @@
         <v>option</v>
       </c>
       <c r="I545" t="str">
-        <v/>
+        <v>applied: Every item under &lt;strong&gt;${esc(_currentClient.name || code)}&lt;/strong&gt;</v>
       </c>
     </row>
     <row r="546">
@@ -16233,7 +16233,7 @@
         <v>option</v>
       </c>
       <c r="I546" t="str">
-        <v/>
+        <v>applied: Item</v>
       </c>
     </row>
     <row r="547">
@@ -16262,7 +16262,7 @@
         <v>toast</v>
       </c>
       <c r="I547" t="str">
-        <v/>
+        <v>applied: ${done} field(s) accepted and written to the item master</v>
       </c>
     </row>
     <row r="548">
@@ -16291,7 +16291,7 @@
         <v>option</v>
       </c>
       <c r="I548" t="str">
-        <v/>
+        <v>applied: Item</v>
       </c>
     </row>
     <row r="549">
@@ -16320,7 +16320,7 @@
         <v>option</v>
       </c>
       <c r="I549" t="str">
-        <v/>
+        <v>skipped — code fragment mis-extracted; the visible words in it are covered by their own rows</v>
       </c>
     </row>
     <row r="550">
@@ -16349,7 +16349,7 @@
         <v>option</v>
       </c>
       <c r="I550" t="str">
-        <v/>
+        <v>kept — physical goods</v>
       </c>
     </row>
     <row r="551">
@@ -16378,7 +16378,7 @@
         <v>option</v>
       </c>
       <c r="I551" t="str">
-        <v/>
+        <v>applied: This overrides the extraction and is written to the item master.</v>
       </c>
     </row>
     <row r="552">
@@ -16407,7 +16407,7 @@
         <v>option</v>
       </c>
       <c r="I552" t="str">
-        <v/>
+        <v>applied: These scored ≥95% and are written straight to the item master:&lt;br&gt;&lt;br&gt;</v>
       </c>
     </row>
     <row r="553">
@@ -16436,7 +16436,7 @@
         <v>option</v>
       </c>
       <c r="I553" t="str">
-        <v/>
+        <v>applied: Total items</v>
       </c>
     </row>
     <row r="554">
@@ -16465,7 +16465,7 @@
         <v>option</v>
       </c>
       <c r="I554" t="str">
-        <v/>
+        <v>applied: License plates</v>
       </c>
     </row>
     <row r="555">
@@ -16494,7 +16494,7 @@
         <v>option</v>
       </c>
       <c r="I555" t="str">
-        <v/>
+        <v>applied: Item</v>
       </c>
     </row>
     <row r="556">
@@ -16523,7 +16523,7 @@
         <v>template-text</v>
       </c>
       <c r="I556" t="str">
-        <v/>
+        <v>applied: Full receive flow (tap a receipt → scan license plate / quantity / location) is coming nex</v>
       </c>
     </row>
     <row r="557">
@@ -16552,7 +16552,7 @@
         <v>template-text</v>
       </c>
       <c r="I557" t="str">
-        <v/>
+        <v>applied: Scan a license plate, scan a destination location, tap Move. Updates location on the licen</v>
       </c>
     </row>
     <row r="558">
@@ -16581,7 +16581,7 @@
         <v>template-text</v>
       </c>
       <c r="I558" t="str">
-        <v/>
+        <v>applied: New receipt</v>
       </c>
     </row>
     <row r="559">
@@ -16610,7 +16610,7 @@
         <v>template-text</v>
       </c>
       <c r="I559" t="str">
-        <v/>
+        <v>applied: Receipt lines</v>
       </c>
     </row>
     <row r="560">
@@ -16639,7 +16639,7 @@
         <v>template-attr</v>
       </c>
       <c r="I560" t="str">
-        <v/>
+        <v>applied: Search items…</v>
       </c>
     </row>
     <row r="561">
@@ -16668,7 +16668,7 @@
         <v>toast</v>
       </c>
       <c r="I561" t="str">
-        <v/>
+        <v>applied: Could not load that receipt</v>
       </c>
     </row>
     <row r="562">
@@ -16697,7 +16697,7 @@
         <v>toast</v>
       </c>
       <c r="I562" t="str">
-        <v/>
+        <v>applied: Receipt ${d.status} — ${d.total_received} of ${d.total_expected} received</v>
       </c>
     </row>
     <row r="563">
@@ -16726,7 +16726,7 @@
         <v>toast</v>
       </c>
       <c r="I563" t="str">
-        <v/>
+        <v>applied: Network error — the receipt was not completed</v>
       </c>
     </row>
     <row r="564">
@@ -16755,7 +16755,7 @@
         <v>toast</v>
       </c>
       <c r="I564" t="str">
-        <v/>
+        <v>applied: ${code} is already on this receipt</v>
       </c>
     </row>
     <row r="565">
@@ -16784,7 +16784,7 @@
         <v>toast</v>
       </c>
       <c r="I565" t="str">
-        <v/>
+        <v>applied: Network error — the receipt was not created</v>
       </c>
     </row>
     <row r="566">
@@ -16813,7 +16813,7 @@
         <v>empty-state</v>
       </c>
       <c r="I566" t="str">
-        <v/>
+        <v>applied: Every line is fully received — complete the receipt.</v>
       </c>
     </row>
     <row r="567">
@@ -16842,7 +16842,7 @@
         <v>empty-state</v>
       </c>
       <c r="I567" t="str">
-        <v/>
+        <v>applied: Pick a client first — items are scoped to the client.</v>
       </c>
     </row>
     <row r="568">
@@ -16871,7 +16871,7 @@
         <v>option</v>
       </c>
       <c r="I568" t="str">
-        <v/>
+        <v>applied: Client PO</v>
       </c>
     </row>
     <row r="569">
@@ -16900,7 +16900,7 @@
         <v>option</v>
       </c>
       <c r="I569" t="str">
-        <v/>
+        <v>applied: Search receipt #, client PO or supplier…</v>
       </c>
     </row>
     <row r="570">
@@ -16929,7 +16929,7 @@
         <v>option</v>
       </c>
       <c r="I570" t="str">
-        <v/>
+        <v>applied: Item</v>
       </c>
     </row>
     <row r="571">
@@ -16958,7 +16958,7 @@
         <v>option</v>
       </c>
       <c r="I571" t="str">
-        <v/>
+        <v>kept — LP allowed in column headers</v>
       </c>
     </row>
     <row r="572">
@@ -16987,7 +16987,7 @@
         <v>option</v>
       </c>
       <c r="I572" t="str">
-        <v/>
+        <v>applied: No lines on this receipt.</v>
       </c>
     </row>
     <row r="573">
@@ -17016,7 +17016,7 @@
         <v>option</v>
       </c>
       <c r="I573" t="str">
-        <v/>
+        <v>applied: Nothing received against this receipt yet.</v>
       </c>
     </row>
     <row r="574">
@@ -17045,7 +17045,7 @@
         <v>option</v>
       </c>
       <c r="I574" t="str">
-        <v/>
+        <v>applied by hand: Complete a short receipt?</v>
       </c>
     </row>
     <row r="575">
@@ -17074,7 +17074,7 @@
         <v>option</v>
       </c>
       <c r="I575" t="str">
-        <v/>
+        <v>applied: New receipt</v>
       </c>
     </row>
     <row r="576">
@@ -17103,7 +17103,7 @@
         <v>option</v>
       </c>
       <c r="I576" t="str">
-        <v/>
+        <v>applied: Create receipt</v>
       </c>
     </row>
     <row r="577">
@@ -17132,7 +17132,7 @@
         <v>option</v>
       </c>
       <c r="I577" t="str">
-        <v/>
+        <v>applied: No lines yet — search an item above.</v>
       </c>
     </row>
     <row r="578">
@@ -17161,7 +17161,7 @@
         <v>error-state</v>
       </c>
       <c r="I578" t="str">
-        <v/>
+        <v>applied: Could not load receipts</v>
       </c>
     </row>
     <row r="579">
@@ -17190,7 +17190,7 @@
         <v>template-text</v>
       </c>
       <c r="I579" t="str">
-        <v/>
+        <v>kept — the client's purchase order number, quoted from the document</v>
       </c>
     </row>
     <row r="580">
@@ -17219,7 +17219,7 @@
         <v>toast</v>
       </c>
       <c r="I580" t="str">
-        <v/>
+        <v>applied: ${codes.length} item(s) don't exist yet: ${codes.join(', ')} — create them to continue</v>
       </c>
     </row>
     <row r="581">
@@ -17248,7 +17248,7 @@
         <v>template-attr</v>
       </c>
       <c r="I581" t="str">
-        <v/>
+        <v>applied: Type or scan a unit code and press Enter to open its license plate</v>
       </c>
     </row>
     <row r="582">
@@ -17277,7 +17277,7 @@
         <v>template-text</v>
       </c>
       <c r="I582" t="str">
-        <v/>
+        <v>applied by hand: Find the case license plate, …</v>
       </c>
     </row>
     <row r="583">
@@ -17306,7 +17306,7 @@
         <v>template-attr</v>
       </c>
       <c r="I583" t="str">
-        <v/>
+        <v>applied: Type a license plate number…</v>
       </c>
     </row>
     <row r="584">
@@ -17335,7 +17335,7 @@
         <v>template-text</v>
       </c>
       <c r="I584" t="str">
-        <v/>
+        <v>applied: resolved from the item settings</v>
       </c>
     </row>
     <row r="585">
@@ -17364,7 +17364,7 @@
         <v>template-text</v>
       </c>
       <c r="I585" t="str">
-        <v/>
+        <v>applied: Only ${esc(max)} case${max === 1 ? '' : 's'} on this license plate</v>
       </c>
     </row>
     <row r="586">
@@ -17393,7 +17393,7 @@
         <v>template-text</v>
       </c>
       <c r="I586" t="str">
-        <v/>
+        <v>skipped — code fragment mis-extracted; the visible words in it are covered by their own rows</v>
       </c>
     </row>
     <row r="587">
@@ -17422,7 +17422,7 @@
         <v>template-text</v>
       </c>
       <c r="I587" t="str">
-        <v/>
+        <v>kept — physical goods</v>
       </c>
     </row>
     <row r="588">
@@ -17451,7 +17451,7 @@
         <v>template-text</v>
       </c>
       <c r="I588" t="str">
-        <v/>
+        <v>kept — physical goods</v>
       </c>
     </row>
     <row r="589">
@@ -17480,7 +17480,7 @@
         <v>template-text</v>
       </c>
       <c r="I589" t="str">
-        <v/>
+        <v>applied: SKU code *</v>
       </c>
     </row>
     <row r="590">
@@ -17509,7 +17509,7 @@
         <v>template-text</v>
       </c>
       <c r="I590" t="str">
-        <v/>
+        <v>human — identifier type: whose SKU code? Left as is</v>
       </c>
     </row>
     <row r="591">
@@ -17538,7 +17538,7 @@
         <v>template-text</v>
       </c>
       <c r="I591" t="str">
-        <v/>
+        <v>applied: this license plate</v>
       </c>
     </row>
     <row r="592">
@@ -17567,7 +17567,7 @@
         <v>template-text</v>
       </c>
       <c r="I592" t="str">
-        <v/>
+        <v>applied: License plate family</v>
       </c>
     </row>
     <row r="593">
@@ -17596,7 +17596,7 @@
         <v>template-text</v>
       </c>
       <c r="I593" t="str">
-        <v/>
+        <v>applied: orders holding this license plate</v>
       </c>
     </row>
     <row r="594">
@@ -17625,7 +17625,7 @@
         <v>toast</v>
       </c>
       <c r="I594" t="str">
-        <v/>
+        <v>applied: Could not read that license plate row</v>
       </c>
     </row>
     <row r="595">
@@ -17654,7 +17654,7 @@
         <v>toast</v>
       </c>
       <c r="I595" t="str">
-        <v/>
+        <v>applied: Find and select a case license plate first</v>
       </c>
     </row>
     <row r="596">
@@ -17683,7 +17683,7 @@
         <v>toast</v>
       </c>
       <c r="I596" t="str">
-        <v/>
+        <v>applied: That row has no license plate ID, so it can\'t be case-broken</v>
       </c>
     </row>
     <row r="597">
@@ -17712,7 +17712,7 @@
         <v>toast</v>
       </c>
       <c r="I597" t="str">
-        <v/>
+        <v>kept — code label</v>
       </c>
     </row>
     <row r="598">
@@ -17741,7 +17741,7 @@
         <v>empty-state</v>
       </c>
       <c r="I598" t="str">
-        <v/>
+        <v>applied: No available case license plates matching “${s}”</v>
       </c>
     </row>
     <row r="599">
@@ -17770,7 +17770,7 @@
         <v>empty-state</v>
       </c>
       <c r="I599" t="str">
-        <v/>
+        <v>applied: No receiving record for this license plate — entered directly, or it predates this WMS.</v>
       </c>
     </row>
     <row r="600">
@@ -17799,7 +17799,7 @@
         <v>option</v>
       </c>
       <c r="I600" t="str">
-        <v/>
+        <v>applied: Item</v>
       </c>
     </row>
     <row r="601">
@@ -17828,7 +17828,7 @@
         <v>option</v>
       </c>
       <c r="I601" t="str">
-        <v/>
+        <v>kept — LP allowed in column headers</v>
       </c>
     </row>
     <row r="602">
@@ -17857,7 +17857,7 @@
         <v>option</v>
       </c>
       <c r="I602" t="str">
-        <v/>
+        <v>applied: Search item, lot, license plate or location…</v>
       </c>
     </row>
     <row r="603">
@@ -17886,7 +17886,7 @@
         <v>option</v>
       </c>
       <c r="I603" t="str">
-        <v/>
+        <v>applied — same string as the row above</v>
       </c>
     </row>
     <row r="604">
@@ -17915,7 +17915,7 @@
         <v>option</v>
       </c>
       <c r="I604" t="str">
-        <v/>
+        <v>kept — pack level value</v>
       </c>
     </row>
     <row r="605">
@@ -17944,7 +17944,7 @@
         <v>option</v>
       </c>
       <c r="I605" t="str">
-        <v/>
+        <v>kept — pack level value</v>
       </c>
     </row>
     <row r="606">
@@ -17973,7 +17973,7 @@
         <v>option</v>
       </c>
       <c r="I606" t="str">
-        <v/>
+        <v>kept — code label</v>
       </c>
     </row>
     <row r="607">
@@ -18002,7 +18002,7 @@
         <v>option</v>
       </c>
       <c r="I607" t="str">
-        <v/>
+        <v>applied: Case SKU code</v>
       </c>
     </row>
     <row r="608">
@@ -18031,7 +18031,7 @@
         <v>option</v>
       </c>
       <c r="I608" t="str">
-        <v/>
+        <v>human — identifier type, see "customer SKU"</v>
       </c>
     </row>
     <row r="609">
@@ -18060,7 +18060,7 @@
         <v>option</v>
       </c>
       <c r="I609" t="str">
-        <v/>
+        <v>kept — "SKU" allowed as the code label</v>
       </c>
     </row>
     <row r="610">
@@ -18089,7 +18089,7 @@
         <v>field-error</v>
       </c>
       <c r="I610" t="str">
-        <v/>
+        <v>applied: Only ${cbSelectedLp.quantity} cases on this license plate</v>
       </c>
     </row>
     <row r="611">
@@ -18118,7 +18118,7 @@
         <v>template-text</v>
       </c>
       <c r="I611" t="str">
-        <v/>
+        <v>kept — "SKU code" is the code label</v>
       </c>
     </row>
     <row r="612">
@@ -18147,7 +18147,7 @@
         <v>template-text</v>
       </c>
       <c r="I612" t="str">
-        <v/>
+        <v>kept — "SKU" allowed as the code label</v>
       </c>
     </row>
     <row r="613">
@@ -18176,7 +18176,7 @@
         <v>template-text</v>
       </c>
       <c r="I613" t="str">
-        <v/>
+        <v>applied: Inventory returns to available at the same lot / license plate / location it came from. Th</v>
       </c>
     </row>
     <row r="614">
@@ -18205,7 +18205,7 @@
         <v>template-attr</v>
       </c>
       <c r="I614" t="str">
-        <v/>
+        <v>applied: Filter by lot # or license plate #…</v>
       </c>
     </row>
     <row r="615">
@@ -18234,7 +18234,7 @@
         <v>template-text</v>
       </c>
       <c r="I615" t="str">
-        <v/>
+        <v>kept — LP allowed in column headers</v>
       </c>
     </row>
     <row r="616">
@@ -18263,7 +18263,7 @@
         <v>template-text</v>
       </c>
       <c r="I616" t="str">
-        <v/>
+        <v>applied: Item</v>
       </c>
     </row>
     <row r="617">
@@ -18292,7 +18292,7 @@
         <v>template-attr</v>
       </c>
       <c r="I617" t="str">
-        <v/>
+        <v>applied: Search or click to browse items…</v>
       </c>
     </row>
     <row r="618">
@@ -18321,7 +18321,7 @@
         <v>template-attr</v>
       </c>
       <c r="I618" t="str">
-        <v/>
+        <v>kept — "SKU code" is the code label</v>
       </c>
     </row>
     <row r="619">
@@ -18350,7 +18350,7 @@
         <v>toast</v>
       </c>
       <c r="I619" t="str">
-        <v/>
+        <v>applied: Pick an item first</v>
       </c>
     </row>
     <row r="620">
@@ -18379,7 +18379,7 @@
         <v>empty-state</v>
       </c>
       <c r="I620" t="str">
-        <v/>
+        <v>applied: Pick a client first — items are scoped to the client.</v>
       </c>
     </row>
     <row r="621">
@@ -18408,7 +18408,7 @@
         <v>empty-state</v>
       </c>
       <c r="I621" t="str">
-        <v/>
+        <v>applied: No available inventory for this item.</v>
       </c>
     </row>
     <row r="622">
@@ -18437,7 +18437,7 @@
         <v>empty-state</v>
       </c>
       <c r="I622" t="str">
-        <v/>
+        <v>applied: No matching items</v>
       </c>
     </row>
     <row r="623">
@@ -18466,7 +18466,7 @@
         <v>option</v>
       </c>
       <c r="I623" t="str">
-        <v/>
+        <v>skipped — code fragment mis-extracted; the visible words in it are covered by their own rows</v>
       </c>
     </row>
     <row r="624">
@@ -18495,7 +18495,7 @@
         <v>option</v>
       </c>
       <c r="I624" t="str">
-        <v/>
+        <v>skipped — code fragment mis-extracted; the visible words in it are covered by their own rows</v>
       </c>
     </row>
     <row r="625">
@@ -18524,7 +18524,7 @@
         <v>option</v>
       </c>
       <c r="I625" t="str">
-        <v/>
+        <v>kept — order type value (FULFILLMENT vs B2B)</v>
       </c>
     </row>
     <row r="626">
@@ -18553,7 +18553,7 @@
         <v>option</v>
       </c>
       <c r="I626" t="str">
-        <v/>
+        <v>applied: No lines yet — search an item above, then pick the lot you want.</v>
       </c>
     </row>
     <row r="627">
@@ -18582,7 +18582,7 @@
         <v>template-text</v>
       </c>
       <c r="I627" t="str">
-        <v/>
+        <v>applied: Item</v>
       </c>
     </row>
     <row r="628">
@@ -18611,7 +18611,7 @@
         <v>text</v>
       </c>
       <c r="I628" t="str">
-        <v/>
+        <v>kept — physical goods</v>
       </c>
     </row>
     <row r="629">
@@ -18640,7 +18640,7 @@
         <v>template-text</v>
       </c>
       <c r="I629" t="str">
-        <v/>
+        <v>kept — the client's purchase order number, quoted from the document</v>
       </c>
     </row>
     <row r="630">
@@ -18669,7 +18669,7 @@
         <v>toast</v>
       </c>
       <c r="I630" t="str">
-        <v/>
+        <v>applied: Could not read that item row</v>
       </c>
     </row>
     <row r="631">
@@ -18698,7 +18698,7 @@
         <v>toast</v>
       </c>
       <c r="I631" t="str">
-        <v/>
+        <v>applied: Add at least one item</v>
       </c>
     </row>
     <row r="632">
@@ -18727,7 +18727,7 @@
         <v>empty-state</v>
       </c>
       <c r="I632" t="str">
-        <v/>
+        <v>applied: No available inventory for this item.</v>
       </c>
     </row>
     <row r="633">
@@ -18756,7 +18756,7 @@
         <v>option</v>
       </c>
       <c r="I633" t="str">
-        <v/>
+        <v>applied: Manual outbound order — choose items, quantities and a ship-to.</v>
       </c>
     </row>
     <row r="634">
@@ -18785,7 +18785,7 @@
         <v>option</v>
       </c>
       <c r="I634" t="str">
-        <v/>
+        <v>kept — the client's purchase order document</v>
       </c>
     </row>
     <row r="635">
@@ -18814,7 +18814,7 @@
         <v>option</v>
       </c>
       <c r="I635" t="str">
-        <v/>
+        <v>applied: On-hand items, lots and license plates held at the warehouse.</v>
       </c>
     </row>
     <row r="636">
@@ -18843,7 +18843,7 @@
         <v>option</v>
       </c>
       <c r="I636" t="str">
-        <v/>
+        <v>applied: Item</v>
       </c>
     </row>
     <row r="637">
@@ -18872,7 +18872,7 @@
         <v>option</v>
       </c>
       <c r="I637" t="str">
-        <v/>
+        <v>applied: No lines yet — search an item above, then pick the lot you want.</v>
       </c>
     </row>
     <row r="638">
@@ -18901,7 +18901,7 @@
         <v>template-text</v>
       </c>
       <c r="I638" t="str">
-        <v/>
+        <v>applied: Item</v>
       </c>
     </row>
     <row r="639">
@@ -18930,7 +18930,7 @@
         <v>option</v>
       </c>
       <c r="I639" t="str">
-        <v/>
+        <v>applied: Item history and license plate trace</v>
       </c>
     </row>
     <row r="640">
@@ -18959,7 +18959,7 @@
         <v>option</v>
       </c>
       <c r="I640" t="str">
-        <v/>
+        <v>applied: Search by item or lot, then follow the license-plate family — receiving, picks, shipments,</v>
       </c>
     </row>
     <row r="641">
@@ -18988,7 +18988,7 @@
         <v>option</v>
       </c>
       <c r="I641" t="str">
-        <v/>
+        <v>applied: Item</v>
       </c>
     </row>
     <row r="642">
@@ -19017,7 +19017,7 @@
         <v>option</v>
       </c>
       <c r="I642" t="str">
-        <v/>
+        <v>kept — LP allowed in column headers</v>
       </c>
     </row>
     <row r="643">
@@ -19046,7 +19046,7 @@
         <v>text</v>
       </c>
       <c r="I643" t="str">
-        <v/>
+        <v>applied: Item history → license plate traceability</v>
       </c>
     </row>
     <row r="644">
@@ -19075,7 +19075,7 @@
         <v>text</v>
       </c>
       <c r="I644" t="str">
-        <v/>
+        <v>applied: Loading license plate trace…</v>
       </c>
     </row>
     <row r="645">
@@ -19104,7 +19104,7 @@
         <v>text</v>
       </c>
       <c r="I645" t="str">
-        <v/>
+        <v>applied: Enter a license plate number</v>
       </c>
     </row>
     <row r="646">
@@ -19133,7 +19133,7 @@
         <v>text</v>
       </c>
       <c r="I646" t="str">
-        <v/>
+        <v>applied: Manual license plate search: ${lp}</v>
       </c>
     </row>
     <row r="647">
@@ -19162,7 +19162,7 @@
         <v>text</v>
       </c>
       <c r="I647" t="str">
-        <v/>
+        <v>applied: No license plates or allocations found.</v>
       </c>
     </row>
     <row r="648">
@@ -19191,7 +19191,7 @@
         <v>option</v>
       </c>
       <c r="I648" t="str">
-        <v/>
+        <v>applied: Optional — needed to resolve items and license plates</v>
       </c>
     </row>
     <row r="649">
@@ -19220,7 +19220,7 @@
         <v>option</v>
       </c>
       <c r="I649" t="str">
-        <v/>
+        <v>kept — physical pallet</v>
       </c>
     </row>
     <row r="650">
@@ -19249,7 +19249,7 @@
         <v>option</v>
       </c>
       <c r="I650" t="str">
-        <v/>
+        <v>kept — LP allowed in column headers</v>
       </c>
     </row>
     <row r="651">
@@ -19278,7 +19278,7 @@
         <v>toast</v>
       </c>
       <c r="I651" t="str">
-        <v/>
+        <v>applied: ${d.uid} is ${UNIT_STATUS_LABEL[d.status] || d.status} and not on a license plate${d.order</v>
       </c>
     </row>
     <row r="652">
@@ -19307,7 +19307,7 @@
         <v>toast</v>
       </c>
       <c r="I652" t="str">
-        <v/>
+        <v>applied: ${d.uid} is on ${d.lpNumber} but that license plate has no inventory record</v>
       </c>
     </row>
     <row r="653">
@@ -19336,7 +19336,7 @@
         <v>api-error</v>
       </c>
       <c r="I653" t="str">
-        <v/>
+        <v>applied: A committed import is part of the history and cannot be deleted.</v>
       </c>
     </row>
     <row r="654">
@@ -19365,7 +19365,7 @@
         <v>api-error</v>
       </c>
       <c r="I654" t="str">
-        <v/>
+        <v>applied: This account has been deactivated — contact an admin.</v>
       </c>
     </row>
     <row r="655">
@@ -19394,7 +19394,7 @@
         <v>api-error</v>
       </c>
       <c r="I655" t="str">
-        <v/>
+        <v>applied: Portal account has no client.</v>
       </c>
     </row>
     <row r="656">
@@ -19423,7 +19423,7 @@
         <v>api-error</v>
       </c>
       <c r="I656" t="str">
-        <v/>
+        <v>applied: An account with ${email} already exists.</v>
       </c>
     </row>
     <row r="657">
@@ -19452,7 +19452,7 @@
         <v>api-error</v>
       </c>
       <c r="I657" t="str">
-        <v/>
+        <v>applied: You cannot deactivate your own account.</v>
       </c>
     </row>
     <row r="658">
@@ -19481,7 +19481,7 @@
         <v>api-error</v>
       </c>
       <c r="I658" t="str">
-        <v/>
+        <v>applied: Account configuration error — contact support.</v>
       </c>
     </row>
     <row r="659">
@@ -19510,7 +19510,7 @@
         <v>api-error</v>
       </c>
       <c r="I659" t="str">
-        <v/>
+        <v>applied: Cannot complete shipment — order is in ${order.status} (must be PACKING or STAGED).</v>
       </c>
     </row>
     <row r="660">
@@ -19539,7 +19539,7 @@
         <v>api-error</v>
       </c>
       <c r="I660" t="str">
-        <v/>
+        <v>kept — dock status banner, upper case by design</v>
       </c>
     </row>
     <row r="661">
@@ -19568,7 +19568,7 @@
         <v>api-error</v>
       </c>
       <c r="I661" t="str">
-        <v/>
+        <v>kept — dock status banner</v>
       </c>
     </row>
     <row r="662">
@@ -19597,7 +19597,7 @@
         <v>api-error</v>
       </c>
       <c r="I662" t="str">
-        <v/>
+        <v>kept — dock status banner</v>
       </c>
     </row>
     <row r="663">
@@ -19626,7 +19626,7 @@
         <v>api-error</v>
       </c>
       <c r="I663" t="str">
-        <v/>
+        <v>kept — login accounts</v>
       </c>
     </row>
     <row r="664">
@@ -19655,7 +19655,7 @@
         <v>api-error</v>
       </c>
       <c r="I664" t="str">
-        <v/>
+        <v>applied: You cannot change your own account here.</v>
       </c>
     </row>
     <row r="665">
@@ -19684,7 +19684,7 @@
         <v>api-error</v>
       </c>
       <c r="I665" t="str">
-        <v/>
+        <v>applied: An account with ${email} already exists.</v>
       </c>
     </row>
     <row r="666">
@@ -19713,7 +19713,7 @@
         <v>api-error</v>
       </c>
       <c r="I666" t="str">
-        <v/>
+        <v>applied: A portal account cannot be turned into an ops account or vice versa — create a new account</v>
       </c>
     </row>
     <row r="667">
@@ -19742,7 +19742,7 @@
         <v>api-error</v>
       </c>
       <c r="I667" t="str">
-        <v/>
+        <v>applied: You cannot deactivate your own account.</v>
       </c>
     </row>
     <row r="668">
@@ -19771,7 +19771,7 @@
         <v>api-error</v>
       </c>
       <c r="I668" t="str">
-        <v/>
+        <v>applied: ${role.name} accounts have no per-user overrides (admin has everything).</v>
       </c>
     </row>
     <row r="669">
@@ -19800,7 +19800,7 @@
         <v>api-error</v>
       </c>
       <c r="I669" t="str">
-        <v/>
+        <v>applied: "${P.labelOf(c.key)}" is ${P.isPortalKey(c.key) ? 'a portal' : 'an ops'} permission — ${cu</v>
       </c>
     </row>
     <row r="670">
@@ -19829,7 +19829,7 @@
         <v>html-text</v>
       </c>
       <c r="I670" t="str">
-        <v/>
+        <v>kept — page name</v>
       </c>
     </row>
     <row r="671">
@@ -19858,7 +19858,7 @@
         <v>html-text</v>
       </c>
       <c r="I671" t="str">
-        <v/>
+        <v>applied: Client portal</v>
       </c>
     </row>
     <row r="672">
@@ -19887,7 +19887,7 @@
         <v>html-text</v>
       </c>
       <c r="I672" t="str">
-        <v/>
+        <v>kept — physical shipment</v>
       </c>
     </row>
     <row r="673">
@@ -19916,7 +19916,7 @@
         <v>html-text</v>
       </c>
       <c r="I673" t="str">
-        <v/>
+        <v>kept — physical shipments that left</v>
       </c>
     </row>
     <row r="674">
@@ -19945,7 +19945,7 @@
         <v>html-text</v>
       </c>
       <c r="I674" t="str">
-        <v/>
+        <v>kept — Receiving is the page name</v>
       </c>
     </row>
     <row r="675">
@@ -19974,7 +19974,7 @@
         <v>html-text</v>
       </c>
       <c r="I675" t="str">
-        <v/>
+        <v>kept — page name</v>
       </c>
     </row>
     <row r="676">
@@ -20003,7 +20003,7 @@
         <v>html-text</v>
       </c>
       <c r="I676" t="str">
-        <v/>
+        <v>applied: Receiving</v>
       </c>
     </row>
     <row r="677">
@@ -20032,7 +20032,7 @@
         <v>html-text</v>
       </c>
       <c r="I677" t="str">
-        <v/>
+        <v>kept — ship-to party</v>
       </c>
     </row>
     <row r="678">
@@ -20061,7 +20061,7 @@
         <v>html-text</v>
       </c>
       <c r="I678" t="str">
-        <v/>
+        <v>kept — login</v>
       </c>
     </row>
     <row r="679">
@@ -20090,7 +20090,7 @@
         <v>html-text</v>
       </c>
       <c r="I679" t="str">
-        <v/>
+        <v>kept — ledger accounts</v>
       </c>
     </row>
     <row r="680">
@@ -20119,7 +20119,7 @@
         <v>html-text</v>
       </c>
       <c r="I680" t="str">
-        <v/>
+        <v>applied: Rate-shop a shipment for a client or prospect — price with markup, save, print</v>
       </c>
     </row>
     <row r="681">
@@ -20148,7 +20148,7 @@
         <v>html-text</v>
       </c>
       <c r="I681" t="str">
-        <v/>
+        <v>kept — ship-to customers reached in the trace</v>
       </c>
     </row>
     <row r="682">
@@ -20177,7 +20177,7 @@
         <v>html-text</v>
       </c>
       <c r="I682" t="str">
-        <v/>
+        <v>kept — ship-to customer; shipment = what left</v>
       </c>
     </row>
     <row r="683">
@@ -20206,7 +20206,7 @@
         <v>html-text</v>
       </c>
       <c r="I683" t="str">
-        <v/>
+        <v>kept — ship-to party on the order</v>
       </c>
     </row>
     <row r="684">
@@ -20235,7 +20235,7 @@
         <v>html-text</v>
       </c>
       <c r="I684" t="str">
-        <v/>
+        <v>kept — physical shipment / tracking number</v>
       </c>
     </row>
     <row r="685">
@@ -20264,7 +20264,7 @@
         <v>html-text</v>
       </c>
       <c r="I685" t="str">
-        <v/>
+        <v>kept — "account" means a login</v>
       </c>
     </row>
     <row r="686">
@@ -20293,7 +20293,7 @@
         <v>html-text</v>
       </c>
       <c r="I686" t="str">
-        <v/>
+        <v>kept — ship-to customer approved it</v>
       </c>
     </row>
     <row r="687">
@@ -20322,7 +20322,7 @@
         <v>option</v>
       </c>
       <c r="I687" t="str">
-        <v/>
+        <v>kept — ledger account</v>
       </c>
     </row>
     <row r="688">
@@ -20351,7 +20351,7 @@
         <v>template-text</v>
       </c>
       <c r="I688" t="str">
-        <v/>
+        <v>applied: Client rules</v>
       </c>
     </row>
     <row r="689">
@@ -20380,7 +20380,7 @@
         <v>empty-state</v>
       </c>
       <c r="I689" t="str">
-        <v/>
+        <v>kept — physical shipments</v>
       </c>
     </row>
     <row r="690">
@@ -20409,7 +20409,7 @@
         <v>template-text</v>
       </c>
       <c r="I690" t="str">
-        <v/>
+        <v>kept — physical shipments that left</v>
       </c>
     </row>
     <row r="691">
@@ -20438,7 +20438,7 @@
         <v>toast</v>
       </c>
       <c r="I691" t="str">
-        <v/>
+        <v>kept — physical shipments</v>
       </c>
     </row>
     <row r="692">
@@ -20467,7 +20467,7 @@
         <v>template-text</v>
       </c>
       <c r="I692" t="str">
-        <v/>
+        <v>kept — verb</v>
       </c>
     </row>
     <row r="693">
@@ -20496,7 +20496,7 @@
         <v>template-text</v>
       </c>
       <c r="I693" t="str">
-        <v/>
+        <v>kept — the inbound physical shipment</v>
       </c>
     </row>
     <row r="694">
@@ -20525,7 +20525,7 @@
         <v>option</v>
       </c>
       <c r="I694" t="str">
-        <v/>
+        <v>kept — page name</v>
       </c>
     </row>
     <row r="695">
@@ -20554,7 +20554,7 @@
         <v>option</v>
       </c>
       <c r="I695" t="str">
-        <v/>
+        <v>skipped — code fragment mis-extracted; the visible words in it are covered by their own rows</v>
       </c>
     </row>
     <row r="696">
@@ -20583,7 +20583,7 @@
         <v>template-text</v>
       </c>
       <c r="I696" t="str">
-        <v/>
+        <v>human — identifier type: is this the client's barcode or the ship-to customer's? Left as is</v>
       </c>
     </row>
     <row r="697">
@@ -20612,7 +20612,7 @@
         <v>template-text</v>
       </c>
       <c r="I697" t="str">
-        <v/>
+        <v>applied: Receipt origin</v>
       </c>
     </row>
     <row r="698">
@@ -20641,7 +20641,7 @@
         <v>option</v>
       </c>
       <c r="I698" t="str">
-        <v/>
+        <v>human — identifier type, see "customer barcode"</v>
       </c>
     </row>
     <row r="699">
@@ -20670,7 +20670,7 @@
         <v>template-text</v>
       </c>
       <c r="I699" t="str">
-        <v/>
+        <v>kept — physical shipment</v>
       </c>
     </row>
     <row r="700">
@@ -20699,7 +20699,7 @@
         <v>template-text</v>
       </c>
       <c r="I700" t="str">
-        <v/>
+        <v>kept — ship-to customer</v>
       </c>
     </row>
     <row r="701">
@@ -20728,7 +20728,7 @@
         <v>template-text</v>
       </c>
       <c r="I701" t="str">
-        <v/>
+        <v>skipped — code fragment mis-extracted; the visible words in it are covered by their own rows</v>
       </c>
     </row>
     <row r="702">
@@ -20757,7 +20757,7 @@
         <v>template-text</v>
       </c>
       <c r="I702" t="str">
-        <v/>
+        <v>kept — ship-to party</v>
       </c>
     </row>
     <row r="703">
@@ -20786,7 +20786,7 @@
         <v>toast</v>
       </c>
       <c r="I703" t="str">
-        <v/>
+        <v>kept — verb</v>
       </c>
     </row>
     <row r="704">
@@ -20815,7 +20815,7 @@
         <v>option</v>
       </c>
       <c r="I704" t="str">
-        <v/>
+        <v>kept — ship-to party on the order</v>
       </c>
     </row>
     <row r="705">
@@ -20844,7 +20844,7 @@
         <v>option</v>
       </c>
       <c r="I705" t="str">
-        <v/>
+        <v>kept — ship-to customer</v>
       </c>
     </row>
     <row r="706">
@@ -20873,7 +20873,7 @@
         <v>option</v>
       </c>
       <c r="I706" t="str">
-        <v/>
+        <v>kept — order-detail tab for the physical shipment</v>
       </c>
     </row>
     <row r="707">
@@ -20902,7 +20902,7 @@
         <v>option</v>
       </c>
       <c r="I707" t="str">
-        <v/>
+        <v>kept — physical shipments</v>
       </c>
     </row>
     <row r="708">
@@ -20931,7 +20931,7 @@
         <v>option</v>
       </c>
       <c r="I708" t="str">
-        <v/>
+        <v>kept — ship-to customer</v>
       </c>
     </row>
     <row r="709">
@@ -20960,7 +20960,7 @@
         <v>template-text</v>
       </c>
       <c r="I709" t="str">
-        <v/>
+        <v>kept — physical shipment</v>
       </c>
     </row>
     <row r="710">
@@ -20989,7 +20989,7 @@
         <v>option</v>
       </c>
       <c r="I710" t="str">
-        <v/>
+        <v>skipped — code fragment mis-extracted; the visible words in it are covered by their own rows</v>
       </c>
     </row>
     <row r="711">
@@ -21018,7 +21018,7 @@
         <v>option</v>
       </c>
       <c r="I711" t="str">
-        <v/>
+        <v>kept — login</v>
       </c>
     </row>
     <row r="712">
@@ -21047,7 +21047,7 @@
         <v>empty-state</v>
       </c>
       <c r="I712" t="str">
-        <v/>
+        <v>kept — the client's account, second person</v>
       </c>
     </row>
     <row r="713">
@@ -21076,7 +21076,7 @@
         <v>option</v>
       </c>
       <c r="I713" t="str">
-        <v/>
+        <v>applied: My account</v>
       </c>
     </row>
     <row r="714">
@@ -21105,7 +21105,7 @@
         <v>option</v>
       </c>
       <c r="I714" t="str">
-        <v/>
+        <v>kept — the client's billing account; reads correctly to the client</v>
       </c>
     </row>
     <row r="715">
@@ -21134,7 +21134,7 @@
         <v>option</v>
       </c>
       <c r="I715" t="str">
-        <v/>
+        <v>kept — verb / physical shipments</v>
       </c>
     </row>
     <row r="716">
@@ -21163,7 +21163,7 @@
         <v>text</v>
       </c>
       <c r="I716" t="str">
-        <v/>
+        <v>applied: Client portal · ${U.fullName}</v>
       </c>
     </row>
     <row r="717">
@@ -21192,7 +21192,7 @@
         <v>template-text</v>
       </c>
       <c r="I717" t="str">
-        <v/>
+        <v>kept — ship-to party on the order</v>
       </c>
     </row>
     <row r="718">
@@ -21221,7 +21221,7 @@
         <v>template-text</v>
       </c>
       <c r="I718" t="str">
-        <v/>
+        <v>applied: TEST RATES — do not send to a client.</v>
       </c>
     </row>
     <row r="719">
@@ -21250,7 +21250,7 @@
         <v>template-text</v>
       </c>
       <c r="I719" t="str">
-        <v/>
+        <v>skipped — code fragment mis-extracted; the visible words in it are covered by their own rows</v>
       </c>
     </row>
     <row r="720">
@@ -21279,7 +21279,7 @@
         <v>option</v>
       </c>
       <c r="I720" t="str">
-        <v/>
+        <v>applied: Client or prospect</v>
       </c>
     </row>
     <row r="721">
@@ -21308,7 +21308,7 @@
         <v>attr</v>
       </c>
       <c r="I721" t="str">
-        <v/>
+        <v>kept — login</v>
       </c>
     </row>
     <row r="722">
@@ -21337,7 +21337,7 @@
         <v>option</v>
       </c>
       <c r="I722" t="str">
-        <v/>
+        <v>kept — ship-to party on the order</v>
       </c>
     </row>
     <row r="723">

--- a/docs/COPY-AUDIT.xlsx
+++ b/docs/COPY-AUDIT.xlsx
@@ -15247,7 +15247,7 @@
         <v>html-text</v>
       </c>
       <c r="I512" t="str">
-        <v>human — "customer POs" on an order: the ship-to customer's PO or the client's? Left as is</v>
+        <v>kept — decided 2026-09-06: "customer POs" stays</v>
       </c>
     </row>
     <row r="513">
@@ -17509,7 +17509,7 @@
         <v>template-text</v>
       </c>
       <c r="I590" t="str">
-        <v>human — identifier type: whose SKU code? Left as is</v>
+        <v>applied: client SKU (label only, key customer_sku unchanged)</v>
       </c>
     </row>
     <row r="591">
@@ -18031,7 +18031,7 @@
         <v>option</v>
       </c>
       <c r="I608" t="str">
-        <v>human — identifier type, see "customer SKU"</v>
+        <v>applied: Client SKU (label only, key customer_sku unchanged)</v>
       </c>
     </row>
     <row r="609">
@@ -20583,7 +20583,7 @@
         <v>template-text</v>
       </c>
       <c r="I696" t="str">
-        <v>human — identifier type: is this the client's barcode or the ship-to customer's? Left as is</v>
+        <v>applied: client barcode (label only, key customer_barcode unchanged)</v>
       </c>
     </row>
     <row r="697">
@@ -20641,7 +20641,7 @@
         <v>option</v>
       </c>
       <c r="I698" t="str">
-        <v>human — identifier type, see "customer barcode"</v>
+        <v>applied: Client barcode (label only, key customer_barcode unchanged)</v>
       </c>
     </row>
     <row r="699">
